--- a/data/pls.xlsx
+++ b/data/pls.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30030"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rssla\Desktop\SPE JARDIM LUZ\01. Relatorio Obra Ramon Gerenciamento\meu-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{131DB70F-07EE-46C2-A86D-343692F063CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F974BA5-7C01-4563-B83A-DB26BE752493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{ECBE0EBD-AF5F-4C5B-967D-6D79DF9A9648}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1697,6 +1700,1883 @@
 </styleSheet>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Instruções de preenchimento"/>
+      <sheetName val="Cronograma"/>
+      <sheetName val="RAE"/>
+      <sheetName val="GRÁFICO"/>
+      <sheetName val="CurvasObservadas"/>
+      <sheetName val="Cronograma_Apoio"/>
+      <sheetName val="Anexo I Fotos"/>
+      <sheetName val="PLS_MODELO_LIVRE"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7">
+        <row r="16">
+          <cell r="GX16">
+            <v>0</v>
+          </cell>
+          <cell r="GY16">
+            <v>100</v>
+          </cell>
+          <cell r="GZ16">
+            <v>0.71832955482661864</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="GX17">
+            <v>0</v>
+          </cell>
+          <cell r="GY17">
+            <v>100</v>
+          </cell>
+          <cell r="GZ17">
+            <v>0.61163199478507113</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="GX18">
+            <v>0</v>
+          </cell>
+          <cell r="GY18">
+            <v>100</v>
+          </cell>
+          <cell r="GZ18">
+            <v>1.8761353243475117E-2</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="GX19">
+            <v>2.9411764705882351</v>
+          </cell>
+          <cell r="GY19">
+            <v>58.82352941176471</v>
+          </cell>
+          <cell r="GZ19">
+            <v>0.61724456202773725</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="GX20">
+            <v>2.9411764705882351</v>
+          </cell>
+          <cell r="GY20">
+            <v>58.82352941176471</v>
+          </cell>
+          <cell r="GZ20">
+            <v>0.48913676250449695</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="GX21">
+            <v>2.9411764705882351</v>
+          </cell>
+          <cell r="GY21">
+            <v>58.82352941176471</v>
+          </cell>
+          <cell r="GZ21">
+            <v>0.10015640009148638</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="GX22">
+            <v>2.9411764705882351</v>
+          </cell>
+          <cell r="GY22">
+            <v>58.82352941176471</v>
+          </cell>
+          <cell r="GZ22">
+            <v>4.5419444917470214E-2</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="GX23">
+            <v>2.9411764705882351</v>
+          </cell>
+          <cell r="GY23">
+            <v>58.82352941176471</v>
+          </cell>
+          <cell r="GZ23">
+            <v>3.726721268147376E-2</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="GX24">
+            <v>2.9411764705882351</v>
+          </cell>
+          <cell r="GY24">
+            <v>58.82352941176471</v>
+          </cell>
+          <cell r="GZ24">
+            <v>2.3885371076554876E-2</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="GX25">
+            <v>2.9411764705882351</v>
+          </cell>
+          <cell r="GY25">
+            <v>58.82352941176471</v>
+          </cell>
+          <cell r="GZ25">
+            <v>2.3431996847346097</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="GX28">
+            <v>0</v>
+          </cell>
+          <cell r="GY28">
+            <v>100</v>
+          </cell>
+          <cell r="GZ28">
+            <v>0.25099673738745631</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="GX29">
+            <v>0</v>
+          </cell>
+          <cell r="GY29">
+            <v>100</v>
+          </cell>
+          <cell r="GZ29">
+            <v>0.16877675666567413</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="GX30">
+            <v>0</v>
+          </cell>
+          <cell r="GY30">
+            <v>100</v>
+          </cell>
+          <cell r="GZ30">
+            <v>1.1845296202093973E-2</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="GX31">
+            <v>0</v>
+          </cell>
+          <cell r="GY31">
+            <v>100</v>
+          </cell>
+          <cell r="GZ31">
+            <v>0.61929638469765858</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="GX32">
+            <v>0</v>
+          </cell>
+          <cell r="GY32">
+            <v>100</v>
+          </cell>
+          <cell r="GZ32">
+            <v>3.0640401025775945E-2</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="GX33">
+            <v>0</v>
+          </cell>
+          <cell r="GY33">
+            <v>100</v>
+          </cell>
+          <cell r="GZ33">
+            <v>0.10949295453574681</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="GX35">
+            <v>0</v>
+          </cell>
+          <cell r="GY35">
+            <v>100</v>
+          </cell>
+          <cell r="GZ35">
+            <v>0.17961874472094869</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="GX36">
+            <v>0</v>
+          </cell>
+          <cell r="GY36">
+            <v>100</v>
+          </cell>
+          <cell r="GZ36">
+            <v>5.7179702221948035E-2</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="GX37">
+            <v>0</v>
+          </cell>
+          <cell r="GY37">
+            <v>100</v>
+          </cell>
+          <cell r="GZ37">
+            <v>4.6698139560893592</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="GX39">
+            <v>0</v>
+          </cell>
+          <cell r="GY39">
+            <v>100</v>
+          </cell>
+          <cell r="GZ39">
+            <v>1.5195610042846177</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="GX41">
+            <v>0</v>
+          </cell>
+          <cell r="GY41">
+            <v>100</v>
+          </cell>
+          <cell r="GZ41">
+            <v>1.3036217881348131</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="GX42">
+            <v>0</v>
+          </cell>
+          <cell r="GY42">
+            <v>100</v>
+          </cell>
+          <cell r="GZ42">
+            <v>1.4911141731378164</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="GX43">
+            <v>0</v>
+          </cell>
+          <cell r="GY43">
+            <v>100</v>
+          </cell>
+          <cell r="GZ43">
+            <v>1.4581168181869806</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="GX44">
+            <v>0</v>
+          </cell>
+          <cell r="GY44">
+            <v>100</v>
+          </cell>
+          <cell r="GZ44">
+            <v>0.3394013652085951</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="GX45">
+            <v>0</v>
+          </cell>
+          <cell r="GY45">
+            <v>100</v>
+          </cell>
+          <cell r="GZ45">
+            <v>3.7711262800955013E-2</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="GX46">
+            <v>0</v>
+          </cell>
+          <cell r="GY46">
+            <v>100</v>
+          </cell>
+          <cell r="GZ46">
+            <v>0.17912849830453628</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="GX47">
+            <v>0</v>
+          </cell>
+          <cell r="GY47">
+            <v>100</v>
+          </cell>
+          <cell r="GZ47">
+            <v>0.14141723550358129</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="GX48">
+            <v>0</v>
+          </cell>
+          <cell r="GY48">
+            <v>100</v>
+          </cell>
+          <cell r="GZ48">
+            <v>0.17912849830453628</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="GX49">
+            <v>0</v>
+          </cell>
+          <cell r="GY49">
+            <v>100</v>
+          </cell>
+          <cell r="GZ49">
+            <v>0.22626757680573006</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="GX50">
+            <v>0</v>
+          </cell>
+          <cell r="GY50">
+            <v>100</v>
+          </cell>
+          <cell r="GZ50">
+            <v>0.35354308875895318</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="GX51">
+            <v>0</v>
+          </cell>
+          <cell r="GY51">
+            <v>100</v>
+          </cell>
+          <cell r="GZ51">
+            <v>0.45253515361146013</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="GX52">
+            <v>0</v>
+          </cell>
+          <cell r="GY52">
+            <v>100</v>
+          </cell>
+          <cell r="GZ52">
+            <v>0.44782124576134069</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="GX53">
+            <v>0</v>
+          </cell>
+          <cell r="GY53">
+            <v>100</v>
+          </cell>
+          <cell r="GZ53">
+            <v>0.92392593862339767</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="GX54">
+            <v>0</v>
+          </cell>
+          <cell r="GY54">
+            <v>100</v>
+          </cell>
+          <cell r="GZ54">
+            <v>6.2412139935580537</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="GX55">
+            <v>0</v>
+          </cell>
+          <cell r="GY55">
+            <v>100</v>
+          </cell>
+          <cell r="GZ55">
+            <v>3.4037384439807465E-2</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="GX56">
+            <v>0</v>
+          </cell>
+          <cell r="GY56">
+            <v>100</v>
+          </cell>
+          <cell r="GZ56">
+            <v>7.8034091831678198</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="GX57">
+            <v>0</v>
+          </cell>
+          <cell r="GY57">
+            <v>100</v>
+          </cell>
+          <cell r="GZ57">
+            <v>0.81119306808318525</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="GX60">
+            <v>0</v>
+          </cell>
+          <cell r="GY60">
+            <v>100</v>
+          </cell>
+          <cell r="GZ60">
+            <v>0.15592744523058322</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="GX61">
+            <v>0</v>
+          </cell>
+          <cell r="GY61">
+            <v>100</v>
+          </cell>
+          <cell r="GZ61">
+            <v>0.18107920765107266</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="GX62">
+            <v>0</v>
+          </cell>
+          <cell r="GY62">
+            <v>0</v>
+          </cell>
+          <cell r="GZ62">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="GX64">
+            <v>17.5</v>
+          </cell>
+          <cell r="GY64">
+            <v>18.333333333333332</v>
+          </cell>
+          <cell r="GZ64">
+            <v>0.42992471626551543</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="GX65">
+            <v>0</v>
+          </cell>
+          <cell r="GY65">
+            <v>0</v>
+          </cell>
+          <cell r="GZ65">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="GX67">
+            <v>0</v>
+          </cell>
+          <cell r="GY67">
+            <v>100</v>
+          </cell>
+          <cell r="GZ67">
+            <v>0.50742729063190206</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="GX68">
+            <v>0</v>
+          </cell>
+          <cell r="GY68">
+            <v>0</v>
+          </cell>
+          <cell r="GZ68">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="GX69">
+            <v>0</v>
+          </cell>
+          <cell r="GY69">
+            <v>0</v>
+          </cell>
+          <cell r="GZ69">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="GX70">
+            <v>0</v>
+          </cell>
+          <cell r="GY70">
+            <v>0</v>
+          </cell>
+          <cell r="GZ70">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="GX71">
+            <v>0</v>
+          </cell>
+          <cell r="GY71">
+            <v>0</v>
+          </cell>
+          <cell r="GZ71">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="73">
+          <cell r="GX73">
+            <v>0</v>
+          </cell>
+          <cell r="GY73">
+            <v>0.83333333333333337</v>
+          </cell>
+          <cell r="GZ73">
+            <v>3.8606905292477688E-3</v>
+          </cell>
+        </row>
+        <row r="74">
+          <cell r="GX74">
+            <v>0</v>
+          </cell>
+          <cell r="GY74">
+            <v>0.83333333333333337</v>
+          </cell>
+          <cell r="GZ74">
+            <v>7.2248494316162959E-3</v>
+          </cell>
+        </row>
+        <row r="75">
+          <cell r="GX75">
+            <v>0</v>
+          </cell>
+          <cell r="GY75">
+            <v>0.83333333333333337</v>
+          </cell>
+          <cell r="GZ75">
+            <v>7.194994681898873E-3</v>
+          </cell>
+        </row>
+        <row r="76">
+          <cell r="GX76">
+            <v>0</v>
+          </cell>
+          <cell r="GY76">
+            <v>0.83333333333333337</v>
+          </cell>
+          <cell r="GZ76">
+            <v>2.8707698807226996E-3</v>
+          </cell>
+        </row>
+        <row r="77">
+          <cell r="GX77">
+            <v>0</v>
+          </cell>
+          <cell r="GY77">
+            <v>0.83333333333333337</v>
+          </cell>
+          <cell r="GZ77">
+            <v>2.2726928222388042E-3</v>
+          </cell>
+        </row>
+        <row r="78">
+          <cell r="GX78">
+            <v>0</v>
+          </cell>
+          <cell r="GY78">
+            <v>0</v>
+          </cell>
+          <cell r="GZ78">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="80">
+          <cell r="GX80">
+            <v>0</v>
+          </cell>
+          <cell r="GY80">
+            <v>0.83333333333333337</v>
+          </cell>
+          <cell r="GZ80">
+            <v>8.7365446835579953E-4</v>
+          </cell>
+        </row>
+        <row r="81">
+          <cell r="GX81">
+            <v>0</v>
+          </cell>
+          <cell r="GY81">
+            <v>0.83333333333333337</v>
+          </cell>
+          <cell r="GZ81">
+            <v>2.0643145257242769E-3</v>
+          </cell>
+        </row>
+        <row r="82">
+          <cell r="GX82">
+            <v>0</v>
+          </cell>
+          <cell r="GY82">
+            <v>0.83333333333333337</v>
+          </cell>
+          <cell r="GZ82">
+            <v>1.3083533731393705E-3</v>
+          </cell>
+        </row>
+        <row r="84">
+          <cell r="GX84">
+            <v>0</v>
+          </cell>
+          <cell r="GY84">
+            <v>0.83333333333333337</v>
+          </cell>
+          <cell r="GZ84">
+            <v>3.2060701461016912E-3</v>
+          </cell>
+        </row>
+        <row r="85">
+          <cell r="GX85">
+            <v>0</v>
+          </cell>
+          <cell r="GY85">
+            <v>0.83333333333333337</v>
+          </cell>
+          <cell r="GZ85">
+            <v>1.445566981317608E-3</v>
+          </cell>
+        </row>
+        <row r="88">
+          <cell r="GX88">
+            <v>0</v>
+          </cell>
+          <cell r="GY88">
+            <v>0</v>
+          </cell>
+          <cell r="GZ88">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="89">
+          <cell r="GX89">
+            <v>0</v>
+          </cell>
+          <cell r="GY89">
+            <v>0</v>
+          </cell>
+          <cell r="GZ89">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="GX90">
+            <v>0</v>
+          </cell>
+          <cell r="GY90">
+            <v>0</v>
+          </cell>
+          <cell r="GZ90">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="GX92">
+            <v>0</v>
+          </cell>
+          <cell r="GY92">
+            <v>0</v>
+          </cell>
+          <cell r="GZ92">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="GX93">
+            <v>0</v>
+          </cell>
+          <cell r="GY93">
+            <v>0</v>
+          </cell>
+          <cell r="GZ93">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="94">
+          <cell r="GX94">
+            <v>0</v>
+          </cell>
+          <cell r="GY94">
+            <v>0</v>
+          </cell>
+          <cell r="GZ94">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="95">
+          <cell r="GX95">
+            <v>0</v>
+          </cell>
+          <cell r="GY95">
+            <v>100</v>
+          </cell>
+          <cell r="GZ95">
+            <v>0.21457420985364542</v>
+          </cell>
+        </row>
+        <row r="96">
+          <cell r="GX96">
+            <v>0</v>
+          </cell>
+          <cell r="GY96">
+            <v>100</v>
+          </cell>
+          <cell r="GZ96">
+            <v>1.7316729043727531E-2</v>
+          </cell>
+        </row>
+        <row r="97">
+          <cell r="GX97">
+            <v>6.666666666666667</v>
+          </cell>
+          <cell r="GY97">
+            <v>52.5</v>
+          </cell>
+          <cell r="GZ97">
+            <v>7.4123228824227699E-2</v>
+          </cell>
+        </row>
+        <row r="98">
+          <cell r="GX98">
+            <v>0</v>
+          </cell>
+          <cell r="GY98">
+            <v>100</v>
+          </cell>
+          <cell r="GZ98">
+            <v>4.5275199337256556E-3</v>
+          </cell>
+        </row>
+        <row r="99">
+          <cell r="GX99">
+            <v>0</v>
+          </cell>
+          <cell r="GY99">
+            <v>0</v>
+          </cell>
+          <cell r="GZ99">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="100">
+          <cell r="GX100">
+            <v>0</v>
+          </cell>
+          <cell r="GY100">
+            <v>100</v>
+          </cell>
+          <cell r="GZ100">
+            <v>0.13982025780211782</v>
+          </cell>
+        </row>
+        <row r="101">
+          <cell r="GX101">
+            <v>0</v>
+          </cell>
+          <cell r="GY101">
+            <v>100</v>
+          </cell>
+          <cell r="GZ101">
+            <v>0.12422825336259198</v>
+          </cell>
+        </row>
+        <row r="104">
+          <cell r="GX104">
+            <v>0</v>
+          </cell>
+          <cell r="GY104">
+            <v>100</v>
+          </cell>
+          <cell r="GZ104">
+            <v>4.1238497616965537</v>
+          </cell>
+        </row>
+        <row r="105">
+          <cell r="GX105">
+            <v>13.333333333333334</v>
+          </cell>
+          <cell r="GY105">
+            <v>100</v>
+          </cell>
+          <cell r="GZ105">
+            <v>0.14855800453217763</v>
+          </cell>
+        </row>
+        <row r="107">
+          <cell r="GX107">
+            <v>13.333333333333334</v>
+          </cell>
+          <cell r="GY107">
+            <v>73.333333333333329</v>
+          </cell>
+          <cell r="GZ107">
+            <v>0.14218455285300277</v>
+          </cell>
+        </row>
+        <row r="108">
+          <cell r="GX108">
+            <v>13.333333333333334</v>
+          </cell>
+          <cell r="GY108">
+            <v>73.333333333333329</v>
+          </cell>
+          <cell r="GZ108">
+            <v>0.63849337216379987</v>
+          </cell>
+        </row>
+        <row r="109">
+          <cell r="GX109">
+            <v>6.666666666666667</v>
+          </cell>
+          <cell r="GY109">
+            <v>45</v>
+          </cell>
+          <cell r="GZ109">
+            <v>1.2931542022105342</v>
+          </cell>
+        </row>
+        <row r="110">
+          <cell r="GX110">
+            <v>6.666666666666667</v>
+          </cell>
+          <cell r="GY110">
+            <v>45</v>
+          </cell>
+          <cell r="GZ110">
+            <v>9.8463517934812256E-2</v>
+          </cell>
+        </row>
+        <row r="111">
+          <cell r="GX111">
+            <v>0</v>
+          </cell>
+          <cell r="GY111">
+            <v>0</v>
+          </cell>
+          <cell r="GZ111">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="113">
+          <cell r="GX113">
+            <v>13.333333333333334</v>
+          </cell>
+          <cell r="GY113">
+            <v>60</v>
+          </cell>
+          <cell r="GZ113">
+            <v>0.22804389041744338</v>
+          </cell>
+        </row>
+        <row r="114">
+          <cell r="GX114">
+            <v>13.333333333333334</v>
+          </cell>
+          <cell r="GY114">
+            <v>60</v>
+          </cell>
+          <cell r="GZ114">
+            <v>1.6939618018446652</v>
+          </cell>
+        </row>
+        <row r="115">
+          <cell r="GX115">
+            <v>13.333333333333334</v>
+          </cell>
+          <cell r="GY115">
+            <v>60</v>
+          </cell>
+          <cell r="GZ115">
+            <v>0.6227881553707405</v>
+          </cell>
+        </row>
+        <row r="117">
+          <cell r="GX117">
+            <v>13.333333333333334</v>
+          </cell>
+          <cell r="GY117">
+            <v>93.333333333333329</v>
+          </cell>
+          <cell r="GZ117">
+            <v>0.52508849320568507</v>
+          </cell>
+        </row>
+        <row r="118">
+          <cell r="GX118">
+            <v>6.666666666666667</v>
+          </cell>
+          <cell r="GY118">
+            <v>53.333333333333336</v>
+          </cell>
+          <cell r="GZ118">
+            <v>0.11558313492178705</v>
+          </cell>
+        </row>
+        <row r="119">
+          <cell r="GX119">
+            <v>6.666666666666667</v>
+          </cell>
+          <cell r="GY119">
+            <v>53.333333333333336</v>
+          </cell>
+          <cell r="GZ119">
+            <v>0.19726253726173842</v>
+          </cell>
+        </row>
+        <row r="121">
+          <cell r="GX121">
+            <v>13.333333333333334</v>
+          </cell>
+          <cell r="GY121">
+            <v>66.666666666666657</v>
+          </cell>
+          <cell r="GZ121">
+            <v>0.50281683734606675</v>
+          </cell>
+        </row>
+        <row r="122">
+          <cell r="GX122">
+            <v>6.25</v>
+          </cell>
+          <cell r="GY122">
+            <v>56.25</v>
+          </cell>
+          <cell r="GZ122">
+            <v>0.26515731656921487</v>
+          </cell>
+        </row>
+        <row r="123">
+          <cell r="GX123">
+            <v>0</v>
+          </cell>
+          <cell r="GY123">
+            <v>0.83333333333333337</v>
+          </cell>
+          <cell r="GZ123">
+            <v>3.1426052334129172E-3</v>
+          </cell>
+        </row>
+        <row r="124">
+          <cell r="GX124">
+            <v>0</v>
+          </cell>
+          <cell r="GY124">
+            <v>0</v>
+          </cell>
+          <cell r="GZ124">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="125">
+          <cell r="GX125">
+            <v>0</v>
+          </cell>
+          <cell r="GY125">
+            <v>0.83333333333333337</v>
+          </cell>
+          <cell r="GZ125">
+            <v>7.0708617751790628E-3</v>
+          </cell>
+        </row>
+        <row r="126">
+          <cell r="GX126">
+            <v>0</v>
+          </cell>
+          <cell r="GY126">
+            <v>0</v>
+          </cell>
+          <cell r="GZ126">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="127">
+          <cell r="GX127">
+            <v>0</v>
+          </cell>
+          <cell r="GY127">
+            <v>0</v>
+          </cell>
+          <cell r="GZ127">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="128">
+          <cell r="GX128">
+            <v>0</v>
+          </cell>
+          <cell r="GY128">
+            <v>0</v>
+          </cell>
+          <cell r="GZ128">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="129">
+          <cell r="GX129">
+            <v>0</v>
+          </cell>
+          <cell r="GY129">
+            <v>0</v>
+          </cell>
+          <cell r="GZ129">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="130">
+          <cell r="GX130">
+            <v>0</v>
+          </cell>
+          <cell r="GY130">
+            <v>0</v>
+          </cell>
+          <cell r="GZ130">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="131">
+          <cell r="GX131">
+            <v>0</v>
+          </cell>
+          <cell r="GY131">
+            <v>0</v>
+          </cell>
+          <cell r="GZ131">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="134">
+          <cell r="GX134">
+            <v>13.333333333333334</v>
+          </cell>
+          <cell r="GY134">
+            <v>86.666666666666671</v>
+          </cell>
+          <cell r="GZ134">
+            <v>1.3557441491789188</v>
+          </cell>
+        </row>
+        <row r="135">
+          <cell r="GX135">
+            <v>6.666666666666667</v>
+          </cell>
+          <cell r="GY135">
+            <v>45</v>
+          </cell>
+          <cell r="GZ135">
+            <v>0.9265653664055139</v>
+          </cell>
+        </row>
+        <row r="136">
+          <cell r="GX136">
+            <v>6.666666666666667</v>
+          </cell>
+          <cell r="GY136">
+            <v>45</v>
+          </cell>
+          <cell r="GZ136">
+            <v>5.0243323523825018E-2</v>
+          </cell>
+        </row>
+        <row r="137">
+          <cell r="GX137">
+            <v>13.333333333333334</v>
+          </cell>
+          <cell r="GY137">
+            <v>93.333333333333329</v>
+          </cell>
+          <cell r="GZ137">
+            <v>0.3168856106300767</v>
+          </cell>
+        </row>
+        <row r="139">
+          <cell r="GX139">
+            <v>0</v>
+          </cell>
+          <cell r="GY139">
+            <v>0</v>
+          </cell>
+          <cell r="GZ139">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="140">
+          <cell r="GX140">
+            <v>0</v>
+          </cell>
+          <cell r="GY140">
+            <v>0</v>
+          </cell>
+          <cell r="GZ140">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="141">
+          <cell r="GX141">
+            <v>0</v>
+          </cell>
+          <cell r="GY141">
+            <v>0</v>
+          </cell>
+          <cell r="GZ141">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="142">
+          <cell r="GX142">
+            <v>0</v>
+          </cell>
+          <cell r="GY142">
+            <v>0</v>
+          </cell>
+          <cell r="GZ142">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="144">
+          <cell r="GX144">
+            <v>6.666666666666667</v>
+          </cell>
+          <cell r="GY144">
+            <v>45</v>
+          </cell>
+          <cell r="GZ144">
+            <v>0.29851684341712914</v>
+          </cell>
+        </row>
+        <row r="146">
+          <cell r="GX146">
+            <v>6.666666666666667</v>
+          </cell>
+          <cell r="GY146">
+            <v>45</v>
+          </cell>
+          <cell r="GZ146">
+            <v>6.9730540796739002E-2</v>
+          </cell>
+        </row>
+        <row r="148">
+          <cell r="GX148">
+            <v>12.5</v>
+          </cell>
+          <cell r="GY148">
+            <v>50</v>
+          </cell>
+          <cell r="GZ148">
+            <v>0.11677016762706485</v>
+          </cell>
+        </row>
+        <row r="150">
+          <cell r="GX150">
+            <v>0</v>
+          </cell>
+          <cell r="GY150">
+            <v>0</v>
+          </cell>
+          <cell r="GZ150">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="151">
+          <cell r="GX151">
+            <v>0</v>
+          </cell>
+          <cell r="GY151">
+            <v>0</v>
+          </cell>
+          <cell r="GZ151">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="154">
+          <cell r="GX154">
+            <v>0</v>
+          </cell>
+          <cell r="GY154">
+            <v>100</v>
+          </cell>
+          <cell r="GZ154">
+            <v>0.44678418603431441</v>
+          </cell>
+        </row>
+        <row r="155">
+          <cell r="GX155">
+            <v>0</v>
+          </cell>
+          <cell r="GY155">
+            <v>100</v>
+          </cell>
+          <cell r="GZ155">
+            <v>1.1397286400018627</v>
+          </cell>
+        </row>
+        <row r="156">
+          <cell r="GX156">
+            <v>0</v>
+          </cell>
+          <cell r="GY156">
+            <v>0</v>
+          </cell>
+          <cell r="GZ156">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="157">
+          <cell r="GX157">
+            <v>13.333333333333334</v>
+          </cell>
+          <cell r="GY157">
+            <v>60</v>
+          </cell>
+          <cell r="GZ157">
+            <v>0.68874719041780186</v>
+          </cell>
+        </row>
+        <row r="158">
+          <cell r="GX158">
+            <v>0</v>
+          </cell>
+          <cell r="GY158">
+            <v>0</v>
+          </cell>
+          <cell r="GZ158">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="159">
+          <cell r="GX159">
+            <v>0</v>
+          </cell>
+          <cell r="GY159">
+            <v>100</v>
+          </cell>
+          <cell r="GZ159">
+            <v>0.53614102324117729</v>
+          </cell>
+        </row>
+        <row r="160">
+          <cell r="GX160">
+            <v>6.666666666666667</v>
+          </cell>
+          <cell r="GY160">
+            <v>8.3333333333333321</v>
+          </cell>
+          <cell r="GZ160">
+            <v>3.8673921349080216E-2</v>
+          </cell>
+        </row>
+        <row r="161">
+          <cell r="GX161">
+            <v>0</v>
+          </cell>
+          <cell r="GY161">
+            <v>0</v>
+          </cell>
+          <cell r="GZ161">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="162">
+          <cell r="GX162">
+            <v>0</v>
+          </cell>
+          <cell r="GY162">
+            <v>0</v>
+          </cell>
+          <cell r="GZ162">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="163">
+          <cell r="GX163">
+            <v>0</v>
+          </cell>
+          <cell r="GY163">
+            <v>0</v>
+          </cell>
+          <cell r="GZ163">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="164">
+          <cell r="GX164">
+            <v>0</v>
+          </cell>
+          <cell r="GY164">
+            <v>0</v>
+          </cell>
+          <cell r="GZ164">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="165">
+          <cell r="GX165">
+            <v>0</v>
+          </cell>
+          <cell r="GY165">
+            <v>0</v>
+          </cell>
+          <cell r="GZ165">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="166">
+          <cell r="GX166">
+            <v>0</v>
+          </cell>
+          <cell r="GY166">
+            <v>0</v>
+          </cell>
+          <cell r="GZ166">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="167">
+          <cell r="GX167">
+            <v>0</v>
+          </cell>
+          <cell r="GY167">
+            <v>0</v>
+          </cell>
+          <cell r="GZ167">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="168">
+          <cell r="GX168">
+            <v>0</v>
+          </cell>
+          <cell r="GY168">
+            <v>0</v>
+          </cell>
+          <cell r="GZ168">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="169">
+          <cell r="GX169">
+            <v>0</v>
+          </cell>
+          <cell r="GY169">
+            <v>0</v>
+          </cell>
+          <cell r="GZ169">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="171">
+          <cell r="GX171">
+            <v>0</v>
+          </cell>
+          <cell r="GY171">
+            <v>0</v>
+          </cell>
+          <cell r="GZ171">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="172">
+          <cell r="GX172">
+            <v>0</v>
+          </cell>
+          <cell r="GY172">
+            <v>0</v>
+          </cell>
+          <cell r="GZ172">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="173">
+          <cell r="GX173">
+            <v>0</v>
+          </cell>
+          <cell r="GY173">
+            <v>13.333333333333334</v>
+          </cell>
+          <cell r="GZ173">
+            <v>0.19121527229276569</v>
+          </cell>
+        </row>
+        <row r="174">
+          <cell r="GX174">
+            <v>20</v>
+          </cell>
+          <cell r="GY174">
+            <v>93.333333333333329</v>
+          </cell>
+          <cell r="GZ174">
+            <v>1.9941181526255327</v>
+          </cell>
+        </row>
+        <row r="175">
+          <cell r="GX175">
+            <v>0</v>
+          </cell>
+          <cell r="GY175">
+            <v>0</v>
+          </cell>
+          <cell r="GZ175">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="176">
+          <cell r="GX176">
+            <v>0</v>
+          </cell>
+          <cell r="GY176">
+            <v>0</v>
+          </cell>
+          <cell r="GZ176">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="178">
+          <cell r="GX178">
+            <v>0</v>
+          </cell>
+          <cell r="GY178">
+            <v>100</v>
+          </cell>
+          <cell r="GZ178">
+            <v>0.13083451238006327</v>
+          </cell>
+        </row>
+        <row r="179">
+          <cell r="GX179">
+            <v>0</v>
+          </cell>
+          <cell r="GY179">
+            <v>0</v>
+          </cell>
+          <cell r="GZ179">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="180">
+          <cell r="GX180">
+            <v>0</v>
+          </cell>
+          <cell r="GY180">
+            <v>0</v>
+          </cell>
+          <cell r="GZ180">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="181">
+          <cell r="GX181">
+            <v>0</v>
+          </cell>
+          <cell r="GY181">
+            <v>100</v>
+          </cell>
+          <cell r="GZ181">
+            <v>0.14518671191592922</v>
+          </cell>
+        </row>
+        <row r="183">
+          <cell r="GX183">
+            <v>0</v>
+          </cell>
+          <cell r="GY183">
+            <v>100</v>
+          </cell>
+          <cell r="GZ183">
+            <v>0.31089306470342809</v>
+          </cell>
+        </row>
+        <row r="184">
+          <cell r="GX184">
+            <v>0</v>
+          </cell>
+          <cell r="GY184">
+            <v>100</v>
+          </cell>
+          <cell r="GZ184">
+            <v>0.29814760065827534</v>
+          </cell>
+        </row>
+        <row r="185">
+          <cell r="GX185">
+            <v>0</v>
+          </cell>
+          <cell r="GY185">
+            <v>100</v>
+          </cell>
+          <cell r="GZ185">
+            <v>7.0614339594788259E-2</v>
+          </cell>
+        </row>
+        <row r="186">
+          <cell r="GX186">
+            <v>0</v>
+          </cell>
+          <cell r="GY186">
+            <v>0</v>
+          </cell>
+          <cell r="GZ186">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="187">
+          <cell r="GX187">
+            <v>0</v>
+          </cell>
+          <cell r="GY187">
+            <v>0</v>
+          </cell>
+          <cell r="GZ187">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="188">
+          <cell r="GX188">
+            <v>0</v>
+          </cell>
+          <cell r="GY188">
+            <v>0</v>
+          </cell>
+          <cell r="GZ188">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="189">
+          <cell r="GX189">
+            <v>0</v>
+          </cell>
+          <cell r="GY189">
+            <v>0</v>
+          </cell>
+          <cell r="GZ189">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="191">
+          <cell r="GX191">
+            <v>0</v>
+          </cell>
+          <cell r="GY191">
+            <v>100</v>
+          </cell>
+          <cell r="GZ191">
+            <v>0.62503589747872845</v>
+          </cell>
+        </row>
+        <row r="192">
+          <cell r="GX192">
+            <v>20</v>
+          </cell>
+          <cell r="GY192">
+            <v>100</v>
+          </cell>
+          <cell r="GZ192">
+            <v>1.2740938693616655</v>
+          </cell>
+        </row>
+        <row r="193">
+          <cell r="GX193">
+            <v>0</v>
+          </cell>
+          <cell r="GY193">
+            <v>0</v>
+          </cell>
+          <cell r="GZ193">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="194">
+          <cell r="GX194">
+            <v>0</v>
+          </cell>
+          <cell r="GY194">
+            <v>100</v>
+          </cell>
+          <cell r="GZ194">
+            <v>0.6533853392893465</v>
+          </cell>
+        </row>
+        <row r="195">
+          <cell r="GX195">
+            <v>0</v>
+          </cell>
+          <cell r="GY195">
+            <v>0</v>
+          </cell>
+          <cell r="GZ195">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="196">
+          <cell r="GX196">
+            <v>0</v>
+          </cell>
+          <cell r="GY196">
+            <v>0</v>
+          </cell>
+          <cell r="GZ196">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="198">
+          <cell r="GX198">
+            <v>0</v>
+          </cell>
+          <cell r="GY198">
+            <v>53.846153846153847</v>
+          </cell>
+          <cell r="GZ198">
+            <v>1.5483374246161334</v>
+          </cell>
+        </row>
+        <row r="199">
+          <cell r="GX199">
+            <v>0</v>
+          </cell>
+          <cell r="GY199">
+            <v>0</v>
+          </cell>
+          <cell r="GZ199">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="200">
+          <cell r="GX200">
+            <v>0</v>
+          </cell>
+          <cell r="GY200">
+            <v>0</v>
+          </cell>
+          <cell r="GZ200">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="202">
+          <cell r="GX202">
+            <v>0</v>
+          </cell>
+          <cell r="GY202">
+            <v>0.83333333333333337</v>
+          </cell>
+          <cell r="GZ202">
+            <v>7.2754233776376092E-3</v>
+          </cell>
+        </row>
+        <row r="203">
+          <cell r="GX203">
+            <v>0</v>
+          </cell>
+          <cell r="GY203">
+            <v>0.83333333333333337</v>
+          </cell>
+          <cell r="GZ203">
+            <v>3.0895737700990743E-3</v>
+          </cell>
+        </row>
+        <row r="204">
+          <cell r="GX204">
+            <v>0</v>
+          </cell>
+          <cell r="GY204">
+            <v>0.83333333333333337</v>
+          </cell>
+          <cell r="GZ204">
+            <v>2.1151697349139822E-3</v>
+          </cell>
+        </row>
+        <row r="205">
+          <cell r="GX205">
+            <v>0</v>
+          </cell>
+          <cell r="GY205">
+            <v>0.83333333333333337</v>
+          </cell>
+          <cell r="GZ205">
+            <v>4.2971567566494799E-3</v>
+          </cell>
+        </row>
+        <row r="206">
+          <cell r="GX206">
+            <v>0</v>
+          </cell>
+          <cell r="GY206">
+            <v>0.83333333333333337</v>
+          </cell>
+          <cell r="GZ206">
+            <v>2.0607633818105204E-3</v>
+          </cell>
+        </row>
+        <row r="207">
+          <cell r="GX207">
+            <v>0</v>
+          </cell>
+          <cell r="GY207">
+            <v>0.83333333333333337</v>
+          </cell>
+          <cell r="GZ207">
+            <v>1.605478448619824E-3</v>
+          </cell>
+        </row>
+        <row r="208">
+          <cell r="GX208">
+            <v>0</v>
+          </cell>
+          <cell r="GY208">
+            <v>0.83333333333333337</v>
+          </cell>
+          <cell r="GZ208">
+            <v>2.6682682559946553E-3</v>
+          </cell>
+        </row>
+        <row r="209">
+          <cell r="GX209">
+            <v>0</v>
+          </cell>
+          <cell r="GY209">
+            <v>0</v>
+          </cell>
+          <cell r="GZ209">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="211">
+          <cell r="GX211">
+            <v>0</v>
+          </cell>
+          <cell r="GY211">
+            <v>100</v>
+          </cell>
+          <cell r="GZ211">
+            <v>7.2704109222903171E-2</v>
+          </cell>
+        </row>
+        <row r="212">
+          <cell r="GX212">
+            <v>0</v>
+          </cell>
+          <cell r="GY212">
+            <v>53.333333333333336</v>
+          </cell>
+          <cell r="GZ212">
+            <v>2.1430958677996589E-2</v>
+          </cell>
+        </row>
+        <row r="213">
+          <cell r="GX213">
+            <v>0</v>
+          </cell>
+          <cell r="GY213">
+            <v>53.333333333333336</v>
+          </cell>
+          <cell r="GZ213">
+            <v>0.1868060588756571</v>
+          </cell>
+        </row>
+        <row r="215">
+          <cell r="GX215">
+            <v>0</v>
+          </cell>
+          <cell r="GY215">
+            <v>0</v>
+          </cell>
+          <cell r="GZ215">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="216">
+          <cell r="GX216">
+            <v>0</v>
+          </cell>
+          <cell r="GY216">
+            <v>0</v>
+          </cell>
+          <cell r="GZ216">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="217">
+          <cell r="GX217">
+            <v>0</v>
+          </cell>
+          <cell r="GY217">
+            <v>0</v>
+          </cell>
+          <cell r="GZ217">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="218">
+          <cell r="GX218">
+            <v>0</v>
+          </cell>
+          <cell r="GY218">
+            <v>0</v>
+          </cell>
+          <cell r="GZ218">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="220">
+          <cell r="GX220">
+            <v>0</v>
+          </cell>
+          <cell r="GY220">
+            <v>0.83333333333333337</v>
+          </cell>
+          <cell r="GZ220">
+            <v>6.6701517172974715E-3</v>
+          </cell>
+        </row>
+        <row r="221">
+          <cell r="GX221">
+            <v>0</v>
+          </cell>
+          <cell r="GY221">
+            <v>0</v>
+          </cell>
+          <cell r="GZ221">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="222">
+          <cell r="GX222">
+            <v>3.128608157696243</v>
+          </cell>
+          <cell r="GZ222">
+            <v>61.069846671647859</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
@@ -2085,7 +3965,7 @@
       </c>
       <c r="I2" s="36">
         <f>AVERAGE(I3:I12)</f>
-        <v>69.117647058823522</v>
+        <v>71.176470588235304</v>
       </c>
       <c r="J2">
         <f>0.637484224224017*100</f>
@@ -2120,12 +4000,15 @@
         <v>182862.18</v>
       </c>
       <c r="H3" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX16</f>
         <v>0</v>
       </c>
       <c r="I3" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY16</f>
         <v>100</v>
       </c>
       <c r="J3" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ16</f>
         <v>0.71832955482661864</v>
       </c>
       <c r="K3" s="37">
@@ -2161,12 +4044,15 @@
         <v>155700.62400000001</v>
       </c>
       <c r="H4" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX17</f>
         <v>0</v>
       </c>
       <c r="I4" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY17</f>
         <v>100</v>
       </c>
       <c r="J4" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ17</f>
         <v>0.61163199478507113</v>
       </c>
       <c r="K4" s="37">
@@ -2202,12 +4088,15 @@
         <v>4776</v>
       </c>
       <c r="H5" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX18</f>
         <v>0</v>
       </c>
       <c r="I5" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY18</f>
         <v>100</v>
       </c>
       <c r="J5" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ18</f>
         <v>1.8761353243475117E-2</v>
       </c>
       <c r="K5" s="37">
@@ -2243,13 +4132,16 @@
         <v>267119.96639999998</v>
       </c>
       <c r="H6" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX19</f>
         <v>2.9411764705882351</v>
       </c>
       <c r="I6" s="36">
-        <v>55.882352941176471</v>
+        <f>[1]PLS_MODELO_LIVRE!GY19</f>
+        <v>58.82352941176471</v>
       </c>
       <c r="J6" s="36">
-        <v>0.58638233392635042</v>
+        <f>[1]PLS_MODELO_LIVRE!GZ19</f>
+        <v>0.61724456202773725</v>
       </c>
       <c r="K6" s="37">
         <f>G6*(H6/100)</f>
@@ -2284,13 +4176,16 @@
         <v>211679.78399999999</v>
       </c>
       <c r="H7" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX20</f>
         <v>2.9411764705882351</v>
       </c>
       <c r="I7" s="36">
-        <v>55.882352941176471</v>
+        <f>[1]PLS_MODELO_LIVRE!GY20</f>
+        <v>58.82352941176471</v>
       </c>
       <c r="J7" s="36">
-        <v>0.46467992437927208</v>
+        <f>[1]PLS_MODELO_LIVRE!GZ20</f>
+        <v>0.48913676250449695</v>
       </c>
       <c r="K7" s="37">
         <f t="shared" ref="K7:K12" si="3">G7*(H7/100)</f>
@@ -2325,13 +4220,16 @@
         <v>43343.88</v>
       </c>
       <c r="H8" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX21</f>
         <v>2.9411764705882351</v>
       </c>
       <c r="I8" s="36">
-        <v>55.882352941176471</v>
+        <f>[1]PLS_MODELO_LIVRE!GY21</f>
+        <v>58.82352941176471</v>
       </c>
       <c r="J8" s="36">
-        <v>9.5148580086912071E-2</v>
+        <f>[1]PLS_MODELO_LIVRE!GZ21</f>
+        <v>0.10015640009148638</v>
       </c>
       <c r="K8" s="37">
         <f t="shared" si="3"/>
@@ -2366,13 +4264,16 @@
         <v>19655.807999999997</v>
       </c>
       <c r="H9" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX22</f>
         <v>2.9411764705882351</v>
       </c>
       <c r="I9" s="36">
-        <v>55.882352941176471</v>
+        <f>[1]PLS_MODELO_LIVRE!GY22</f>
+        <v>58.82352941176471</v>
       </c>
       <c r="J9" s="36">
-        <v>4.3148472671596702E-2</v>
+        <f>[1]PLS_MODELO_LIVRE!GZ22</f>
+        <v>4.5419444917470214E-2</v>
       </c>
       <c r="K9" s="37">
         <f t="shared" si="3"/>
@@ -2407,13 +4308,16 @@
         <v>16127.832</v>
       </c>
       <c r="H10" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX23</f>
         <v>2.9411764705882351</v>
       </c>
       <c r="I10" s="36">
-        <v>55.882352941176471</v>
+        <f>[1]PLS_MODELO_LIVRE!GY23</f>
+        <v>58.82352941176471</v>
       </c>
       <c r="J10" s="36">
-        <v>3.540385204740007E-2</v>
+        <f>[1]PLS_MODELO_LIVRE!GZ23</f>
+        <v>3.726721268147376E-2</v>
       </c>
       <c r="K10" s="37">
         <f t="shared" si="3"/>
@@ -2448,13 +4352,16 @@
         <v>10336.68</v>
       </c>
       <c r="H11" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX24</f>
         <v>2.9411764705882351</v>
       </c>
       <c r="I11" s="36">
-        <v>55.882352941176471</v>
+        <f>[1]PLS_MODELO_LIVRE!GY24</f>
+        <v>58.82352941176471</v>
       </c>
       <c r="J11" s="36">
-        <v>2.2691102522727134E-2</v>
+        <f>[1]PLS_MODELO_LIVRE!GZ24</f>
+        <v>2.3885371076554876E-2</v>
       </c>
       <c r="K11" s="37">
         <f>G11*(H11/100)</f>
@@ -2489,13 +4396,16 @@
         <v>1014047.6880000001</v>
       </c>
       <c r="H12" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX25</f>
         <v>2.9411764705882351</v>
       </c>
       <c r="I12" s="36">
-        <v>55.882352941176471</v>
+        <f>[1]PLS_MODELO_LIVRE!GY25</f>
+        <v>58.82352941176471</v>
       </c>
       <c r="J12" s="36">
-        <v>2.2260397004978794</v>
+        <f>[1]PLS_MODELO_LIVRE!GZ25</f>
+        <v>2.3431996847346097</v>
       </c>
       <c r="K12" s="37">
         <f t="shared" si="3"/>
@@ -2585,12 +4495,15 @@
         <v>63895.199999999997</v>
       </c>
       <c r="H15" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX28</f>
         <v>0</v>
       </c>
       <c r="I15" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY28</f>
         <v>100</v>
       </c>
       <c r="J15" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ28</f>
         <v>0.25099673738745631</v>
       </c>
       <c r="K15" s="37">
@@ -2626,12 +4539,15 @@
         <v>42964.799999999996</v>
       </c>
       <c r="H16" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX29</f>
         <v>0</v>
       </c>
       <c r="I16" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY29</f>
         <v>100</v>
       </c>
       <c r="J16" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ29</f>
         <v>0.16877675666567413</v>
       </c>
       <c r="K16" s="37">
@@ -2667,12 +4583,15 @@
         <v>3015.4079999999999</v>
       </c>
       <c r="H17" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX30</f>
         <v>0</v>
       </c>
       <c r="I17" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY30</f>
         <v>100</v>
       </c>
       <c r="J17" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ30</f>
         <v>1.1845296202093973E-2</v>
       </c>
       <c r="K17" s="37">
@@ -2708,12 +4627,15 @@
         <v>157651.71599999999</v>
       </c>
       <c r="H18" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX31</f>
         <v>0</v>
       </c>
       <c r="I18" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY31</f>
         <v>100</v>
       </c>
       <c r="J18" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ31</f>
         <v>0.61929638469765858</v>
       </c>
       <c r="K18" s="37">
@@ -2749,12 +4671,15 @@
         <v>7800</v>
       </c>
       <c r="H19" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX32</f>
         <v>0</v>
       </c>
       <c r="I19" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY32</f>
         <v>100</v>
       </c>
       <c r="J19" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ32</f>
         <v>3.0640401025775945E-2</v>
       </c>
       <c r="K19" s="37">
@@ -2790,12 +4715,15 @@
         <v>27873.167999999998</v>
       </c>
       <c r="H20" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX33</f>
         <v>0</v>
       </c>
       <c r="I20" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY33</f>
         <v>100</v>
       </c>
       <c r="J20" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ33</f>
         <v>0.10949295453574681</v>
       </c>
       <c r="K20" s="37">
@@ -2856,12 +4784,15 @@
         <v>45724.799999999996</v>
       </c>
       <c r="H22" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX35</f>
         <v>0</v>
       </c>
       <c r="I22" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY35</f>
         <v>100</v>
       </c>
       <c r="J22" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ35</f>
         <v>0.17961874472094869</v>
       </c>
       <c r="K22" s="37">
@@ -2897,12 +4828,15 @@
         <v>14556</v>
       </c>
       <c r="H23" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX36</f>
         <v>0</v>
       </c>
       <c r="I23" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY36</f>
         <v>100</v>
       </c>
       <c r="J23" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ36</f>
         <v>5.7179702221948035E-2</v>
       </c>
       <c r="K23" s="37">
@@ -2938,12 +4872,15 @@
         <v>1188775.2</v>
       </c>
       <c r="H24" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX37</f>
         <v>0</v>
       </c>
       <c r="I24" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY37</f>
         <v>100</v>
       </c>
       <c r="J24" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ37</f>
         <v>4.6698139560893592</v>
       </c>
       <c r="K24" s="37">
@@ -3004,12 +4941,15 @@
         <v>386828.35200000001</v>
       </c>
       <c r="H26" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX39</f>
         <v>0</v>
       </c>
       <c r="I26" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY39</f>
         <v>100</v>
       </c>
       <c r="J26" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ39</f>
         <v>1.5195610042846177</v>
       </c>
       <c r="K26" s="37">
@@ -3078,12 +5018,15 @@
         <v>331857.59999999998</v>
       </c>
       <c r="H28" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX41</f>
         <v>0</v>
       </c>
       <c r="I28" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY41</f>
         <v>100</v>
       </c>
       <c r="J28" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ41</f>
         <v>1.3036217881348131</v>
       </c>
       <c r="K28" s="37">
@@ -3119,12 +5062,15 @@
         <v>379586.76</v>
       </c>
       <c r="H29" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX42</f>
         <v>0</v>
       </c>
       <c r="I29" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY42</f>
         <v>100</v>
       </c>
       <c r="J29" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ42</f>
         <v>1.4911141731378164</v>
       </c>
       <c r="K29" s="37">
@@ -3160,12 +5106,15 @@
         <v>371186.76</v>
       </c>
       <c r="H30" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX43</f>
         <v>0</v>
       </c>
       <c r="I30" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY43</f>
         <v>100</v>
       </c>
       <c r="J30" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ43</f>
         <v>1.4581168181869806</v>
       </c>
       <c r="K30" s="37">
@@ -3201,12 +5150,15 @@
         <v>86400</v>
       </c>
       <c r="H31" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX44</f>
         <v>0</v>
       </c>
       <c r="I31" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY44</f>
         <v>100</v>
       </c>
       <c r="J31" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ44</f>
         <v>0.3394013652085951</v>
       </c>
       <c r="K31" s="37">
@@ -3242,12 +5194,15 @@
         <v>9600</v>
       </c>
       <c r="H32" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX45</f>
         <v>0</v>
       </c>
       <c r="I32" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY45</f>
         <v>100</v>
       </c>
       <c r="J32" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ45</f>
         <v>3.7711262800955013E-2</v>
       </c>
       <c r="K32" s="37">
@@ -3283,12 +5238,15 @@
         <v>45600</v>
       </c>
       <c r="H33" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX46</f>
         <v>0</v>
       </c>
       <c r="I33" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY46</f>
         <v>100</v>
       </c>
       <c r="J33" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ46</f>
         <v>0.17912849830453628</v>
       </c>
       <c r="K33" s="37">
@@ -3324,12 +5282,15 @@
         <v>36000</v>
       </c>
       <c r="H34" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX47</f>
         <v>0</v>
       </c>
       <c r="I34" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY47</f>
         <v>100</v>
       </c>
       <c r="J34" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ47</f>
         <v>0.14141723550358129</v>
       </c>
       <c r="K34" s="37">
@@ -3365,12 +5326,15 @@
         <v>45600</v>
       </c>
       <c r="H35" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX48</f>
         <v>0</v>
       </c>
       <c r="I35" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY48</f>
         <v>100</v>
       </c>
       <c r="J35" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ48</f>
         <v>0.17912849830453628</v>
       </c>
       <c r="K35" s="37">
@@ -3406,12 +5370,15 @@
         <v>57600</v>
       </c>
       <c r="H36" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX49</f>
         <v>0</v>
       </c>
       <c r="I36" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY49</f>
         <v>100</v>
       </c>
       <c r="J36" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ49</f>
         <v>0.22626757680573006</v>
       </c>
       <c r="K36" s="37">
@@ -3447,12 +5414,15 @@
         <v>90000</v>
       </c>
       <c r="H37" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX50</f>
         <v>0</v>
       </c>
       <c r="I37" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY50</f>
         <v>100</v>
       </c>
       <c r="J37" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ50</f>
         <v>0.35354308875895318</v>
       </c>
       <c r="K37" s="37">
@@ -3488,12 +5458,15 @@
         <v>115200</v>
       </c>
       <c r="H38" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX51</f>
         <v>0</v>
       </c>
       <c r="I38" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY51</f>
         <v>100</v>
       </c>
       <c r="J38" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ51</f>
         <v>0.45253515361146013</v>
       </c>
       <c r="K38" s="37">
@@ -3529,12 +5502,15 @@
         <v>114000</v>
       </c>
       <c r="H39" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX52</f>
         <v>0</v>
       </c>
       <c r="I39" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY52</f>
         <v>100</v>
       </c>
       <c r="J39" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ52</f>
         <v>0.44782124576134069</v>
       </c>
       <c r="K39" s="37">
@@ -3570,12 +5546,15 @@
         <v>235200</v>
       </c>
       <c r="H40" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX53</f>
         <v>0</v>
       </c>
       <c r="I40" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY53</f>
         <v>100</v>
       </c>
       <c r="J40" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ53</f>
         <v>0.92392593862339767</v>
       </c>
       <c r="K40" s="37">
@@ -3611,12 +5590,15 @@
         <v>1588800</v>
       </c>
       <c r="H41" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX54</f>
         <v>0</v>
       </c>
       <c r="I41" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY54</f>
         <v>100</v>
       </c>
       <c r="J41" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ54</f>
         <v>6.2412139935580537</v>
       </c>
       <c r="K41" s="37">
@@ -3652,12 +5634,15 @@
         <v>8664.7559999999994</v>
       </c>
       <c r="H42" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX55</f>
         <v>0</v>
       </c>
       <c r="I42" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY55</f>
         <v>100</v>
       </c>
       <c r="J42" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ55</f>
         <v>3.4037384439807465E-2</v>
       </c>
       <c r="K42" s="37">
@@ -3693,12 +5678,15 @@
         <v>1986481.5599999998</v>
       </c>
       <c r="H43" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX56</f>
         <v>0</v>
       </c>
       <c r="I43" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY56</f>
         <v>100</v>
       </c>
       <c r="J43" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ56</f>
         <v>7.8034091831678198</v>
       </c>
       <c r="K43" s="37">
@@ -3734,12 +5722,15 @@
         <v>206502.05999999997</v>
       </c>
       <c r="H44" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX57</f>
         <v>0</v>
       </c>
       <c r="I44" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY57</f>
         <v>100</v>
       </c>
       <c r="J44" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ57</f>
         <v>0.81119306808318525</v>
       </c>
       <c r="K44" s="37">
@@ -3770,11 +5761,11 @@
       <c r="G45" s="1"/>
       <c r="H45" s="36">
         <f>SUM(L46:L72)</f>
-        <v>0</v>
+        <v>0.41038268370799202</v>
       </c>
       <c r="I45" s="36">
         <f>AVERAGE(I46:I72)</f>
-        <v>14.722222222222214</v>
+        <v>15.555555555555548</v>
       </c>
       <c r="J45" s="36">
         <f>0.109556413087872*100</f>
@@ -3782,7 +5773,7 @@
       </c>
       <c r="K45" s="39">
         <f t="shared" ref="K45" si="9">SUM(K46:K72)</f>
-        <v>0</v>
+        <v>104469.42029999998</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
@@ -3828,12 +5819,15 @@
         <v>39693.803999999996</v>
       </c>
       <c r="H47" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX60</f>
         <v>0</v>
       </c>
       <c r="I47" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY60</f>
         <v>100</v>
       </c>
       <c r="J47" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ60</f>
         <v>0.15592744523058322</v>
       </c>
       <c r="K47" s="37">
@@ -3869,12 +5863,15 @@
         <v>46096.583999999995</v>
       </c>
       <c r="H48" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX61</f>
         <v>0</v>
       </c>
       <c r="I48" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY61</f>
         <v>100</v>
       </c>
       <c r="J48" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ61</f>
         <v>0.18107920765107266</v>
       </c>
       <c r="K48" s="37">
@@ -3910,12 +5907,15 @@
         <v>80624.915999999983</v>
       </c>
       <c r="H49" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX62</f>
         <v>0</v>
       </c>
       <c r="I49" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY62</f>
         <v>0</v>
       </c>
       <c r="J49" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ62</f>
         <v>0</v>
       </c>
       <c r="K49" s="37">
@@ -3970,21 +5970,24 @@
         <v>596968.11599999992</v>
       </c>
       <c r="H51" s="36">
-        <v>0</v>
+        <f>[1]PLS_MODELO_LIVRE!GX64</f>
+        <v>17.5</v>
       </c>
       <c r="I51" s="36">
-        <v>0.83333333333333337</v>
+        <f>[1]PLS_MODELO_LIVRE!GY64</f>
+        <v>18.333333333333332</v>
       </c>
       <c r="J51" s="36">
-        <v>1.9542032557523428E-2</v>
+        <f>[1]PLS_MODELO_LIVRE!GZ64</f>
+        <v>0.42992471626551543</v>
       </c>
       <c r="K51" s="37">
         <f t="shared" ref="K51:K52" si="12">G51*(H51/100)</f>
-        <v>0</v>
+        <v>104469.42029999998</v>
       </c>
       <c r="L51">
         <f t="shared" ref="L51:L52" si="13">H51*D51/100</f>
-        <v>0</v>
+        <v>0.41038268370799202</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
@@ -4011,12 +6014,15 @@
         <v>43829.423999999992</v>
       </c>
       <c r="H52" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX65</f>
         <v>0</v>
       </c>
       <c r="I52" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY65</f>
         <v>0</v>
       </c>
       <c r="J52" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ65</f>
         <v>0</v>
       </c>
       <c r="K52" s="37">
@@ -4071,12 +6077,15 @@
         <v>129173.66399999998</v>
       </c>
       <c r="H54" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX67</f>
         <v>0</v>
       </c>
       <c r="I54" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY67</f>
         <v>100</v>
       </c>
       <c r="J54" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ67</f>
         <v>0.50742729063190206</v>
       </c>
       <c r="K54" s="37">
@@ -4112,12 +6121,15 @@
         <v>96141.09599999999</v>
       </c>
       <c r="H55" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX68</f>
         <v>0</v>
       </c>
       <c r="I55" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY68</f>
         <v>0</v>
       </c>
       <c r="J55" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ68</f>
         <v>0</v>
       </c>
       <c r="K55" s="37">
@@ -4153,12 +6165,15 @@
         <v>56969.4</v>
       </c>
       <c r="H56" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX69</f>
         <v>0</v>
       </c>
       <c r="I56" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY69</f>
         <v>0</v>
       </c>
       <c r="J56" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ69</f>
         <v>0</v>
       </c>
       <c r="K56" s="37">
@@ -4194,12 +6209,15 @@
         <v>2537.2800000000002</v>
       </c>
       <c r="H57" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX70</f>
         <v>0</v>
       </c>
       <c r="I57" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY70</f>
         <v>0</v>
       </c>
       <c r="J57" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ70</f>
         <v>0</v>
       </c>
       <c r="K57" s="37">
@@ -4235,12 +6253,15 @@
         <v>539.59199999999998</v>
       </c>
       <c r="H58" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX71</f>
         <v>0</v>
       </c>
       <c r="I58" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY71</f>
         <v>0</v>
       </c>
       <c r="J58" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ71</f>
         <v>0</v>
       </c>
       <c r="K58" s="37">
@@ -4295,12 +6316,15 @@
         <v>117936</v>
       </c>
       <c r="H60" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX73</f>
         <v>0</v>
       </c>
       <c r="I60" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY73</f>
         <v>0.83333333333333337</v>
       </c>
       <c r="J60" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ73</f>
         <v>3.8606905292477688E-3</v>
       </c>
       <c r="K60" s="37">
@@ -4336,12 +6360,15 @@
         <v>220704</v>
       </c>
       <c r="H61" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX74</f>
         <v>0</v>
       </c>
       <c r="I61" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY74</f>
         <v>0.83333333333333337</v>
       </c>
       <c r="J61" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ74</f>
         <v>7.2248494316162959E-3</v>
       </c>
       <c r="K61" s="37">
@@ -4377,12 +6404,15 @@
         <v>219792</v>
       </c>
       <c r="H62" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX75</f>
         <v>0</v>
       </c>
       <c r="I62" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY75</f>
         <v>0.83333333333333337</v>
       </c>
       <c r="J62" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ75</f>
         <v>7.194994681898873E-3</v>
       </c>
       <c r="K62" s="37">
@@ -4418,12 +6448,15 @@
         <v>87696</v>
       </c>
       <c r="H63" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX76</f>
         <v>0</v>
       </c>
       <c r="I63" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY76</f>
         <v>0.83333333333333337</v>
       </c>
       <c r="J63" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ76</f>
         <v>2.8707698807226996E-3</v>
       </c>
       <c r="K63" s="37">
@@ -4459,12 +6492,15 @@
         <v>69426</v>
       </c>
       <c r="H64" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX77</f>
         <v>0</v>
       </c>
       <c r="I64" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY77</f>
         <v>0.83333333333333337</v>
       </c>
       <c r="J64" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ77</f>
         <v>2.2726928222388042E-3</v>
       </c>
       <c r="K64" s="37">
@@ -4500,12 +6536,15 @@
         <v>2700.72</v>
       </c>
       <c r="H65" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX78</f>
         <v>0</v>
       </c>
       <c r="I65" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY78</f>
         <v>0</v>
       </c>
       <c r="J65" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ78</f>
         <v>0</v>
       </c>
       <c r="K65" s="37">
@@ -4560,12 +6599,15 @@
         <v>26688.311999999998</v>
       </c>
       <c r="H67" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX80</f>
         <v>0</v>
       </c>
       <c r="I67" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY80</f>
         <v>0.83333333333333337</v>
       </c>
       <c r="J67" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ80</f>
         <v>8.7365446835579953E-4</v>
       </c>
       <c r="K67" s="37">
@@ -4601,12 +6643,15 @@
         <v>63060.480000000003</v>
       </c>
       <c r="H68" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX81</f>
         <v>0</v>
       </c>
       <c r="I68" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY81</f>
         <v>0.83333333333333337</v>
       </c>
       <c r="J68" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ81</f>
         <v>2.0643145257242769E-3</v>
       </c>
       <c r="K68" s="37">
@@ -4642,12 +6687,15 @@
         <v>39967.451999999997</v>
       </c>
       <c r="H69" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX82</f>
         <v>0</v>
       </c>
       <c r="I69" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY82</f>
         <v>0.83333333333333337</v>
       </c>
       <c r="J69" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ82</f>
         <v>1.3083533731393705E-3</v>
       </c>
       <c r="K69" s="37">
@@ -4705,12 +6753,15 @@
         <v>97938.72</v>
       </c>
       <c r="H71" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX84</f>
         <v>0</v>
       </c>
       <c r="I71" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY84</f>
         <v>0.83333333333333337</v>
       </c>
       <c r="J71" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ84</f>
         <v>3.2060701461016912E-3</v>
       </c>
       <c r="K71" s="37">
@@ -4746,12 +6797,15 @@
         <v>44159.040000000001</v>
       </c>
       <c r="H72" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX85</f>
         <v>0</v>
       </c>
       <c r="I72" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY85</f>
         <v>0.83333333333333337</v>
       </c>
       <c r="J72" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ85</f>
         <v>1.445566981317608E-3</v>
       </c>
       <c r="K72" s="37">
@@ -4782,11 +6836,11 @@
       <c r="G73" s="1"/>
       <c r="H73" s="36">
         <f>SUM(L74:L88)</f>
-        <v>1.8824947002978463E-2</v>
+        <v>9.4124735014892314E-3</v>
       </c>
       <c r="I73" s="36">
         <f>AVERAGE(I74:I88)</f>
-        <v>41.987179487179482</v>
+        <v>42.5</v>
       </c>
       <c r="J73" s="36">
         <f>0.42784181832181*100</f>
@@ -4794,7 +6848,7 @@
       </c>
       <c r="K73" s="39">
         <f t="shared" ref="K73" si="23">SUM(K74:K88)</f>
-        <v>4792.1887999999999</v>
+        <v>2396.0944</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.3">
@@ -4837,12 +6891,15 @@
       </c>
       <c r="G75" s="1"/>
       <c r="H75" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX88</f>
         <v>0</v>
       </c>
       <c r="I75" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY88</f>
         <v>0</v>
       </c>
       <c r="J75" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ88</f>
         <v>0</v>
       </c>
       <c r="K75" s="37">
@@ -4875,12 +6932,15 @@
       </c>
       <c r="G76" s="1"/>
       <c r="H76" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX89</f>
         <v>0</v>
       </c>
       <c r="I76" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY89</f>
         <v>0</v>
       </c>
       <c r="J76" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ89</f>
         <v>0</v>
       </c>
       <c r="K76" s="37">
@@ -4913,12 +6973,15 @@
       </c>
       <c r="G77" s="1"/>
       <c r="H77" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX90</f>
         <v>0</v>
       </c>
       <c r="I77" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY90</f>
         <v>0</v>
       </c>
       <c r="J77" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ90</f>
         <v>0</v>
       </c>
       <c r="K77" s="37">
@@ -4973,12 +7036,15 @@
         <v>144269.44799999997</v>
       </c>
       <c r="H79" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX92</f>
         <v>0</v>
       </c>
       <c r="I79" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY92</f>
         <v>0</v>
       </c>
       <c r="J79" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ92</f>
         <v>0</v>
       </c>
       <c r="K79" s="37">
@@ -5014,12 +7080,15 @@
         <v>10440.575999999999</v>
       </c>
       <c r="H80" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX93</f>
         <v>0</v>
       </c>
       <c r="I80" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY93</f>
         <v>0</v>
       </c>
       <c r="J80" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ93</f>
         <v>0</v>
       </c>
       <c r="K80" s="37">
@@ -5055,12 +7124,15 @@
         <v>11471.111999999999</v>
       </c>
       <c r="H81" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX94</f>
         <v>0</v>
       </c>
       <c r="I81" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY94</f>
         <v>0</v>
       </c>
       <c r="J81" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ94</f>
         <v>0</v>
       </c>
       <c r="K81" s="37">
@@ -5096,12 +7168,15 @@
         <v>54623.267999999996</v>
       </c>
       <c r="H82" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX95</f>
         <v>0</v>
       </c>
       <c r="I82" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY95</f>
         <v>100</v>
       </c>
       <c r="J82" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ95</f>
         <v>0.21457420985364542</v>
       </c>
       <c r="K82" s="37">
@@ -5137,12 +7212,15 @@
         <v>4408.2479999999996</v>
       </c>
       <c r="H83" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX96</f>
         <v>0</v>
       </c>
       <c r="I83" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY96</f>
         <v>100</v>
       </c>
       <c r="J83" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ96</f>
         <v>1.7316729043727531E-2</v>
       </c>
       <c r="K83" s="37">
@@ -5178,21 +7256,24 @@
         <v>35941.415999999997</v>
       </c>
       <c r="H84" s="36">
-        <v>13.333333333333334</v>
+        <f>[1]PLS_MODELO_LIVRE!GX97</f>
+        <v>6.666666666666667</v>
       </c>
       <c r="I84" s="36">
-        <v>45.833333333333329</v>
+        <f>[1]PLS_MODELO_LIVRE!GY97</f>
+        <v>52.5</v>
       </c>
       <c r="J84" s="36">
-        <v>6.4710755322738456E-2</v>
+        <f>[1]PLS_MODELO_LIVRE!GZ97</f>
+        <v>7.4123228824227699E-2</v>
       </c>
       <c r="K84" s="37">
         <f t="shared" si="26"/>
-        <v>4792.1887999999999</v>
+        <v>2396.0944</v>
       </c>
       <c r="L84">
         <f t="shared" si="27"/>
-        <v>1.8824947002978463E-2</v>
+        <v>9.4124735014892314E-3</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.3">
@@ -5219,12 +7300,15 @@
         <v>1152.5519999999999</v>
       </c>
       <c r="H85" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX98</f>
         <v>0</v>
       </c>
       <c r="I85" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY98</f>
         <v>100</v>
       </c>
       <c r="J85" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ98</f>
         <v>4.5275199337256556E-3</v>
       </c>
       <c r="K85" s="37">
@@ -5260,12 +7344,15 @@
         <v>6756.36</v>
       </c>
       <c r="H86" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX99</f>
         <v>0</v>
       </c>
       <c r="I86" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY99</f>
         <v>0</v>
       </c>
       <c r="J86" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ99</f>
         <v>0</v>
       </c>
       <c r="K86" s="37">
@@ -5301,12 +7388,15 @@
         <v>35593.464</v>
       </c>
       <c r="H87" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX100</f>
         <v>0</v>
       </c>
       <c r="I87" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY100</f>
         <v>100</v>
       </c>
       <c r="J87" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ100</f>
         <v>0.13982025780211782</v>
       </c>
       <c r="K87" s="37">
@@ -5342,12 +7432,15 @@
         <v>31624.272000000001</v>
       </c>
       <c r="H88" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX101</f>
         <v>0</v>
       </c>
       <c r="I88" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY101</f>
         <v>100</v>
       </c>
       <c r="J88" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ101</f>
         <v>0.12422825336259198</v>
       </c>
       <c r="K88" s="37">
@@ -5378,11 +7471,11 @@
       <c r="G89" s="1"/>
       <c r="H89" s="36">
         <f>SUM(L90:L118)</f>
-        <v>2.0814555234259573</v>
+        <v>1.1775681493797878</v>
       </c>
       <c r="I89" s="36">
         <f>AVERAGE(I90:I118)</f>
-        <v>33.402777777777779</v>
+        <v>39.218750000000007</v>
       </c>
       <c r="J89" s="36">
         <f>0.423925829955751*100</f>
@@ -5390,7 +7483,7 @@
       </c>
       <c r="K89" s="39">
         <f>SUM(K90:K118)</f>
-        <v>529867.51279999991</v>
+        <v>299768.64719999995</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.3">
@@ -5436,12 +7529,15 @@
         <v>1049791.3559999999</v>
       </c>
       <c r="H91" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX104</f>
         <v>0</v>
       </c>
       <c r="I91" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY104</f>
         <v>100</v>
       </c>
       <c r="J91" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ104</f>
         <v>4.1238497616965537</v>
       </c>
       <c r="K91" s="37">
@@ -5477,21 +7573,24 @@
         <v>37817.796000000002</v>
       </c>
       <c r="H92" s="36">
-        <v>26.666666666666668</v>
+        <f>[1]PLS_MODELO_LIVRE!GX105</f>
+        <v>13.333333333333334</v>
       </c>
       <c r="I92" s="36">
-        <v>86.666666666666671</v>
+        <f>[1]PLS_MODELO_LIVRE!GY105</f>
+        <v>100</v>
       </c>
       <c r="J92" s="36">
-        <v>0.12875027059455396</v>
+        <f>[1]PLS_MODELO_LIVRE!GZ105</f>
+        <v>0.14855800453217763</v>
       </c>
       <c r="K92" s="37">
         <f t="shared" si="28"/>
-        <v>10084.7456</v>
+        <v>5042.3728000000001</v>
       </c>
       <c r="L92">
         <f t="shared" si="29"/>
-        <v>3.9615467875247369E-2</v>
+        <v>1.9807733937623685E-2</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.3">
@@ -5537,13 +7636,16 @@
         <v>49357.271999999997</v>
       </c>
       <c r="H94" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX107</f>
         <v>13.333333333333334</v>
       </c>
       <c r="I94" s="36">
-        <v>60</v>
+        <f>[1]PLS_MODELO_LIVRE!GY107</f>
+        <v>73.333333333333329</v>
       </c>
       <c r="J94" s="36">
-        <v>0.11633281597063863</v>
+        <f>[1]PLS_MODELO_LIVRE!GZ107</f>
+        <v>0.14218455285300277</v>
       </c>
       <c r="K94" s="37">
         <f t="shared" ref="K94:K98" si="30">G94*(H94/100)</f>
@@ -5578,13 +7680,16 @@
         <v>221643.56399999998</v>
       </c>
       <c r="H95" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX108</f>
         <v>13.333333333333334</v>
       </c>
       <c r="I95" s="36">
-        <v>60</v>
+        <f>[1]PLS_MODELO_LIVRE!GY108</f>
+        <v>73.333333333333329</v>
       </c>
       <c r="J95" s="36">
-        <v>0.52240366813401806</v>
+        <f>[1]PLS_MODELO_LIVRE!GZ108</f>
+        <v>0.63849337216379987</v>
       </c>
       <c r="K95" s="37">
         <f t="shared" si="30"/>
@@ -5619,21 +7724,24 @@
         <v>731539.79999999993</v>
       </c>
       <c r="H96" s="36">
-        <v>13.333333333333334</v>
+        <f>[1]PLS_MODELO_LIVRE!GX109</f>
+        <v>6.666666666666667</v>
       </c>
       <c r="I96" s="36">
-        <v>38.333333333333336</v>
+        <f>[1]PLS_MODELO_LIVRE!GY109</f>
+        <v>45</v>
       </c>
       <c r="J96" s="36">
-        <v>1.1015758018830477</v>
+        <f>[1]PLS_MODELO_LIVRE!GZ109</f>
+        <v>1.2931542022105342</v>
       </c>
       <c r="K96" s="37">
         <f t="shared" si="30"/>
-        <v>97538.639999999985</v>
+        <v>48769.319999999992</v>
       </c>
       <c r="L96">
         <f t="shared" si="31"/>
-        <v>0.3831568006549731</v>
+        <v>0.19157840032748655</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.3">
@@ -5660,21 +7768,24 @@
         <v>55701</v>
       </c>
       <c r="H97" s="36">
-        <v>13.333333333333334</v>
+        <f>[1]PLS_MODELO_LIVRE!GX110</f>
+        <v>6.666666666666667</v>
       </c>
       <c r="I97" s="36">
-        <v>38.333333333333336</v>
+        <f>[1]PLS_MODELO_LIVRE!GY110</f>
+        <v>45</v>
       </c>
       <c r="J97" s="36">
-        <v>8.3876330092617857E-2</v>
+        <f>[1]PLS_MODELO_LIVRE!GZ110</f>
+        <v>9.8463517934812256E-2</v>
       </c>
       <c r="K97" s="37">
         <f t="shared" si="30"/>
-        <v>7426.8</v>
+        <v>3713.4</v>
       </c>
       <c r="L97">
         <f t="shared" si="31"/>
-        <v>2.9174375684388819E-2</v>
+        <v>1.4587187842194409E-2</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.3">
@@ -5701,12 +7812,15 @@
         <v>18765.696</v>
       </c>
       <c r="H98" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX111</f>
         <v>0</v>
       </c>
       <c r="I98" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY111</f>
         <v>0</v>
       </c>
       <c r="J98" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ111</f>
         <v>0</v>
       </c>
       <c r="K98" s="37">
@@ -5761,21 +7875,24 @@
         <v>96753.647999999986</v>
       </c>
       <c r="H100" s="36">
-        <v>26.666666666666668</v>
+        <f>[1]PLS_MODELO_LIVRE!GX113</f>
+        <v>13.333333333333334</v>
       </c>
       <c r="I100" s="36">
-        <v>46.666666666666664</v>
+        <f>[1]PLS_MODELO_LIVRE!GY113</f>
+        <v>60</v>
       </c>
       <c r="J100" s="36">
-        <v>0.1773674703246782</v>
+        <f>[1]PLS_MODELO_LIVRE!GZ113</f>
+        <v>0.22804389041744338</v>
       </c>
       <c r="K100" s="37">
         <f t="shared" ref="K100:K102" si="32">G100*(H100/100)</f>
-        <v>25800.972799999996</v>
+        <v>12900.486399999998</v>
       </c>
       <c r="L100">
         <f t="shared" ref="L100:L102" si="33">H100*D100/100</f>
-        <v>0.10135284018553041</v>
+        <v>5.0676420092765205E-2</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.3">
@@ -5802,21 +7919,24 @@
         <v>718708.06799999997</v>
       </c>
       <c r="H101" s="36">
-        <v>26.666666666666668</v>
+        <f>[1]PLS_MODELO_LIVRE!GX114</f>
+        <v>13.333333333333334</v>
       </c>
       <c r="I101" s="36">
-        <v>46.666666666666664</v>
+        <f>[1]PLS_MODELO_LIVRE!GY114</f>
+        <v>60</v>
       </c>
       <c r="J101" s="36">
-        <v>1.3175258458791841</v>
+        <f>[1]PLS_MODELO_LIVRE!GZ114</f>
+        <v>1.6939618018446652</v>
       </c>
       <c r="K101" s="37">
         <f t="shared" si="32"/>
-        <v>191655.48479999998</v>
+        <v>95827.742399999988</v>
       </c>
       <c r="L101">
         <f t="shared" si="33"/>
-        <v>0.75287191193096237</v>
+        <v>0.37643595596548118</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.3">
@@ -5843,21 +7963,24 @@
         <v>264234.33600000001</v>
       </c>
       <c r="H102" s="36">
-        <v>26.666666666666668</v>
+        <f>[1]PLS_MODELO_LIVRE!GX115</f>
+        <v>13.333333333333334</v>
       </c>
       <c r="I102" s="36">
-        <v>46.666666666666664</v>
+        <f>[1]PLS_MODELO_LIVRE!GY115</f>
+        <v>60</v>
       </c>
       <c r="J102" s="36">
-        <v>0.48439078751057596</v>
+        <f>[1]PLS_MODELO_LIVRE!GZ115</f>
+        <v>0.6227881553707405</v>
       </c>
       <c r="K102" s="37">
         <f t="shared" si="32"/>
-        <v>70462.489600000001</v>
+        <v>35231.2448</v>
       </c>
       <c r="L102">
         <f t="shared" si="33"/>
-        <v>0.27679473572032909</v>
+        <v>0.13839736786016454</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.3">
@@ -5903,21 +8026,24 @@
         <v>143217.432</v>
       </c>
       <c r="H104" s="36">
-        <v>0</v>
+        <f>[1]PLS_MODELO_LIVRE!GX117</f>
+        <v>13.333333333333334</v>
       </c>
       <c r="I104" s="36">
-        <v>80</v>
+        <f>[1]PLS_MODELO_LIVRE!GY117</f>
+        <v>93.333333333333329</v>
       </c>
       <c r="J104" s="36">
-        <v>0.45007585131915867</v>
+        <f>[1]PLS_MODELO_LIVRE!GZ117</f>
+        <v>0.52508849320568507</v>
       </c>
       <c r="K104" s="37">
         <f t="shared" ref="K104:K106" si="34">G104*(H104/100)</f>
-        <v>0</v>
+        <v>19095.657599999999</v>
       </c>
       <c r="L104">
         <f t="shared" ref="L104:L106" si="35">H104*D104/100</f>
-        <v>0</v>
+        <v>7.501264188652644E-2</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.3">
@@ -5944,21 +8070,24 @@
         <v>55169.1</v>
       </c>
       <c r="H105" s="36">
-        <v>20</v>
+        <f>[1]PLS_MODELO_LIVRE!GX118</f>
+        <v>6.666666666666667</v>
       </c>
       <c r="I105" s="36">
-        <v>46.666666666666664</v>
+        <f>[1]PLS_MODELO_LIVRE!GY118</f>
+        <v>53.333333333333336</v>
       </c>
       <c r="J105" s="36">
-        <v>0.10113524305656367</v>
+        <f>[1]PLS_MODELO_LIVRE!GZ118</f>
+        <v>0.11558313492178705</v>
       </c>
       <c r="K105" s="37">
         <f t="shared" si="34"/>
-        <v>11033.82</v>
+        <v>3677.94</v>
       </c>
       <c r="L105">
         <f t="shared" si="35"/>
-        <v>4.3343675595670143E-2</v>
+        <v>1.4447891865223382E-2</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.3">
@@ -5985,21 +8114,24 @@
         <v>94155.575999999986</v>
       </c>
       <c r="H106" s="36">
-        <v>20</v>
+        <f>[1]PLS_MODELO_LIVRE!GX119</f>
+        <v>6.666666666666667</v>
       </c>
       <c r="I106" s="36">
-        <v>46.666666666666664</v>
+        <f>[1]PLS_MODELO_LIVRE!GY119</f>
+        <v>53.333333333333336</v>
       </c>
       <c r="J106" s="36">
-        <v>0.17260472010402111</v>
+        <f>[1]PLS_MODELO_LIVRE!GZ119</f>
+        <v>0.19726253726173842</v>
       </c>
       <c r="K106" s="37">
         <f t="shared" si="34"/>
-        <v>18831.115199999997</v>
+        <v>6277.0383999999995</v>
       </c>
       <c r="L106">
         <f t="shared" si="35"/>
-        <v>7.3973451473151902E-2</v>
+        <v>2.4657817157717307E-2</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.3">
@@ -6045,21 +8177,24 @@
         <v>192000</v>
       </c>
       <c r="H108" s="36">
-        <v>20</v>
+        <f>[1]PLS_MODELO_LIVRE!GX121</f>
+        <v>13.333333333333334</v>
       </c>
       <c r="I108" s="36">
-        <v>53.333333333333336</v>
+        <f>[1]PLS_MODELO_LIVRE!GY121</f>
+        <v>66.666666666666657</v>
       </c>
       <c r="J108" s="36">
-        <v>0.4022534698768534</v>
+        <f>[1]PLS_MODELO_LIVRE!GZ121</f>
+        <v>0.50281683734606675</v>
       </c>
       <c r="K108" s="37">
         <f t="shared" ref="K108:K118" si="36">G108*(H108/100)</f>
-        <v>38400</v>
+        <v>25600</v>
       </c>
       <c r="L108">
         <f t="shared" ref="L108:L118" si="37">H108*D108/100</f>
-        <v>0.15084505120382002</v>
+        <v>0.10056336746921335</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.3">
@@ -6086,21 +8221,24 @@
         <v>120000</v>
       </c>
       <c r="H109" s="36">
-        <v>18.75</v>
+        <f>[1]PLS_MODELO_LIVRE!GX122</f>
+        <v>6.25</v>
       </c>
       <c r="I109" s="36">
-        <v>50</v>
+        <f>[1]PLS_MODELO_LIVRE!GY122</f>
+        <v>56.25</v>
       </c>
       <c r="J109" s="36">
-        <v>0.2356953925059688</v>
+        <f>[1]PLS_MODELO_LIVRE!GZ122</f>
+        <v>0.26515731656921487</v>
       </c>
       <c r="K109" s="37">
         <f t="shared" si="36"/>
-        <v>22500</v>
+        <v>7500</v>
       </c>
       <c r="L109">
         <f t="shared" si="37"/>
-        <v>8.8385772189738296E-2</v>
+        <v>2.94619240632461E-2</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.3">
@@ -6127,12 +8265,15 @@
         <v>96000</v>
       </c>
       <c r="H110" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX123</f>
         <v>0</v>
       </c>
       <c r="I110" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY123</f>
         <v>0.83333333333333337</v>
       </c>
       <c r="J110" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ123</f>
         <v>3.1426052334129172E-3</v>
       </c>
       <c r="K110" s="37">
@@ -6168,12 +8309,15 @@
         <v>60000</v>
       </c>
       <c r="H111" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX124</f>
         <v>0</v>
       </c>
       <c r="I111" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY124</f>
         <v>0</v>
       </c>
       <c r="J111" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ124</f>
         <v>0</v>
       </c>
       <c r="K111" s="37">
@@ -6209,12 +8353,15 @@
         <v>216000</v>
       </c>
       <c r="H112" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX125</f>
         <v>0</v>
       </c>
       <c r="I112" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY125</f>
         <v>0.83333333333333337</v>
       </c>
       <c r="J112" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ125</f>
         <v>7.0708617751790628E-3</v>
       </c>
       <c r="K112" s="37">
@@ -6250,12 +8397,15 @@
         <v>144041.67599999998</v>
       </c>
       <c r="H113" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX126</f>
         <v>0</v>
       </c>
       <c r="I113" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY126</f>
         <v>0</v>
       </c>
       <c r="J113" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ126</f>
         <v>0</v>
       </c>
       <c r="K113" s="37">
@@ -6291,12 +8441,15 @@
         <v>609331.31999999995</v>
       </c>
       <c r="H114" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX127</f>
         <v>0</v>
       </c>
       <c r="I114" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY127</f>
         <v>0</v>
       </c>
       <c r="J114" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ127</f>
         <v>0</v>
       </c>
       <c r="K114" s="37">
@@ -6332,12 +8485,15 @@
         <v>5299.1639999999998</v>
       </c>
       <c r="H115" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX128</f>
         <v>0</v>
       </c>
       <c r="I115" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY128</f>
         <v>0</v>
       </c>
       <c r="J115" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ128</f>
         <v>0</v>
       </c>
       <c r="K115" s="37">
@@ -6373,12 +8529,15 @@
         <v>50344.007999999994</v>
       </c>
       <c r="H116" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX129</f>
         <v>0</v>
       </c>
       <c r="I116" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY129</f>
         <v>0</v>
       </c>
       <c r="J116" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ129</f>
         <v>0</v>
       </c>
       <c r="K116" s="37">
@@ -6414,12 +8573,15 @@
         <v>609331.31999999995</v>
       </c>
       <c r="H117" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX130</f>
         <v>0</v>
       </c>
       <c r="I117" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY130</f>
         <v>0</v>
       </c>
       <c r="J117" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ130</f>
         <v>0</v>
       </c>
       <c r="K117" s="37">
@@ -6455,12 +8617,15 @@
         <v>22306.799999999999</v>
       </c>
       <c r="H118" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX131</f>
         <v>0</v>
       </c>
       <c r="I118" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY131</f>
         <v>0</v>
       </c>
       <c r="J118" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ131</f>
         <v>0</v>
       </c>
       <c r="K118" s="37">
@@ -6491,11 +8656,11 @@
       <c r="G119" s="1"/>
       <c r="H119" s="36">
         <f>SUM(L120:L138)</f>
-        <v>0.86493468318595135</v>
+        <v>0.48230550434425734</v>
       </c>
       <c r="I119" s="36">
         <f>AVERAGE(I120:I138)</f>
-        <v>26.474358974358971</v>
+        <v>31.53846153846154</v>
       </c>
       <c r="J119" s="36">
         <f>0.39822979986831*100</f>
@@ -6503,7 +8668,7 @@
       </c>
       <c r="K119" s="39">
         <f t="shared" ref="K119" si="38">SUM(K120:K138)</f>
-        <v>220182.84040000002</v>
+        <v>122778.51489999998</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.3">
@@ -6549,21 +8714,24 @@
         <v>398222.50799999997</v>
       </c>
       <c r="H121" s="36">
-        <v>20</v>
+        <f>[1]PLS_MODELO_LIVRE!GX134</f>
+        <v>13.333333333333334</v>
       </c>
       <c r="I121" s="36">
-        <v>73.333333333333329</v>
+        <f>[1]PLS_MODELO_LIVRE!GY134</f>
+        <v>86.666666666666671</v>
       </c>
       <c r="J121" s="36">
-        <v>1.1471681262283158</v>
+        <f>[1]PLS_MODELO_LIVRE!GZ134</f>
+        <v>1.3557441491789188</v>
       </c>
       <c r="K121" s="37">
         <f t="shared" ref="K121:K124" si="39">G121*(H121/100)</f>
-        <v>79644.501600000003</v>
+        <v>53096.334399999992</v>
       </c>
       <c r="L121">
         <f t="shared" ref="L121:L124" si="40">H121*D121/100</f>
-        <v>0.31286403442590432</v>
+        <v>0.2085760229506029</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.3">
@@ -6590,21 +8758,24 @@
         <v>524159.79599999991</v>
       </c>
       <c r="H122" s="36">
-        <v>13.333333333333334</v>
+        <f>[1]PLS_MODELO_LIVRE!GX135</f>
+        <v>6.666666666666667</v>
       </c>
       <c r="I122" s="36">
-        <v>38.333333333333336</v>
+        <f>[1]PLS_MODELO_LIVRE!GY135</f>
+        <v>45</v>
       </c>
       <c r="J122" s="36">
-        <v>0.78929642323432669</v>
+        <f>[1]PLS_MODELO_LIVRE!GZ135</f>
+        <v>0.9265653664055139</v>
       </c>
       <c r="K122" s="37">
         <f t="shared" si="39"/>
-        <v>69887.972799999989</v>
+        <v>34943.986399999994</v>
       </c>
       <c r="L122">
         <f t="shared" si="40"/>
-        <v>0.27453788634237453</v>
+        <v>0.13726894317118726</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.3">
@@ -6631,21 +8802,24 @@
         <v>28422.743999999999</v>
       </c>
       <c r="H123" s="36">
-        <v>13.333333333333334</v>
+        <f>[1]PLS_MODELO_LIVRE!GX136</f>
+        <v>6.666666666666667</v>
       </c>
       <c r="I123" s="36">
-        <v>38.333333333333336</v>
+        <f>[1]PLS_MODELO_LIVRE!GY136</f>
+        <v>45</v>
       </c>
       <c r="J123" s="36">
-        <v>4.2799868186962055E-2</v>
+        <f>[1]PLS_MODELO_LIVRE!GZ136</f>
+        <v>5.0243323523825018E-2</v>
       </c>
       <c r="K123" s="37">
         <f t="shared" si="39"/>
-        <v>3789.6991999999996</v>
+        <v>1894.8495999999998</v>
       </c>
       <c r="L123">
         <f t="shared" si="40"/>
-        <v>1.4886910673725931E-2</v>
+        <v>7.4434553368629653E-3</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.3">
@@ -6672,21 +8846,24 @@
         <v>86430.275999999998</v>
       </c>
       <c r="H124" s="36">
-        <v>20</v>
+        <f>[1]PLS_MODELO_LIVRE!GX137</f>
+        <v>13.333333333333334</v>
       </c>
       <c r="I124" s="36">
-        <v>80</v>
+        <f>[1]PLS_MODELO_LIVRE!GY137</f>
+        <v>93.333333333333329</v>
       </c>
       <c r="J124" s="36">
-        <v>0.27161623768292292</v>
+        <f>[1]PLS_MODELO_LIVRE!GZ137</f>
+        <v>0.3168856106300767</v>
       </c>
       <c r="K124" s="37">
         <f t="shared" si="39"/>
-        <v>17286.055199999999</v>
+        <v>11524.0368</v>
       </c>
       <c r="L124">
         <f t="shared" si="40"/>
-        <v>6.7904059420730717E-2</v>
+        <v>4.5269372947153823E-2</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.3">
@@ -6732,12 +8909,15 @@
         <v>9700.9920000000002</v>
       </c>
       <c r="H126" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX139</f>
         <v>0</v>
       </c>
       <c r="I126" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY139</f>
         <v>0</v>
       </c>
       <c r="J126" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ139</f>
         <v>0</v>
       </c>
       <c r="K126" s="37">
@@ -6773,12 +8953,15 @@
         <v>64832.843999999997</v>
       </c>
       <c r="H127" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX140</f>
         <v>0</v>
       </c>
       <c r="I127" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY140</f>
         <v>0</v>
       </c>
       <c r="J127" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ140</f>
         <v>0</v>
       </c>
       <c r="K127" s="37">
@@ -6814,12 +8997,15 @@
         <v>54821.231999999996</v>
       </c>
       <c r="H128" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX141</f>
         <v>0</v>
       </c>
       <c r="I128" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY141</f>
         <v>0</v>
       </c>
       <c r="J128" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ141</f>
         <v>0</v>
       </c>
       <c r="K128" s="37">
@@ -6855,12 +9041,15 @@
         <v>242789.95199999999</v>
       </c>
       <c r="H129" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX142</f>
         <v>0</v>
       </c>
       <c r="I129" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY142</f>
         <v>0</v>
       </c>
       <c r="J129" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ142</f>
         <v>0</v>
       </c>
       <c r="K129" s="37">
@@ -6915,21 +9104,24 @@
         <v>168871.54800000001</v>
       </c>
       <c r="H131" s="36">
-        <v>13.333333333333334</v>
+        <f>[1]PLS_MODELO_LIVRE!GX144</f>
+        <v>6.666666666666667</v>
       </c>
       <c r="I131" s="36">
-        <v>38.333333333333336</v>
+        <f>[1]PLS_MODELO_LIVRE!GY144</f>
+        <v>45</v>
       </c>
       <c r="J131" s="36">
-        <v>0.25429212587385075</v>
+        <f>[1]PLS_MODELO_LIVRE!GZ144</f>
+        <v>0.29851684341712914</v>
       </c>
       <c r="K131" s="37">
         <f t="shared" ref="K131" si="43">G131*(H131/100)</f>
-        <v>22516.206400000003</v>
+        <v>11258.103200000001</v>
       </c>
       <c r="L131">
         <f t="shared" ref="L131" si="44">H131*D131/100</f>
-        <v>8.8449435086556782E-2</v>
+        <v>4.4224717543278391E-2</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.3">
@@ -6975,21 +9167,24 @@
         <v>39446.699999999997</v>
       </c>
       <c r="H133" s="36">
-        <v>13.333333333333334</v>
+        <f>[1]PLS_MODELO_LIVRE!GX146</f>
+        <v>6.666666666666667</v>
       </c>
       <c r="I133" s="36">
-        <v>38.333333333333336</v>
+        <f>[1]PLS_MODELO_LIVRE!GY146</f>
+        <v>45</v>
       </c>
       <c r="J133" s="36">
-        <v>5.9400090308333223E-2</v>
+        <f>[1]PLS_MODELO_LIVRE!GZ146</f>
+        <v>6.9730540796739002E-2</v>
       </c>
       <c r="K133" s="37">
         <f t="shared" ref="K133" si="46">G133*(H133/100)</f>
-        <v>5259.5599999999995</v>
+        <v>2629.7799999999997</v>
       </c>
       <c r="L133">
         <f t="shared" ref="L133" si="47">H133*D133/100</f>
-        <v>2.0660900976811555E-2</v>
+        <v>1.0330450488405777E-2</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.3">
@@ -7035,21 +9230,24 @@
         <v>59451.396000000001</v>
       </c>
       <c r="H135" s="36">
-        <v>36.666666666666664</v>
+        <f>[1]PLS_MODELO_LIVRE!GX148</f>
+        <v>12.5</v>
       </c>
       <c r="I135" s="36">
-        <v>37.5</v>
+        <f>[1]PLS_MODELO_LIVRE!GY148</f>
+        <v>50</v>
       </c>
       <c r="J135" s="36">
-        <v>8.7577625720298646E-2</v>
+        <f>[1]PLS_MODELO_LIVRE!GZ148</f>
+        <v>0.11677016762706485</v>
       </c>
       <c r="K135" s="37">
         <f t="shared" ref="K135" si="48">G135*(H135/100)</f>
-        <v>21798.8452</v>
+        <v>7431.4245000000001</v>
       </c>
       <c r="L135">
         <f t="shared" ref="L135" si="49">H135*D135/100</f>
-        <v>8.5631456259847555E-2</v>
+        <v>2.9192541906766213E-2</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.3">
@@ -7095,12 +9293,15 @@
         <v>2705.9639999999995</v>
       </c>
       <c r="H137" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX150</f>
         <v>0</v>
       </c>
       <c r="I137" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY150</f>
         <v>0</v>
       </c>
       <c r="J137" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ150</f>
         <v>0</v>
       </c>
       <c r="K137" s="37">
@@ -7136,12 +9337,15 @@
         <v>15514.332</v>
       </c>
       <c r="H138" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX151</f>
         <v>0</v>
       </c>
       <c r="I138" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY151</f>
         <v>0</v>
       </c>
       <c r="J138" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ151</f>
         <v>0</v>
       </c>
       <c r="K138" s="37">
@@ -7172,11 +9376,11 @@
       <c r="G139" s="1"/>
       <c r="H139" s="36">
         <f>SUM(L140:L205)</f>
-        <v>1.329634759521283</v>
+        <v>0.8661238748610246</v>
       </c>
       <c r="I139" s="36">
         <f>AVERAGE(I140:I205)</f>
-        <v>25.98852901484479</v>
+        <v>27.04116059379216</v>
       </c>
       <c r="J139" s="36">
         <f>0.414110048029731*100</f>
@@ -7184,7 +9388,7 @@
       </c>
       <c r="K139" s="39">
         <f>SUM(K140:K205)</f>
-        <v>338479.61439999996</v>
+        <v>220485.568</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.3">
@@ -7230,12 +9434,15 @@
         <v>113736</v>
       </c>
       <c r="H141" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX154</f>
         <v>0</v>
       </c>
       <c r="I141" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY154</f>
         <v>100</v>
       </c>
       <c r="J141" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ154</f>
         <v>0.44678418603431441</v>
       </c>
       <c r="K141" s="37">
@@ -7271,12 +9478,15 @@
         <v>290136</v>
       </c>
       <c r="H142" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX155</f>
         <v>0</v>
       </c>
       <c r="I142" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY155</f>
         <v>100</v>
       </c>
       <c r="J142" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ155</f>
         <v>1.1397286400018627</v>
       </c>
       <c r="K142" s="37">
@@ -7312,12 +9522,15 @@
         <v>169285.19999999998</v>
       </c>
       <c r="H143" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX156</f>
         <v>0</v>
       </c>
       <c r="I143" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY156</f>
         <v>0</v>
       </c>
       <c r="J143" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ156</f>
         <v>0</v>
       </c>
       <c r="K143" s="37">
@@ -7353,13 +9566,16 @@
         <v>292219.2</v>
       </c>
       <c r="H144" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX157</f>
         <v>13.333333333333334</v>
       </c>
       <c r="I144" s="36">
-        <v>46.666666666666664</v>
+        <f>[1]PLS_MODELO_LIVRE!GY157</f>
+        <v>60</v>
       </c>
       <c r="J144" s="36">
-        <v>0.535692259213846</v>
+        <f>[1]PLS_MODELO_LIVRE!GZ157</f>
+        <v>0.68874719041780186</v>
       </c>
       <c r="K144" s="37">
         <f t="shared" si="52"/>
@@ -7394,12 +9610,15 @@
         <v>164094</v>
       </c>
       <c r="H145" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX158</f>
         <v>0</v>
       </c>
       <c r="I145" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY158</f>
         <v>0</v>
       </c>
       <c r="J145" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ158</f>
         <v>0</v>
       </c>
       <c r="K145" s="37">
@@ -7435,21 +9654,24 @@
         <v>136483.19999999998</v>
       </c>
       <c r="H146" s="36">
-        <v>33.333333333333329</v>
+        <f>[1]PLS_MODELO_LIVRE!GX159</f>
+        <v>0</v>
       </c>
       <c r="I146" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY159</f>
         <v>100</v>
       </c>
       <c r="J146" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ159</f>
         <v>0.53614102324117729</v>
       </c>
       <c r="K146" s="37">
         <f t="shared" si="52"/>
-        <v>45494.399999999987</v>
+        <v>0</v>
       </c>
       <c r="L146">
         <f t="shared" si="53"/>
-        <v>0.17871367441372574</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.3">
@@ -7476,21 +9698,24 @@
         <v>118140.72</v>
       </c>
       <c r="H147" s="36">
-        <v>0</v>
+        <f>[1]PLS_MODELO_LIVRE!GX160</f>
+        <v>6.666666666666667</v>
       </c>
       <c r="I147" s="36">
-        <v>1.6666666666666667</v>
+        <f>[1]PLS_MODELO_LIVRE!GY160</f>
+        <v>8.3333333333333321</v>
       </c>
       <c r="J147" s="36">
-        <v>7.7347842698160434E-3</v>
+        <f>[1]PLS_MODELO_LIVRE!GZ160</f>
+        <v>3.8673921349080216E-2</v>
       </c>
       <c r="K147" s="37">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>7876.0479999999998</v>
       </c>
       <c r="L147">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>3.0939137079264177E-2</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.3">
@@ -7517,12 +9742,15 @@
         <v>10740</v>
       </c>
       <c r="H148" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX161</f>
         <v>0</v>
       </c>
       <c r="I148" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY161</f>
         <v>0</v>
       </c>
       <c r="J148" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ161</f>
         <v>0</v>
       </c>
       <c r="K148" s="37">
@@ -7558,12 +9786,15 @@
         <v>30677.556</v>
       </c>
       <c r="H149" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX162</f>
         <v>0</v>
       </c>
       <c r="I149" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY162</f>
         <v>0</v>
       </c>
       <c r="J149" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ162</f>
         <v>0</v>
       </c>
       <c r="K149" s="37">
@@ -7599,12 +9830,15 @@
         <v>25512</v>
       </c>
       <c r="H150" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX163</f>
         <v>0</v>
       </c>
       <c r="I150" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY163</f>
         <v>0</v>
       </c>
       <c r="J150" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ163</f>
         <v>0</v>
       </c>
       <c r="K150" s="37">
@@ -7640,12 +9874,15 @@
         <v>118380.23999999999</v>
       </c>
       <c r="H151" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX164</f>
         <v>0</v>
       </c>
       <c r="I151" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY164</f>
         <v>0</v>
       </c>
       <c r="J151" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ164</f>
         <v>0</v>
       </c>
       <c r="K151" s="37">
@@ -7681,12 +9918,15 @@
         <v>1656.54</v>
       </c>
       <c r="H152" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX165</f>
         <v>0</v>
       </c>
       <c r="I152" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY165</f>
         <v>0</v>
       </c>
       <c r="J152" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ165</f>
         <v>0</v>
       </c>
       <c r="K152" s="37">
@@ -7722,12 +9962,15 @@
         <v>5508</v>
       </c>
       <c r="H153" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX166</f>
         <v>0</v>
       </c>
       <c r="I153" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY166</f>
         <v>0</v>
       </c>
       <c r="J153" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ166</f>
         <v>0</v>
       </c>
       <c r="K153" s="37">
@@ -7763,12 +10006,15 @@
         <v>42720</v>
       </c>
       <c r="H154" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX167</f>
         <v>0</v>
       </c>
       <c r="I154" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY167</f>
         <v>0</v>
       </c>
       <c r="J154" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ167</f>
         <v>0</v>
       </c>
       <c r="K154" s="37">
@@ -7804,12 +10050,15 @@
         <v>14790.023999999999</v>
       </c>
       <c r="H155" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX168</f>
         <v>0</v>
       </c>
       <c r="I155" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY168</f>
         <v>0</v>
       </c>
       <c r="J155" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ168</f>
         <v>0</v>
       </c>
       <c r="K155" s="37">
@@ -7845,12 +10094,15 @@
         <v>121749.59999999999</v>
       </c>
       <c r="H156" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX169</f>
         <v>0</v>
       </c>
       <c r="I156" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY169</f>
         <v>0</v>
       </c>
       <c r="J156" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ169</f>
         <v>0</v>
       </c>
       <c r="K156" s="37">
@@ -7905,12 +10157,15 @@
         <v>62940.360000000008</v>
       </c>
       <c r="H158" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX171</f>
         <v>0</v>
       </c>
       <c r="I158" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY171</f>
         <v>0</v>
       </c>
       <c r="J158" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ171</f>
         <v>0</v>
       </c>
       <c r="K158" s="37">
@@ -7946,12 +10201,15 @@
         <v>104340.36</v>
       </c>
       <c r="H159" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX172</f>
         <v>0</v>
       </c>
       <c r="I159" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY172</f>
         <v>0</v>
       </c>
       <c r="J159" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ172</f>
         <v>0</v>
       </c>
       <c r="K159" s="37">
@@ -7987,12 +10245,15 @@
         <v>365076.6</v>
       </c>
       <c r="H160" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX173</f>
         <v>0</v>
       </c>
       <c r="I160" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY173</f>
         <v>13.333333333333334</v>
       </c>
       <c r="J160" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ173</f>
         <v>0.19121527229276569</v>
       </c>
       <c r="K160" s="37">
@@ -8028,21 +10289,24 @@
         <v>543894</v>
       </c>
       <c r="H161" s="36">
-        <v>26.666666666666668</v>
+        <f>[1]PLS_MODELO_LIVRE!GX174</f>
+        <v>20</v>
       </c>
       <c r="I161" s="36">
-        <v>73.333333333333329</v>
+        <f>[1]PLS_MODELO_LIVRE!GY174</f>
+        <v>93.333333333333329</v>
       </c>
       <c r="J161" s="36">
-        <v>1.5668071199200613</v>
+        <f>[1]PLS_MODELO_LIVRE!GZ174</f>
+        <v>1.9941181526255327</v>
       </c>
       <c r="K161" s="37">
         <f t="shared" si="54"/>
-        <v>145038.39999999999</v>
+        <v>108778.8</v>
       </c>
       <c r="L161">
         <f t="shared" si="55"/>
-        <v>0.56974804360729503</v>
+        <v>0.42731103270547133</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.3">
@@ -8069,12 +10333,15 @@
         <v>35340.959999999999</v>
       </c>
       <c r="H162" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX175</f>
         <v>0</v>
       </c>
       <c r="I162" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY175</f>
         <v>0</v>
       </c>
       <c r="J162" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ175</f>
         <v>0</v>
       </c>
       <c r="K162" s="37">
@@ -8110,12 +10377,15 @@
         <v>54320.039999999994</v>
       </c>
       <c r="H163" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX176</f>
         <v>0</v>
       </c>
       <c r="I163" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY176</f>
         <v>0</v>
       </c>
       <c r="J163" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ176</f>
         <v>0</v>
       </c>
       <c r="K163" s="37">
@@ -8170,12 +10440,15 @@
         <v>33306</v>
       </c>
       <c r="H165" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX178</f>
         <v>0</v>
       </c>
       <c r="I165" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY178</f>
         <v>100</v>
       </c>
       <c r="J165" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ178</f>
         <v>0.13083451238006327</v>
       </c>
       <c r="K165" s="37">
@@ -8211,12 +10484,15 @@
         <v>38880</v>
       </c>
       <c r="H166" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX179</f>
         <v>0</v>
       </c>
       <c r="I166" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY179</f>
         <v>0</v>
       </c>
       <c r="J166" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ179</f>
         <v>0</v>
       </c>
       <c r="K166" s="37">
@@ -8252,12 +10528,15 @@
         <v>24540.42</v>
       </c>
       <c r="H167" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX180</f>
         <v>0</v>
       </c>
       <c r="I167" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY180</f>
         <v>0</v>
       </c>
       <c r="J167" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ180</f>
         <v>0</v>
       </c>
       <c r="K167" s="37">
@@ -8293,12 +10572,15 @@
         <v>36959.579999999994</v>
       </c>
       <c r="H168" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX181</f>
         <v>0</v>
       </c>
       <c r="I168" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY181</f>
         <v>100</v>
       </c>
       <c r="J168" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ181</f>
         <v>0.14518671191592922</v>
       </c>
       <c r="K168" s="37">
@@ -8356,12 +10638,15 @@
         <v>79142.759999999995</v>
       </c>
       <c r="H170" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX183</f>
         <v>0</v>
       </c>
       <c r="I170" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY183</f>
         <v>100</v>
       </c>
       <c r="J170" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ183</f>
         <v>0.31089306470342809</v>
       </c>
       <c r="K170" s="37">
@@ -8397,12 +10682,15 @@
         <v>75898.2</v>
       </c>
       <c r="H171" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX184</f>
         <v>0</v>
       </c>
       <c r="I171" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY184</f>
         <v>100</v>
       </c>
       <c r="J171" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ184</f>
         <v>0.29814760065827534</v>
       </c>
       <c r="K171" s="37">
@@ -8438,12 +10726,15 @@
         <v>17976</v>
       </c>
       <c r="H172" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX185</f>
         <v>0</v>
       </c>
       <c r="I172" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY185</f>
         <v>100</v>
       </c>
       <c r="J172" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ185</f>
         <v>7.0614339594788259E-2</v>
       </c>
       <c r="K172" s="37">
@@ -8479,12 +10770,15 @@
         <v>34116</v>
       </c>
       <c r="H173" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX186</f>
         <v>0</v>
       </c>
       <c r="I173" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY186</f>
         <v>0</v>
       </c>
       <c r="J173" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ186</f>
         <v>0</v>
       </c>
       <c r="K173" s="37">
@@ -8520,12 +10814,15 @@
         <v>1182.3599999999999</v>
       </c>
       <c r="H174" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX187</f>
         <v>0</v>
       </c>
       <c r="I174" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY187</f>
         <v>0</v>
       </c>
       <c r="J174" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ187</f>
         <v>0</v>
       </c>
       <c r="K174" s="37">
@@ -8561,12 +10858,15 @@
         <v>10272</v>
       </c>
       <c r="H175" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX188</f>
         <v>0</v>
       </c>
       <c r="I175" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY188</f>
         <v>0</v>
       </c>
       <c r="J175" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ188</f>
         <v>0</v>
       </c>
       <c r="K175" s="37">
@@ -8602,12 +10902,15 @@
         <v>51816</v>
       </c>
       <c r="H176" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX189</f>
         <v>0</v>
       </c>
       <c r="I176" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY189</f>
         <v>0</v>
       </c>
       <c r="J176" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ189</f>
         <v>0</v>
       </c>
       <c r="K176" s="37">
@@ -8662,21 +10965,24 @@
         <v>159112.79999999999</v>
       </c>
       <c r="H178" s="36">
-        <v>13.333333333333334</v>
+        <f>[1]PLS_MODELO_LIVRE!GX191</f>
+        <v>0</v>
       </c>
       <c r="I178" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY191</f>
         <v>100</v>
       </c>
       <c r="J178" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ191</f>
         <v>0.62503589747872845</v>
       </c>
       <c r="K178" s="37">
         <f t="shared" ref="K178:K183" si="60">G178*(H178/100)</f>
-        <v>21215.039999999997</v>
+        <v>0</v>
       </c>
       <c r="L178">
         <f t="shared" ref="L178:L183" si="61">H178*D178/100</f>
-        <v>8.3338119663830479E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.3">
@@ -8703,21 +11009,24 @@
         <v>324340.8</v>
       </c>
       <c r="H179" s="36">
-        <v>13.333333333333334</v>
+        <f>[1]PLS_MODELO_LIVRE!GX192</f>
+        <v>20</v>
       </c>
       <c r="I179" s="36">
-        <v>80</v>
+        <f>[1]PLS_MODELO_LIVRE!GY192</f>
+        <v>100</v>
       </c>
       <c r="J179" s="36">
-        <v>1.0192750954893324</v>
+        <f>[1]PLS_MODELO_LIVRE!GZ192</f>
+        <v>1.2740938693616655</v>
       </c>
       <c r="K179" s="37">
         <f t="shared" si="60"/>
-        <v>43245.439999999995</v>
+        <v>64868.160000000003</v>
       </c>
       <c r="L179">
         <f t="shared" si="61"/>
-        <v>0.16987918258155543</v>
+        <v>0.25481877387233309</v>
       </c>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.3">
@@ -8744,12 +11053,15 @@
         <v>224786.87999999998</v>
       </c>
       <c r="H180" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX193</f>
         <v>0</v>
       </c>
       <c r="I180" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY193</f>
         <v>0</v>
       </c>
       <c r="J180" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ193</f>
         <v>0</v>
       </c>
       <c r="K180" s="37">
@@ -8785,21 +11097,24 @@
         <v>166329.60000000001</v>
       </c>
       <c r="H181" s="36">
-        <v>13.333333333333334</v>
+        <f>[1]PLS_MODELO_LIVRE!GX194</f>
+        <v>0</v>
       </c>
       <c r="I181" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY194</f>
         <v>100</v>
       </c>
       <c r="J181" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ194</f>
         <v>0.6533853392893465</v>
       </c>
       <c r="K181" s="37">
         <f t="shared" si="60"/>
-        <v>22177.279999999999</v>
+        <v>0</v>
       </c>
       <c r="L181">
         <f t="shared" si="61"/>
-        <v>8.7118045238579536E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.3">
@@ -8826,12 +11141,15 @@
         <v>44550.36</v>
       </c>
       <c r="H182" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX195</f>
         <v>0</v>
       </c>
       <c r="I182" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY195</f>
         <v>0</v>
       </c>
       <c r="J182" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ195</f>
         <v>0</v>
       </c>
       <c r="K182" s="37">
@@ -8867,12 +11185,15 @@
         <v>10380</v>
       </c>
       <c r="H183" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX196</f>
         <v>0</v>
       </c>
       <c r="I183" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY196</f>
         <v>0</v>
       </c>
       <c r="J183" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ196</f>
         <v>0</v>
       </c>
       <c r="K183" s="37">
@@ -8927,12 +11248,15 @@
         <v>732000</v>
       </c>
       <c r="H185" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX198</f>
         <v>0</v>
       </c>
       <c r="I185" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY198</f>
         <v>53.846153846153847</v>
       </c>
       <c r="J185" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ198</f>
         <v>1.5483374246161334</v>
       </c>
       <c r="K185" s="37">
@@ -8968,12 +11292,15 @@
         <v>74920.319999999992</v>
       </c>
       <c r="H186" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX199</f>
         <v>0</v>
       </c>
       <c r="I186" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY199</f>
         <v>0</v>
       </c>
       <c r="J186" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ199</f>
         <v>0</v>
       </c>
       <c r="K186" s="37">
@@ -9009,12 +11336,15 @@
         <v>23641.439999999999</v>
       </c>
       <c r="H187" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX200</f>
         <v>0</v>
       </c>
       <c r="I187" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY200</f>
         <v>0</v>
       </c>
       <c r="J187" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ200</f>
         <v>0</v>
       </c>
       <c r="K187" s="37">
@@ -9069,12 +11399,15 @@
         <v>222248.92799999999</v>
       </c>
       <c r="H189" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX202</f>
         <v>0</v>
       </c>
       <c r="I189" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY202</f>
         <v>0.83333333333333337</v>
       </c>
       <c r="J189" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ202</f>
         <v>7.2754233776376092E-3</v>
       </c>
       <c r="K189" s="37">
@@ -9110,12 +11443,15 @@
         <v>94380</v>
       </c>
       <c r="H190" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX203</f>
         <v>0</v>
       </c>
       <c r="I190" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY203</f>
         <v>0.83333333333333337</v>
       </c>
       <c r="J190" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ203</f>
         <v>3.0895737700990743E-3</v>
       </c>
       <c r="K190" s="37">
@@ -9151,12 +11487,15 @@
         <v>64614.000000000007</v>
       </c>
       <c r="H191" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX204</f>
         <v>0</v>
       </c>
       <c r="I191" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY204</f>
         <v>0.83333333333333337</v>
       </c>
       <c r="J191" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ204</f>
         <v>2.1151697349139822E-3</v>
       </c>
       <c r="K191" s="37">
@@ -9192,12 +11531,15 @@
         <v>131269.128</v>
       </c>
       <c r="H192" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX205</f>
         <v>0</v>
       </c>
       <c r="I192" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY205</f>
         <v>0.83333333333333337</v>
       </c>
       <c r="J192" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ205</f>
         <v>4.2971567566494799E-3</v>
       </c>
       <c r="K192" s="37">
@@ -9233,12 +11575,15 @@
         <v>62952</v>
       </c>
       <c r="H193" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX206</f>
         <v>0</v>
       </c>
       <c r="I193" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY206</f>
         <v>0.83333333333333337</v>
       </c>
       <c r="J193" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ206</f>
         <v>2.0607633818105204E-3</v>
       </c>
       <c r="K193" s="37">
@@ -9274,12 +11619,15 @@
         <v>49044</v>
       </c>
       <c r="H194" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX207</f>
         <v>0</v>
       </c>
       <c r="I194" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY207</f>
         <v>0.83333333333333337</v>
       </c>
       <c r="J194" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ207</f>
         <v>1.605478448619824E-3</v>
       </c>
       <c r="K194" s="37">
@@ -9315,12 +11663,15 @@
         <v>81510</v>
       </c>
       <c r="H195" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX208</f>
         <v>0</v>
       </c>
       <c r="I195" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY208</f>
         <v>0.83333333333333337</v>
       </c>
       <c r="J195" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ208</f>
         <v>2.6682682559946553E-3</v>
       </c>
       <c r="K195" s="37">
@@ -9356,12 +11707,15 @@
         <v>17710.189999999999</v>
       </c>
       <c r="H196" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX209</f>
         <v>0</v>
       </c>
       <c r="I196" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY209</f>
         <v>0</v>
       </c>
       <c r="J196" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ209</f>
         <v>0</v>
       </c>
       <c r="K196" s="37">
@@ -9416,21 +11770,24 @@
         <v>18507.984</v>
       </c>
       <c r="H198" s="36">
-        <v>13.333333333333334</v>
+        <f>[1]PLS_MODELO_LIVRE!GX211</f>
+        <v>0</v>
       </c>
       <c r="I198" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY211</f>
         <v>100</v>
       </c>
       <c r="J198" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ211</f>
         <v>7.2704109222903171E-2</v>
       </c>
       <c r="K198" s="37">
         <f t="shared" ref="K198:K200" si="67">G198*(H198/100)</f>
-        <v>2467.7312000000002</v>
+        <v>0</v>
       </c>
       <c r="L198">
         <f t="shared" ref="L198:L200" si="68">H198*D198/100</f>
-        <v>9.6938812297204229E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.3">
@@ -9457,21 +11814,24 @@
         <v>10229.232</v>
       </c>
       <c r="H199" s="36">
-        <v>20</v>
+        <f>[1]PLS_MODELO_LIVRE!GX212</f>
+        <v>0</v>
       </c>
       <c r="I199" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY212</f>
         <v>53.333333333333336</v>
       </c>
       <c r="J199" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ212</f>
         <v>2.1430958677996589E-2</v>
       </c>
       <c r="K199" s="37">
         <f t="shared" si="67"/>
-        <v>2045.8464000000001</v>
+        <v>0</v>
       </c>
       <c r="L199">
         <f t="shared" si="68"/>
-        <v>8.036609504248721E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.3">
@@ -9498,21 +11858,24 @@
         <v>89164.584000000003</v>
       </c>
       <c r="H200" s="36">
-        <v>20</v>
+        <f>[1]PLS_MODELO_LIVRE!GX213</f>
+        <v>0</v>
       </c>
       <c r="I200" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY213</f>
         <v>53.333333333333336</v>
       </c>
       <c r="J200" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ213</f>
         <v>0.1868060588756571</v>
       </c>
       <c r="K200" s="37">
         <f t="shared" si="67"/>
-        <v>17832.916800000003</v>
+        <v>0</v>
       </c>
       <c r="L200">
         <f t="shared" si="68"/>
-        <v>7.0052272078371405E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.3">
@@ -9558,12 +11921,15 @@
         <v>7029.9359999999997</v>
       </c>
       <c r="H202" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX215</f>
         <v>0</v>
       </c>
       <c r="I202" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY215</f>
         <v>0</v>
       </c>
       <c r="J202" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ215</f>
         <v>0</v>
       </c>
       <c r="K202" s="37">
@@ -9599,12 +11965,15 @@
         <v>5886</v>
       </c>
       <c r="H203" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX216</f>
         <v>0</v>
       </c>
       <c r="I203" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY216</f>
         <v>0</v>
       </c>
       <c r="J203" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ216</f>
         <v>0</v>
       </c>
       <c r="K203" s="37">
@@ -9640,12 +12009,15 @@
         <v>16356</v>
       </c>
       <c r="H204" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX217</f>
         <v>0</v>
       </c>
       <c r="I204" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY217</f>
         <v>0</v>
       </c>
       <c r="J204" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ217</f>
         <v>0</v>
       </c>
       <c r="K204" s="37">
@@ -9681,12 +12053,15 @@
         <v>1500.3119999999999</v>
       </c>
       <c r="H205" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX218</f>
         <v>0</v>
       </c>
       <c r="I205" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY218</f>
         <v>0</v>
       </c>
       <c r="J205" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ218</f>
         <v>0</v>
       </c>
       <c r="K205" s="37">
@@ -9756,12 +12131,15 @@
         <v>203759.14800000002</v>
       </c>
       <c r="H207" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX220</f>
         <v>0</v>
       </c>
       <c r="I207" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY220</f>
         <v>0.83333333333333337</v>
       </c>
       <c r="J207" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ220</f>
         <v>6.6701517172974715E-3</v>
       </c>
       <c r="K207" s="37">
@@ -9797,12 +12175,15 @@
         <v>45715.199999999997</v>
       </c>
       <c r="H208" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GX221</f>
         <v>0</v>
       </c>
       <c r="I208" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GY221</f>
         <v>0</v>
       </c>
       <c r="J208" s="36">
+        <f>[1]PLS_MODELO_LIVRE!GZ221</f>
         <v>0</v>
       </c>
       <c r="K208" s="37">
@@ -9823,17 +12204,19 @@
         <v>399</v>
       </c>
       <c r="H209" s="36">
-        <v>4.4776653850378603</v>
+        <f>[1]PLS_MODELO_LIVRE!$GX$222</f>
+        <v>3.128608157696243</v>
       </c>
       <c r="I209" t="s">
         <v>398</v>
       </c>
       <c r="J209" s="36">
-        <v>57.941238513951596</v>
+        <f>[1]PLS_MODELO_LIVRE!$GZ$222</f>
+        <v>61.069846671647859</v>
       </c>
       <c r="K209" s="37">
         <f>K139+K119+K89+K73+K45+K27+K13+K2+K206</f>
-        <v>1139860.7339999997</v>
+        <v>796436.82239999983</v>
       </c>
     </row>
   </sheetData>

--- a/data/pls.xlsx
+++ b/data/pls.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30030"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30125"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rssla\Desktop\SPE JARDIM LUZ\01. Relatorio Obra Ramon Gerenciamento\meu-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F974BA5-7C01-4563-B83A-DB26BE752493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42CC588E-DC55-4F95-B61E-3EB204065BD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{ECBE0EBD-AF5F-4C5B-967D-6D79DF9A9648}"/>
   </bookViews>
@@ -1764,10 +1764,10 @@
             <v>2.9411764705882351</v>
           </cell>
           <cell r="GY19">
-            <v>58.82352941176471</v>
+            <v>61.764705882352942</v>
           </cell>
           <cell r="GZ19">
-            <v>0.61724456202773725</v>
+            <v>0.64810679012912409</v>
           </cell>
         </row>
         <row r="20">
@@ -1775,10 +1775,10 @@
             <v>2.9411764705882351</v>
           </cell>
           <cell r="GY20">
-            <v>58.82352941176471</v>
+            <v>61.764705882352942</v>
           </cell>
           <cell r="GZ20">
-            <v>0.48913676250449695</v>
+            <v>0.51359360062972181</v>
           </cell>
         </row>
         <row r="21">
@@ -1786,10 +1786,10 @@
             <v>2.9411764705882351</v>
           </cell>
           <cell r="GY21">
-            <v>58.82352941176471</v>
+            <v>61.764705882352942</v>
           </cell>
           <cell r="GZ21">
-            <v>0.10015640009148638</v>
+            <v>0.1051642200960607</v>
           </cell>
         </row>
         <row r="22">
@@ -1797,10 +1797,10 @@
             <v>2.9411764705882351</v>
           </cell>
           <cell r="GY22">
-            <v>58.82352941176471</v>
+            <v>61.764705882352942</v>
           </cell>
           <cell r="GZ22">
-            <v>4.5419444917470214E-2</v>
+            <v>4.7690417163343719E-2</v>
           </cell>
         </row>
         <row r="23">
@@ -1808,10 +1808,10 @@
             <v>2.9411764705882351</v>
           </cell>
           <cell r="GY23">
-            <v>58.82352941176471</v>
+            <v>61.764705882352942</v>
           </cell>
           <cell r="GZ23">
-            <v>3.726721268147376E-2</v>
+            <v>3.9130573315547451E-2</v>
           </cell>
         </row>
         <row r="24">
@@ -1819,10 +1819,10 @@
             <v>2.9411764705882351</v>
           </cell>
           <cell r="GY24">
-            <v>58.82352941176471</v>
+            <v>61.764705882352942</v>
           </cell>
           <cell r="GZ24">
-            <v>2.3885371076554876E-2</v>
+            <v>2.5079639630382622E-2</v>
           </cell>
         </row>
         <row r="25">
@@ -1830,10 +1830,10 @@
             <v>2.9411764705882351</v>
           </cell>
           <cell r="GY25">
-            <v>58.82352941176471</v>
+            <v>61.764705882352942</v>
           </cell>
           <cell r="GZ25">
-            <v>2.3431996847346097</v>
+            <v>2.4603596689713401</v>
           </cell>
         </row>
         <row r="28">
@@ -2168,13 +2168,13 @@
         </row>
         <row r="64">
           <cell r="GX64">
-            <v>17.5</v>
+            <v>8.3333333333333321</v>
           </cell>
           <cell r="GY64">
-            <v>18.333333333333332</v>
+            <v>26.666666666666668</v>
           </cell>
           <cell r="GZ64">
-            <v>0.42992471626551543</v>
+            <v>0.62534504184074968</v>
           </cell>
         </row>
         <row r="65">
@@ -2344,24 +2344,24 @@
         </row>
         <row r="84">
           <cell r="GX84">
-            <v>0</v>
+            <v>24.166666666666668</v>
           </cell>
           <cell r="GY84">
-            <v>0.83333333333333337</v>
+            <v>25</v>
           </cell>
           <cell r="GZ84">
-            <v>3.2060701461016912E-3</v>
+            <v>9.6182104383050734E-2</v>
           </cell>
         </row>
         <row r="85">
           <cell r="GX85">
-            <v>0</v>
+            <v>24.166666666666668</v>
           </cell>
           <cell r="GY85">
-            <v>0.83333333333333337</v>
+            <v>25</v>
           </cell>
           <cell r="GZ85">
-            <v>1.445566981317608E-3</v>
+            <v>4.3367009439528238E-2</v>
           </cell>
         </row>
         <row r="88">
@@ -2421,13 +2421,13 @@
         </row>
         <row r="94">
           <cell r="GX94">
-            <v>0</v>
+            <v>100</v>
           </cell>
           <cell r="GY94">
-            <v>0</v>
+            <v>100</v>
           </cell>
           <cell r="GZ94">
-            <v>0</v>
+            <v>4.5061470755332143E-2</v>
           </cell>
         </row>
         <row r="95">
@@ -2454,13 +2454,13 @@
         </row>
         <row r="97">
           <cell r="GX97">
-            <v>6.666666666666667</v>
+            <v>13.333333333333334</v>
           </cell>
           <cell r="GY97">
-            <v>52.5</v>
+            <v>65.833333333333329</v>
           </cell>
           <cell r="GZ97">
-            <v>7.4123228824227699E-2</v>
+            <v>9.2948175827206145E-2</v>
           </cell>
         </row>
         <row r="98">
@@ -2520,7 +2520,7 @@
         </row>
         <row r="105">
           <cell r="GX105">
-            <v>13.333333333333334</v>
+            <v>0</v>
           </cell>
           <cell r="GY105">
             <v>100</v>
@@ -2531,46 +2531,46 @@
         </row>
         <row r="107">
           <cell r="GX107">
-            <v>13.333333333333334</v>
+            <v>6.666666666666667</v>
           </cell>
           <cell r="GY107">
-            <v>73.333333333333329</v>
+            <v>80</v>
           </cell>
           <cell r="GZ107">
-            <v>0.14218455285300277</v>
+            <v>0.15511042129418484</v>
           </cell>
         </row>
         <row r="108">
           <cell r="GX108">
-            <v>13.333333333333334</v>
+            <v>6.666666666666667</v>
           </cell>
           <cell r="GY108">
-            <v>73.333333333333329</v>
+            <v>80</v>
           </cell>
           <cell r="GZ108">
-            <v>0.63849337216379987</v>
+            <v>0.69653822417869082</v>
           </cell>
         </row>
         <row r="109">
           <cell r="GX109">
-            <v>6.666666666666667</v>
+            <v>13.333333333333334</v>
           </cell>
           <cell r="GY109">
-            <v>45</v>
+            <v>58.333333333333336</v>
           </cell>
           <cell r="GZ109">
-            <v>1.2931542022105342</v>
+            <v>1.6763110028655075</v>
           </cell>
         </row>
         <row r="110">
           <cell r="GX110">
-            <v>6.666666666666667</v>
+            <v>13.333333333333334</v>
           </cell>
           <cell r="GY110">
-            <v>45</v>
+            <v>58.333333333333336</v>
           </cell>
           <cell r="GZ110">
-            <v>9.8463517934812256E-2</v>
+            <v>0.12763789361920108</v>
           </cell>
         </row>
         <row r="111">
@@ -2589,10 +2589,10 @@
             <v>13.333333333333334</v>
           </cell>
           <cell r="GY113">
-            <v>60</v>
+            <v>73.333333333333329</v>
           </cell>
           <cell r="GZ113">
-            <v>0.22804389041744338</v>
+            <v>0.27872031051020857</v>
           </cell>
         </row>
         <row r="114">
@@ -2600,10 +2600,10 @@
             <v>13.333333333333334</v>
           </cell>
           <cell r="GY114">
-            <v>60</v>
+            <v>73.333333333333329</v>
           </cell>
           <cell r="GZ114">
-            <v>1.6939618018446652</v>
+            <v>2.070397757810146</v>
           </cell>
         </row>
         <row r="115">
@@ -2611,21 +2611,21 @@
             <v>13.333333333333334</v>
           </cell>
           <cell r="GY115">
-            <v>60</v>
+            <v>73.333333333333329</v>
           </cell>
           <cell r="GZ115">
-            <v>0.6227881553707405</v>
+            <v>0.76118552323090494</v>
           </cell>
         </row>
         <row r="117">
           <cell r="GX117">
-            <v>13.333333333333334</v>
+            <v>6.666666666666667</v>
           </cell>
           <cell r="GY117">
-            <v>93.333333333333329</v>
+            <v>100</v>
           </cell>
           <cell r="GZ117">
-            <v>0.52508849320568507</v>
+            <v>0.5625948141489483</v>
           </cell>
         </row>
         <row r="118">
@@ -2633,10 +2633,10 @@
             <v>6.666666666666667</v>
           </cell>
           <cell r="GY118">
-            <v>53.333333333333336</v>
+            <v>60</v>
           </cell>
           <cell r="GZ118">
-            <v>0.11558313492178705</v>
+            <v>0.13003102678701042</v>
           </cell>
         </row>
         <row r="119">
@@ -2644,10 +2644,10 @@
             <v>6.666666666666667</v>
           </cell>
           <cell r="GY119">
-            <v>53.333333333333336</v>
+            <v>60</v>
           </cell>
           <cell r="GZ119">
-            <v>0.19726253726173842</v>
+            <v>0.22192035441945571</v>
           </cell>
         </row>
         <row r="121">
@@ -2655,21 +2655,21 @@
             <v>13.333333333333334</v>
           </cell>
           <cell r="GY121">
-            <v>66.666666666666657</v>
+            <v>80</v>
           </cell>
           <cell r="GZ121">
-            <v>0.50281683734606675</v>
+            <v>0.60338020481528021</v>
           </cell>
         </row>
         <row r="122">
           <cell r="GX122">
-            <v>6.25</v>
+            <v>18.75</v>
           </cell>
           <cell r="GY122">
-            <v>56.25</v>
+            <v>75</v>
           </cell>
           <cell r="GZ122">
-            <v>0.26515731656921487</v>
+            <v>0.35354308875895318</v>
           </cell>
         </row>
         <row r="123">
@@ -2773,46 +2773,46 @@
         </row>
         <row r="134">
           <cell r="GX134">
-            <v>13.333333333333334</v>
+            <v>6.666666666666667</v>
           </cell>
           <cell r="GY134">
-            <v>86.666666666666671</v>
+            <v>93.333333333333329</v>
           </cell>
           <cell r="GZ134">
-            <v>1.3557441491789188</v>
+            <v>1.4600321606542204</v>
           </cell>
         </row>
         <row r="135">
           <cell r="GX135">
-            <v>6.666666666666667</v>
+            <v>13.333333333333334</v>
           </cell>
           <cell r="GY135">
-            <v>45</v>
+            <v>58.333333333333336</v>
           </cell>
           <cell r="GZ135">
-            <v>0.9265653664055139</v>
+            <v>1.2011032527478884</v>
           </cell>
         </row>
         <row r="136">
           <cell r="GX136">
-            <v>6.666666666666667</v>
+            <v>13.333333333333334</v>
           </cell>
           <cell r="GY136">
-            <v>45</v>
+            <v>58.333333333333336</v>
           </cell>
           <cell r="GZ136">
-            <v>5.0243323523825018E-2</v>
+            <v>6.5130234197550943E-2</v>
           </cell>
         </row>
         <row r="137">
           <cell r="GX137">
-            <v>13.333333333333334</v>
+            <v>6.666666666666667</v>
           </cell>
           <cell r="GY137">
-            <v>93.333333333333329</v>
+            <v>100</v>
           </cell>
           <cell r="GZ137">
-            <v>0.3168856106300767</v>
+            <v>0.33952029710365361</v>
           </cell>
         </row>
         <row r="139">
@@ -2850,40 +2850,40 @@
         </row>
         <row r="142">
           <cell r="GX142">
-            <v>0</v>
+            <v>100</v>
           </cell>
           <cell r="GY142">
-            <v>0</v>
+            <v>100</v>
           </cell>
           <cell r="GZ142">
-            <v>0</v>
+            <v>0.95374121721908867</v>
           </cell>
         </row>
         <row r="144">
           <cell r="GX144">
-            <v>6.666666666666667</v>
+            <v>13.333333333333334</v>
           </cell>
           <cell r="GY144">
-            <v>45</v>
+            <v>58.333333333333336</v>
           </cell>
           <cell r="GZ144">
-            <v>0.29851684341712914</v>
+            <v>0.38696627850368592</v>
           </cell>
         </row>
         <row r="146">
           <cell r="GX146">
-            <v>6.666666666666667</v>
+            <v>13.333333333333334</v>
           </cell>
           <cell r="GY146">
-            <v>45</v>
+            <v>58.333333333333336</v>
           </cell>
           <cell r="GZ146">
-            <v>6.9730540796739002E-2</v>
+            <v>9.039144177355056E-2</v>
           </cell>
         </row>
         <row r="148">
           <cell r="GX148">
-            <v>12.5</v>
+            <v>0</v>
           </cell>
           <cell r="GY148">
             <v>50</v>
@@ -2952,10 +2952,10 @@
             <v>13.333333333333334</v>
           </cell>
           <cell r="GY157">
-            <v>60</v>
+            <v>73.333333333333329</v>
           </cell>
           <cell r="GZ157">
-            <v>0.68874719041780186</v>
+            <v>0.84180212162175783</v>
           </cell>
         </row>
         <row r="158">
@@ -2982,13 +2982,13 @@
         </row>
         <row r="160">
           <cell r="GX160">
-            <v>6.666666666666667</v>
+            <v>5</v>
           </cell>
           <cell r="GY160">
-            <v>8.3333333333333321</v>
+            <v>13.333333333333334</v>
           </cell>
           <cell r="GZ160">
-            <v>3.8673921349080216E-2</v>
+            <v>6.1878274158528347E-2</v>
           </cell>
         </row>
         <row r="161">
@@ -3048,13 +3048,13 @@
         </row>
         <row r="166">
           <cell r="GX166">
-            <v>0</v>
+            <v>100</v>
           </cell>
           <cell r="GY166">
-            <v>0</v>
+            <v>100</v>
           </cell>
           <cell r="GZ166">
-            <v>0</v>
+            <v>2.1636837032047933E-2</v>
           </cell>
         </row>
         <row r="167">
@@ -3125,13 +3125,13 @@
         </row>
         <row r="174">
           <cell r="GX174">
-            <v>20</v>
+            <v>6.666666666666667</v>
           </cell>
           <cell r="GY174">
-            <v>93.333333333333329</v>
+            <v>100</v>
           </cell>
           <cell r="GZ174">
-            <v>1.9941181526255327</v>
+            <v>2.1365551635273565</v>
           </cell>
         </row>
         <row r="175">
@@ -3290,7 +3290,7 @@
         </row>
         <row r="192">
           <cell r="GX192">
-            <v>20</v>
+            <v>0</v>
           </cell>
           <cell r="GY192">
             <v>100</v>
@@ -3477,24 +3477,24 @@
         </row>
         <row r="212">
           <cell r="GX212">
-            <v>0</v>
+            <v>46.666666666666664</v>
           </cell>
           <cell r="GY212">
-            <v>53.333333333333336</v>
+            <v>100</v>
           </cell>
           <cell r="GZ212">
-            <v>2.1430958677996589E-2</v>
+            <v>4.0183047521243603E-2</v>
           </cell>
         </row>
         <row r="213">
           <cell r="GX213">
-            <v>0</v>
+            <v>46.666666666666664</v>
           </cell>
           <cell r="GY213">
-            <v>53.333333333333336</v>
+            <v>100</v>
           </cell>
           <cell r="GZ213">
-            <v>0.1868060588756571</v>
+            <v>0.35026136039185707</v>
           </cell>
         </row>
         <row r="215">
@@ -3565,10 +3565,10 @@
         </row>
         <row r="222">
           <cell r="GX222">
-            <v>3.128608157696243</v>
+            <v>3.8931320728235561</v>
           </cell>
           <cell r="GZ222">
-            <v>61.069846671647859</v>
+            <v>64.962978744471414</v>
           </cell>
         </row>
       </sheetData>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="I2" s="36">
         <f>AVERAGE(I3:I12)</f>
-        <v>71.176470588235304</v>
+        <v>73.235294117647044</v>
       </c>
       <c r="J2">
         <f>0.637484224224017*100</f>
@@ -4128,7 +4128,7 @@
         <v>65</v>
       </c>
       <c r="G6" s="1">
-        <f t="shared" si="1"/>
+        <f>C6*E6</f>
         <v>267119.96639999998</v>
       </c>
       <c r="H6" s="36">
@@ -4137,11 +4137,11 @@
       </c>
       <c r="I6" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY19</f>
-        <v>58.82352941176471</v>
+        <v>61.764705882352942</v>
       </c>
       <c r="J6" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ19</f>
-        <v>0.61724456202773725</v>
+        <v>0.64810679012912409</v>
       </c>
       <c r="K6" s="37">
         <f>G6*(H6/100)</f>
@@ -4181,11 +4181,11 @@
       </c>
       <c r="I7" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY20</f>
-        <v>58.82352941176471</v>
+        <v>61.764705882352942</v>
       </c>
       <c r="J7" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ20</f>
-        <v>0.48913676250449695</v>
+        <v>0.51359360062972181</v>
       </c>
       <c r="K7" s="37">
         <f t="shared" ref="K7:K12" si="3">G7*(H7/100)</f>
@@ -4225,11 +4225,11 @@
       </c>
       <c r="I8" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY21</f>
-        <v>58.82352941176471</v>
+        <v>61.764705882352942</v>
       </c>
       <c r="J8" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ21</f>
-        <v>0.10015640009148638</v>
+        <v>0.1051642200960607</v>
       </c>
       <c r="K8" s="37">
         <f t="shared" si="3"/>
@@ -4269,11 +4269,11 @@
       </c>
       <c r="I9" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY22</f>
-        <v>58.82352941176471</v>
+        <v>61.764705882352942</v>
       </c>
       <c r="J9" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ22</f>
-        <v>4.5419444917470214E-2</v>
+        <v>4.7690417163343719E-2</v>
       </c>
       <c r="K9" s="37">
         <f t="shared" si="3"/>
@@ -4313,11 +4313,11 @@
       </c>
       <c r="I10" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY23</f>
-        <v>58.82352941176471</v>
+        <v>61.764705882352942</v>
       </c>
       <c r="J10" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ23</f>
-        <v>3.726721268147376E-2</v>
+        <v>3.9130573315547451E-2</v>
       </c>
       <c r="K10" s="37">
         <f t="shared" si="3"/>
@@ -4357,11 +4357,11 @@
       </c>
       <c r="I11" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY24</f>
-        <v>58.82352941176471</v>
+        <v>61.764705882352942</v>
       </c>
       <c r="J11" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ24</f>
-        <v>2.3885371076554876E-2</v>
+        <v>2.5079639630382622E-2</v>
       </c>
       <c r="K11" s="37">
         <f>G11*(H11/100)</f>
@@ -4401,11 +4401,11 @@
       </c>
       <c r="I12" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY25</f>
-        <v>58.82352941176471</v>
+        <v>61.764705882352942</v>
       </c>
       <c r="J12" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ25</f>
-        <v>2.3431996847346097</v>
+        <v>2.4603596689713401</v>
       </c>
       <c r="K12" s="37">
         <f t="shared" si="3"/>
@@ -5761,11 +5761,11 @@
       <c r="G45" s="1"/>
       <c r="H45" s="36">
         <f>SUM(L46:L72)</f>
-        <v>0.41038268370799202</v>
+        <v>0.33031780227039398</v>
       </c>
       <c r="I45" s="36">
         <f>AVERAGE(I46:I72)</f>
-        <v>15.555555555555548</v>
+        <v>18.253968253968246</v>
       </c>
       <c r="J45" s="36">
         <f>0.109556413087872*100</f>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="K45" s="39">
         <f t="shared" ref="K45" si="9">SUM(K46:K72)</f>
-        <v>104469.42029999998</v>
+        <v>84087.63499999998</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
@@ -5971,23 +5971,23 @@
       </c>
       <c r="H51" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX64</f>
-        <v>17.5</v>
+        <v>8.3333333333333321</v>
       </c>
       <c r="I51" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY64</f>
-        <v>18.333333333333332</v>
+        <v>26.666666666666668</v>
       </c>
       <c r="J51" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ64</f>
-        <v>0.42992471626551543</v>
+        <v>0.62534504184074968</v>
       </c>
       <c r="K51" s="37">
         <f t="shared" ref="K51:K52" si="12">G51*(H51/100)</f>
-        <v>104469.42029999998</v>
+        <v>49747.342999999979</v>
       </c>
       <c r="L51">
         <f t="shared" ref="L51:L52" si="13">H51*D51/100</f>
-        <v>0.41038268370799202</v>
+        <v>0.19542032557523428</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
@@ -6754,23 +6754,23 @@
       </c>
       <c r="H71" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX84</f>
-        <v>0</v>
+        <v>24.166666666666668</v>
       </c>
       <c r="I71" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY84</f>
-        <v>0.83333333333333337</v>
+        <v>25</v>
       </c>
       <c r="J71" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ84</f>
-        <v>3.2060701461016912E-3</v>
+        <v>9.6182104383050734E-2</v>
       </c>
       <c r="K71" s="37">
         <f t="shared" ref="K71:K72" si="21">G71*(H71/100)</f>
-        <v>0</v>
+        <v>23668.524000000001</v>
       </c>
       <c r="L71">
         <f t="shared" ref="L71:L72" si="22">H71*D71/100</f>
-        <v>0</v>
+        <v>9.2976034236949057E-2</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.3">
@@ -6798,23 +6798,23 @@
       </c>
       <c r="H72" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX85</f>
-        <v>0</v>
+        <v>24.166666666666668</v>
       </c>
       <c r="I72" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY85</f>
-        <v>0.83333333333333337</v>
+        <v>25</v>
       </c>
       <c r="J72" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ85</f>
-        <v>1.445566981317608E-3</v>
+        <v>4.3367009439528238E-2</v>
       </c>
       <c r="K72" s="37">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>10671.768</v>
       </c>
       <c r="L72">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>4.1921442458210632E-2</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
@@ -6836,11 +6836,11 @@
       <c r="G73" s="1"/>
       <c r="H73" s="36">
         <f>SUM(L74:L88)</f>
-        <v>9.4124735014892314E-3</v>
+        <v>6.388641775831061E-2</v>
       </c>
       <c r="I73" s="36">
         <f>AVERAGE(I74:I88)</f>
-        <v>42.5</v>
+        <v>51.217948717948715</v>
       </c>
       <c r="J73" s="36">
         <f>0.42784181832181*100</f>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="K73" s="39">
         <f t="shared" ref="K73" si="23">SUM(K74:K88)</f>
-        <v>2396.0944</v>
+        <v>16263.300799999999</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.3">
@@ -7125,23 +7125,23 @@
       </c>
       <c r="H81" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX94</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I81" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY94</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J81" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ94</f>
-        <v>0</v>
+        <v>4.5061470755332143E-2</v>
       </c>
       <c r="K81" s="37">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>11471.111999999999</v>
       </c>
       <c r="L81">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>4.506147075533215E-2</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.3">
@@ -7257,23 +7257,23 @@
       </c>
       <c r="H84" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX97</f>
-        <v>6.666666666666667</v>
+        <v>13.333333333333334</v>
       </c>
       <c r="I84" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY97</f>
-        <v>52.5</v>
+        <v>65.833333333333329</v>
       </c>
       <c r="J84" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ97</f>
-        <v>7.4123228824227699E-2</v>
+        <v>9.2948175827206145E-2</v>
       </c>
       <c r="K84" s="37">
         <f t="shared" si="26"/>
-        <v>2396.0944</v>
+        <v>4792.1887999999999</v>
       </c>
       <c r="L84">
         <f t="shared" si="27"/>
-        <v>9.4124735014892314E-3</v>
+        <v>1.8824947002978463E-2</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.3">
@@ -7471,11 +7471,11 @@
       <c r="G89" s="1"/>
       <c r="H89" s="36">
         <f>SUM(L90:L118)</f>
-        <v>1.1775681493797878</v>
+        <v>1.3143728103390011</v>
       </c>
       <c r="I89" s="36">
         <f>AVERAGE(I90:I118)</f>
-        <v>39.218750000000007</v>
+        <v>44.722222222222221</v>
       </c>
       <c r="J89" s="36">
         <f>0.423925829955751*100</f>
@@ -7483,7 +7483,7 @@
       </c>
       <c r="K89" s="39">
         <f>SUM(K90:K118)</f>
-        <v>299768.64719999995</v>
+        <v>334594.44320000004</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.3">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="H92" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX105</f>
-        <v>13.333333333333334</v>
+        <v>0</v>
       </c>
       <c r="I92" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY105</f>
@@ -7586,11 +7586,11 @@
       </c>
       <c r="K92" s="37">
         <f t="shared" si="28"/>
-        <v>5042.3728000000001</v>
+        <v>0</v>
       </c>
       <c r="L92">
         <f t="shared" si="29"/>
-        <v>1.9807733937623685E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.3">
@@ -7637,23 +7637,23 @@
       </c>
       <c r="H94" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX107</f>
-        <v>13.333333333333334</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="I94" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY107</f>
-        <v>73.333333333333329</v>
+        <v>80</v>
       </c>
       <c r="J94" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ107</f>
-        <v>0.14218455285300277</v>
+        <v>0.15511042129418484</v>
       </c>
       <c r="K94" s="37">
         <f t="shared" ref="K94:K98" si="30">G94*(H94/100)</f>
-        <v>6580.9695999999994</v>
+        <v>3290.4847999999997</v>
       </c>
       <c r="L94">
         <f t="shared" ref="L94:L98" si="31">H94*D94/100</f>
-        <v>2.5851736882364144E-2</v>
+        <v>1.2925868441182072E-2</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.3">
@@ -7681,23 +7681,23 @@
       </c>
       <c r="H95" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX108</f>
-        <v>13.333333333333334</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="I95" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY108</f>
-        <v>73.333333333333329</v>
+        <v>80</v>
       </c>
       <c r="J95" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ108</f>
-        <v>0.63849337216379987</v>
+        <v>0.69653822417869082</v>
       </c>
       <c r="K95" s="37">
         <f t="shared" si="30"/>
-        <v>29552.475199999997</v>
+        <v>14776.237599999999</v>
       </c>
       <c r="L95">
         <f t="shared" si="31"/>
-        <v>0.1160897040297818</v>
+        <v>5.8044852014890902E-2</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.3">
@@ -7725,23 +7725,23 @@
       </c>
       <c r="H96" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX109</f>
-        <v>6.666666666666667</v>
+        <v>13.333333333333334</v>
       </c>
       <c r="I96" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY109</f>
-        <v>45</v>
+        <v>58.333333333333336</v>
       </c>
       <c r="J96" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ109</f>
-        <v>1.2931542022105342</v>
+        <v>1.6763110028655075</v>
       </c>
       <c r="K96" s="37">
         <f t="shared" si="30"/>
-        <v>48769.319999999992</v>
+        <v>97538.639999999985</v>
       </c>
       <c r="L96">
         <f t="shared" si="31"/>
-        <v>0.19157840032748655</v>
+        <v>0.3831568006549731</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.3">
@@ -7769,23 +7769,23 @@
       </c>
       <c r="H97" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX110</f>
-        <v>6.666666666666667</v>
+        <v>13.333333333333334</v>
       </c>
       <c r="I97" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY110</f>
-        <v>45</v>
+        <v>58.333333333333336</v>
       </c>
       <c r="J97" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ110</f>
-        <v>9.8463517934812256E-2</v>
+        <v>0.12763789361920108</v>
       </c>
       <c r="K97" s="37">
         <f t="shared" si="30"/>
-        <v>3713.4</v>
+        <v>7426.8</v>
       </c>
       <c r="L97">
         <f t="shared" si="31"/>
-        <v>1.4587187842194409E-2</v>
+        <v>2.9174375684388819E-2</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.3">
@@ -7880,11 +7880,11 @@
       </c>
       <c r="I100" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY113</f>
-        <v>60</v>
+        <v>73.333333333333329</v>
       </c>
       <c r="J100" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ113</f>
-        <v>0.22804389041744338</v>
+        <v>0.27872031051020857</v>
       </c>
       <c r="K100" s="37">
         <f t="shared" ref="K100:K102" si="32">G100*(H100/100)</f>
@@ -7924,11 +7924,11 @@
       </c>
       <c r="I101" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY114</f>
-        <v>60</v>
+        <v>73.333333333333329</v>
       </c>
       <c r="J101" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ114</f>
-        <v>1.6939618018446652</v>
+        <v>2.070397757810146</v>
       </c>
       <c r="K101" s="37">
         <f t="shared" si="32"/>
@@ -7968,11 +7968,11 @@
       </c>
       <c r="I102" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY115</f>
-        <v>60</v>
+        <v>73.333333333333329</v>
       </c>
       <c r="J102" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ115</f>
-        <v>0.6227881553707405</v>
+        <v>0.76118552323090494</v>
       </c>
       <c r="K102" s="37">
         <f t="shared" si="32"/>
@@ -8027,23 +8027,23 @@
       </c>
       <c r="H104" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX117</f>
-        <v>13.333333333333334</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="I104" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY117</f>
-        <v>93.333333333333329</v>
+        <v>100</v>
       </c>
       <c r="J104" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ117</f>
-        <v>0.52508849320568507</v>
+        <v>0.5625948141489483</v>
       </c>
       <c r="K104" s="37">
         <f t="shared" ref="K104:K106" si="34">G104*(H104/100)</f>
-        <v>19095.657599999999</v>
+        <v>9547.8287999999993</v>
       </c>
       <c r="L104">
         <f t="shared" ref="L104:L106" si="35">H104*D104/100</f>
-        <v>7.501264188652644E-2</v>
+        <v>3.750632094326322E-2</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.3">
@@ -8075,11 +8075,11 @@
       </c>
       <c r="I105" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY118</f>
-        <v>53.333333333333336</v>
+        <v>60</v>
       </c>
       <c r="J105" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ118</f>
-        <v>0.11558313492178705</v>
+        <v>0.13003102678701042</v>
       </c>
       <c r="K105" s="37">
         <f t="shared" si="34"/>
@@ -8119,11 +8119,11 @@
       </c>
       <c r="I106" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY119</f>
-        <v>53.333333333333336</v>
+        <v>60</v>
       </c>
       <c r="J106" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ119</f>
-        <v>0.19726253726173842</v>
+        <v>0.22192035441945571</v>
       </c>
       <c r="K106" s="37">
         <f t="shared" si="34"/>
@@ -8182,11 +8182,11 @@
       </c>
       <c r="I108" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY121</f>
-        <v>66.666666666666657</v>
+        <v>80</v>
       </c>
       <c r="J108" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ121</f>
-        <v>0.50281683734606675</v>
+        <v>0.60338020481528021</v>
       </c>
       <c r="K108" s="37">
         <f t="shared" ref="K108:K118" si="36">G108*(H108/100)</f>
@@ -8222,23 +8222,23 @@
       </c>
       <c r="H109" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX122</f>
-        <v>6.25</v>
+        <v>18.75</v>
       </c>
       <c r="I109" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY122</f>
-        <v>56.25</v>
+        <v>75</v>
       </c>
       <c r="J109" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ122</f>
-        <v>0.26515731656921487</v>
+        <v>0.35354308875895318</v>
       </c>
       <c r="K109" s="37">
         <f t="shared" si="36"/>
-        <v>7500</v>
+        <v>22500</v>
       </c>
       <c r="L109">
         <f t="shared" si="37"/>
-        <v>2.94619240632461E-2</v>
+        <v>8.8385772189738296E-2</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.3">
@@ -8656,11 +8656,11 @@
       <c r="G119" s="1"/>
       <c r="H119" s="36">
         <f>SUM(L120:L138)</f>
-        <v>0.48230550434425734</v>
+        <v>1.4791990482474358</v>
       </c>
       <c r="I119" s="36">
         <f>AVERAGE(I120:I138)</f>
-        <v>31.53846153846154</v>
+        <v>44.358974358974358</v>
       </c>
       <c r="J119" s="36">
         <f>0.39822979986831*100</f>
@@ -8668,7 +8668,7 @@
       </c>
       <c r="K119" s="39">
         <f t="shared" ref="K119" si="38">SUM(K120:K138)</f>
-        <v>122778.51489999998</v>
+        <v>376553.576</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.3">
@@ -8715,23 +8715,23 @@
       </c>
       <c r="H121" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX134</f>
-        <v>13.333333333333334</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="I121" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY134</f>
-        <v>86.666666666666671</v>
+        <v>93.333333333333329</v>
       </c>
       <c r="J121" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ134</f>
-        <v>1.3557441491789188</v>
+        <v>1.4600321606542204</v>
       </c>
       <c r="K121" s="37">
         <f t="shared" ref="K121:K124" si="39">G121*(H121/100)</f>
-        <v>53096.334399999992</v>
+        <v>26548.167199999996</v>
       </c>
       <c r="L121">
         <f t="shared" ref="L121:L124" si="40">H121*D121/100</f>
-        <v>0.2085760229506029</v>
+        <v>0.10428801147530145</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.3">
@@ -8759,23 +8759,23 @@
       </c>
       <c r="H122" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX135</f>
-        <v>6.666666666666667</v>
+        <v>13.333333333333334</v>
       </c>
       <c r="I122" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY135</f>
-        <v>45</v>
+        <v>58.333333333333336</v>
       </c>
       <c r="J122" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ135</f>
-        <v>0.9265653664055139</v>
+        <v>1.2011032527478884</v>
       </c>
       <c r="K122" s="37">
         <f t="shared" si="39"/>
-        <v>34943.986399999994</v>
+        <v>69887.972799999989</v>
       </c>
       <c r="L122">
         <f t="shared" si="40"/>
-        <v>0.13726894317118726</v>
+        <v>0.27453788634237453</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.3">
@@ -8803,23 +8803,23 @@
       </c>
       <c r="H123" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX136</f>
-        <v>6.666666666666667</v>
+        <v>13.333333333333334</v>
       </c>
       <c r="I123" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY136</f>
-        <v>45</v>
+        <v>58.333333333333336</v>
       </c>
       <c r="J123" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ136</f>
-        <v>5.0243323523825018E-2</v>
+        <v>6.5130234197550943E-2</v>
       </c>
       <c r="K123" s="37">
         <f t="shared" si="39"/>
-        <v>1894.8495999999998</v>
+        <v>3789.6991999999996</v>
       </c>
       <c r="L123">
         <f t="shared" si="40"/>
-        <v>7.4434553368629653E-3</v>
+        <v>1.4886910673725931E-2</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.3">
@@ -8847,23 +8847,23 @@
       </c>
       <c r="H124" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX137</f>
-        <v>13.333333333333334</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="I124" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY137</f>
-        <v>93.333333333333329</v>
+        <v>100</v>
       </c>
       <c r="J124" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ137</f>
-        <v>0.3168856106300767</v>
+        <v>0.33952029710365361</v>
       </c>
       <c r="K124" s="37">
         <f t="shared" si="39"/>
-        <v>11524.0368</v>
+        <v>5762.0183999999999</v>
       </c>
       <c r="L124">
         <f t="shared" si="40"/>
-        <v>4.5269372947153823E-2</v>
+        <v>2.2634686473576911E-2</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.3">
@@ -9042,23 +9042,23 @@
       </c>
       <c r="H129" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX142</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I129" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY142</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J129" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ142</f>
-        <v>0</v>
+        <v>0.95374121721908867</v>
       </c>
       <c r="K129" s="37">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>242789.95199999999</v>
       </c>
       <c r="L129">
         <f t="shared" si="42"/>
-        <v>0</v>
+        <v>0.95374121721908867</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.3">
@@ -9105,23 +9105,23 @@
       </c>
       <c r="H131" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX144</f>
-        <v>6.666666666666667</v>
+        <v>13.333333333333334</v>
       </c>
       <c r="I131" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY144</f>
-        <v>45</v>
+        <v>58.333333333333336</v>
       </c>
       <c r="J131" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ144</f>
-        <v>0.29851684341712914</v>
+        <v>0.38696627850368592</v>
       </c>
       <c r="K131" s="37">
         <f t="shared" ref="K131" si="43">G131*(H131/100)</f>
-        <v>11258.103200000001</v>
+        <v>22516.206400000003</v>
       </c>
       <c r="L131">
         <f t="shared" ref="L131" si="44">H131*D131/100</f>
-        <v>4.4224717543278391E-2</v>
+        <v>8.8449435086556782E-2</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.3">
@@ -9168,23 +9168,23 @@
       </c>
       <c r="H133" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX146</f>
-        <v>6.666666666666667</v>
+        <v>13.333333333333334</v>
       </c>
       <c r="I133" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY146</f>
-        <v>45</v>
+        <v>58.333333333333336</v>
       </c>
       <c r="J133" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ146</f>
-        <v>6.9730540796739002E-2</v>
+        <v>9.039144177355056E-2</v>
       </c>
       <c r="K133" s="37">
         <f t="shared" ref="K133" si="46">G133*(H133/100)</f>
-        <v>2629.7799999999997</v>
+        <v>5259.5599999999995</v>
       </c>
       <c r="L133">
         <f t="shared" ref="L133" si="47">H133*D133/100</f>
-        <v>1.0330450488405777E-2</v>
+        <v>2.0660900976811555E-2</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.3">
@@ -9231,7 +9231,7 @@
       </c>
       <c r="H135" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX148</f>
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="I135" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY148</f>
@@ -9243,11 +9243,11 @@
       </c>
       <c r="K135" s="37">
         <f t="shared" ref="K135" si="48">G135*(H135/100)</f>
-        <v>7431.4245000000001</v>
+        <v>0</v>
       </c>
       <c r="L135">
         <f t="shared" ref="L135" si="49">H135*D135/100</f>
-        <v>2.9192541906766213E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.3">
@@ -9376,11 +9376,11 @@
       <c r="G139" s="1"/>
       <c r="H139" s="36">
         <f>SUM(L140:L205)</f>
-        <v>0.8661238748610246</v>
+        <v>0.52254052230672277</v>
       </c>
       <c r="I139" s="36">
         <f>AVERAGE(I140:I205)</f>
-        <v>27.04116059379216</v>
+        <v>30.871569950517308</v>
       </c>
       <c r="J139" s="36">
         <f>0.414110048029731*100</f>
@@ -9388,7 +9388,7 @@
       </c>
       <c r="K139" s="39">
         <f>SUM(K140:K205)</f>
-        <v>220485.568</v>
+        <v>133020.9768</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.3">
@@ -9571,11 +9571,11 @@
       </c>
       <c r="I144" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY157</f>
-        <v>60</v>
+        <v>73.333333333333329</v>
       </c>
       <c r="J144" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ157</f>
-        <v>0.68874719041780186</v>
+        <v>0.84180212162175783</v>
       </c>
       <c r="K144" s="37">
         <f t="shared" si="52"/>
@@ -9699,23 +9699,23 @@
       </c>
       <c r="H147" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX160</f>
-        <v>6.666666666666667</v>
+        <v>5</v>
       </c>
       <c r="I147" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY160</f>
-        <v>8.3333333333333321</v>
+        <v>13.333333333333334</v>
       </c>
       <c r="J147" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ160</f>
-        <v>3.8673921349080216E-2</v>
+        <v>6.1878274158528347E-2</v>
       </c>
       <c r="K147" s="37">
         <f t="shared" si="52"/>
-        <v>7876.0479999999998</v>
+        <v>5907.0360000000001</v>
       </c>
       <c r="L147">
         <f t="shared" si="53"/>
-        <v>3.0939137079264177E-2</v>
+        <v>2.3204352809448131E-2</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.3">
@@ -9963,23 +9963,23 @@
       </c>
       <c r="H153" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX166</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I153" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY166</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J153" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ166</f>
-        <v>0</v>
+        <v>2.1636837032047933E-2</v>
       </c>
       <c r="K153" s="37">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>5508</v>
       </c>
       <c r="L153">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>2.1636837032047933E-2</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.3">
@@ -10290,23 +10290,23 @@
       </c>
       <c r="H161" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX174</f>
-        <v>20</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="I161" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY174</f>
-        <v>93.333333333333329</v>
+        <v>100</v>
       </c>
       <c r="J161" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ174</f>
-        <v>1.9941181526255327</v>
+        <v>2.1365551635273565</v>
       </c>
       <c r="K161" s="37">
         <f t="shared" si="54"/>
-        <v>108778.8</v>
+        <v>36259.599999999999</v>
       </c>
       <c r="L161">
         <f t="shared" si="55"/>
-        <v>0.42731103270547133</v>
+        <v>0.14243701090182376</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.3">
@@ -11010,7 +11010,7 @@
       </c>
       <c r="H179" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX192</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I179" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY192</f>
@@ -11022,11 +11022,11 @@
       </c>
       <c r="K179" s="37">
         <f t="shared" si="60"/>
-        <v>64868.160000000003</v>
+        <v>0</v>
       </c>
       <c r="L179">
         <f t="shared" si="61"/>
-        <v>0.25481877387233309</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.3">
@@ -11815,23 +11815,23 @@
       </c>
       <c r="H199" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX212</f>
-        <v>0</v>
+        <v>46.666666666666664</v>
       </c>
       <c r="I199" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY212</f>
-        <v>53.333333333333336</v>
+        <v>100</v>
       </c>
       <c r="J199" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ212</f>
-        <v>2.1430958677996589E-2</v>
+        <v>4.0183047521243603E-2</v>
       </c>
       <c r="K199" s="37">
         <f t="shared" si="67"/>
-        <v>0</v>
+        <v>4773.6415999999999</v>
       </c>
       <c r="L199">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>1.8752088843247014E-2</v>
       </c>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.3">
@@ -11859,23 +11859,23 @@
       </c>
       <c r="H200" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX213</f>
-        <v>0</v>
+        <v>46.666666666666664</v>
       </c>
       <c r="I200" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY213</f>
-        <v>53.333333333333336</v>
+        <v>100</v>
       </c>
       <c r="J200" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ213</f>
-        <v>0.1868060588756571</v>
+        <v>0.35026136039185707</v>
       </c>
       <c r="K200" s="37">
         <f t="shared" si="67"/>
-        <v>0</v>
+        <v>41610.139199999998</v>
       </c>
       <c r="L200">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>0.16345530151619997</v>
       </c>
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.3">
@@ -12205,18 +12205,18 @@
       </c>
       <c r="H209" s="36">
         <f>[1]PLS_MODELO_LIVRE!$GX$222</f>
-        <v>3.128608157696243</v>
+        <v>3.8931320728235561</v>
       </c>
       <c r="I209" t="s">
         <v>398</v>
       </c>
       <c r="J209" s="36">
         <f>[1]PLS_MODELO_LIVRE!$GZ$222</f>
-        <v>61.069846671647859</v>
+        <v>64.962978744471414</v>
       </c>
       <c r="K209" s="37">
         <f>K139+K119+K89+K73+K45+K27+K13+K2+K206</f>
-        <v>796436.82239999983</v>
+        <v>991058.50939999998</v>
       </c>
     </row>
   </sheetData>

--- a/data/pls.xlsx
+++ b/data/pls.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rssla\Desktop\SPE JARDIM LUZ\01. Relatorio Obra Ramon Gerenciamento\meu-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42CC588E-DC55-4F95-B61E-3EB204065BD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21C89E5C-14D8-4EDF-92D0-52B6156BB3D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{ECBE0EBD-AF5F-4C5B-967D-6D79DF9A9648}"/>
   </bookViews>
@@ -1764,10 +1764,10 @@
             <v>2.9411764705882351</v>
           </cell>
           <cell r="GY19">
-            <v>61.764705882352942</v>
+            <v>64.705882352941174</v>
           </cell>
           <cell r="GZ19">
-            <v>0.64810679012912409</v>
+            <v>0.67896901823051092</v>
           </cell>
         </row>
         <row r="20">
@@ -1775,10 +1775,10 @@
             <v>2.9411764705882351</v>
           </cell>
           <cell r="GY20">
-            <v>61.764705882352942</v>
+            <v>64.705882352941174</v>
           </cell>
           <cell r="GZ20">
-            <v>0.51359360062972181</v>
+            <v>0.53805043875494662</v>
           </cell>
         </row>
         <row r="21">
@@ -1786,10 +1786,10 @@
             <v>2.9411764705882351</v>
           </cell>
           <cell r="GY21">
-            <v>61.764705882352942</v>
+            <v>64.705882352941174</v>
           </cell>
           <cell r="GZ21">
-            <v>0.1051642200960607</v>
+            <v>0.11017204010063503</v>
           </cell>
         </row>
         <row r="22">
@@ -1797,10 +1797,10 @@
             <v>2.9411764705882351</v>
           </cell>
           <cell r="GY22">
-            <v>61.764705882352942</v>
+            <v>64.705882352941174</v>
           </cell>
           <cell r="GZ22">
-            <v>4.7690417163343719E-2</v>
+            <v>4.9961389409217231E-2</v>
           </cell>
         </row>
         <row r="23">
@@ -1808,10 +1808,10 @@
             <v>2.9411764705882351</v>
           </cell>
           <cell r="GY23">
-            <v>61.764705882352942</v>
+            <v>64.705882352941174</v>
           </cell>
           <cell r="GZ23">
-            <v>3.9130573315547451E-2</v>
+            <v>4.0993933949621135E-2</v>
           </cell>
         </row>
         <row r="24">
@@ -1819,10 +1819,10 @@
             <v>2.9411764705882351</v>
           </cell>
           <cell r="GY24">
-            <v>61.764705882352942</v>
+            <v>64.705882352941174</v>
           </cell>
           <cell r="GZ24">
-            <v>2.5079639630382622E-2</v>
+            <v>2.6273908184210364E-2</v>
           </cell>
         </row>
         <row r="25">
@@ -1830,10 +1830,10 @@
             <v>2.9411764705882351</v>
           </cell>
           <cell r="GY25">
-            <v>61.764705882352942</v>
+            <v>64.705882352941174</v>
           </cell>
           <cell r="GZ25">
-            <v>2.4603596689713401</v>
+            <v>2.5775196532080709</v>
           </cell>
         </row>
         <row r="28">
@@ -2168,13 +2168,13 @@
         </row>
         <row r="64">
           <cell r="GX64">
-            <v>8.3333333333333321</v>
+            <v>37.5</v>
           </cell>
           <cell r="GY64">
-            <v>26.666666666666668</v>
+            <v>64.166666666666671</v>
           </cell>
           <cell r="GZ64">
-            <v>0.62534504184074968</v>
+            <v>1.5047365069293042</v>
           </cell>
         </row>
         <row r="65">
@@ -2344,24 +2344,24 @@
         </row>
         <row r="84">
           <cell r="GX84">
-            <v>24.166666666666668</v>
+            <v>39.166666666666664</v>
           </cell>
           <cell r="GY84">
-            <v>25</v>
+            <v>64.166666666666671</v>
           </cell>
           <cell r="GZ84">
-            <v>9.6182104383050734E-2</v>
+            <v>0.24686740124983023</v>
           </cell>
         </row>
         <row r="85">
           <cell r="GX85">
-            <v>24.166666666666668</v>
+            <v>39.166666666666664</v>
           </cell>
           <cell r="GY85">
-            <v>25</v>
+            <v>64.166666666666671</v>
           </cell>
           <cell r="GZ85">
-            <v>4.3367009439528238E-2</v>
+            <v>0.11130865756145582</v>
           </cell>
         </row>
         <row r="88">
@@ -2421,7 +2421,7 @@
         </row>
         <row r="94">
           <cell r="GX94">
-            <v>100</v>
+            <v>0</v>
           </cell>
           <cell r="GY94">
             <v>100</v>
@@ -2454,13 +2454,13 @@
         </row>
         <row r="97">
           <cell r="GX97">
-            <v>13.333333333333334</v>
+            <v>6.666666666666667</v>
           </cell>
           <cell r="GY97">
-            <v>65.833333333333329</v>
+            <v>72.5</v>
           </cell>
           <cell r="GZ97">
-            <v>9.2948175827206145E-2</v>
+            <v>0.10236064932869537</v>
           </cell>
         </row>
         <row r="98">
@@ -2531,46 +2531,46 @@
         </row>
         <row r="107">
           <cell r="GX107">
-            <v>6.666666666666667</v>
+            <v>13.333333333333334</v>
           </cell>
           <cell r="GY107">
-            <v>80</v>
+            <v>93.333333333333329</v>
           </cell>
           <cell r="GZ107">
-            <v>0.15511042129418484</v>
+            <v>0.18096215817654898</v>
           </cell>
         </row>
         <row r="108">
           <cell r="GX108">
-            <v>6.666666666666667</v>
+            <v>13.333333333333334</v>
           </cell>
           <cell r="GY108">
-            <v>80</v>
+            <v>93.333333333333329</v>
           </cell>
           <cell r="GZ108">
-            <v>0.69653822417869082</v>
+            <v>0.81262792820847263</v>
           </cell>
         </row>
         <row r="109">
           <cell r="GX109">
-            <v>13.333333333333334</v>
+            <v>6.666666666666667</v>
           </cell>
           <cell r="GY109">
-            <v>58.333333333333336</v>
+            <v>65</v>
           </cell>
           <cell r="GZ109">
-            <v>1.6763110028655075</v>
+            <v>1.867889403192994</v>
           </cell>
         </row>
         <row r="110">
           <cell r="GX110">
-            <v>13.333333333333334</v>
+            <v>6.666666666666667</v>
           </cell>
           <cell r="GY110">
-            <v>58.333333333333336</v>
+            <v>65</v>
           </cell>
           <cell r="GZ110">
-            <v>0.12763789361920108</v>
+            <v>0.14222508146139548</v>
           </cell>
         </row>
         <row r="111">
@@ -2589,10 +2589,10 @@
             <v>13.333333333333334</v>
           </cell>
           <cell r="GY113">
-            <v>73.333333333333329</v>
+            <v>86.666666666666671</v>
           </cell>
           <cell r="GZ113">
-            <v>0.27872031051020857</v>
+            <v>0.32939673060297381</v>
           </cell>
         </row>
         <row r="114">
@@ -2600,10 +2600,10 @@
             <v>13.333333333333334</v>
           </cell>
           <cell r="GY114">
-            <v>73.333333333333329</v>
+            <v>86.666666666666671</v>
           </cell>
           <cell r="GZ114">
-            <v>2.070397757810146</v>
+            <v>2.4468337137756277</v>
           </cell>
         </row>
         <row r="115">
@@ -2611,15 +2611,15 @@
             <v>13.333333333333334</v>
           </cell>
           <cell r="GY115">
-            <v>73.333333333333329</v>
+            <v>86.666666666666671</v>
           </cell>
           <cell r="GZ115">
-            <v>0.76118552323090494</v>
+            <v>0.89958289109106959</v>
           </cell>
         </row>
         <row r="117">
           <cell r="GX117">
-            <v>6.666666666666667</v>
+            <v>0</v>
           </cell>
           <cell r="GY117">
             <v>100</v>
@@ -2630,24 +2630,24 @@
         </row>
         <row r="118">
           <cell r="GX118">
-            <v>6.666666666666667</v>
+            <v>20</v>
           </cell>
           <cell r="GY118">
-            <v>60</v>
+            <v>80</v>
           </cell>
           <cell r="GZ118">
-            <v>0.13003102678701042</v>
+            <v>0.1733747023826806</v>
           </cell>
         </row>
         <row r="119">
           <cell r="GX119">
-            <v>6.666666666666667</v>
+            <v>20</v>
           </cell>
           <cell r="GY119">
-            <v>60</v>
+            <v>80</v>
           </cell>
           <cell r="GZ119">
-            <v>0.22192035441945571</v>
+            <v>0.29589380589260766</v>
           </cell>
         </row>
         <row r="121">
@@ -2655,21 +2655,21 @@
             <v>13.333333333333334</v>
           </cell>
           <cell r="GY121">
-            <v>80</v>
+            <v>93.333333333333329</v>
           </cell>
           <cell r="GZ121">
-            <v>0.60338020481528021</v>
+            <v>0.70394357228449356</v>
           </cell>
         </row>
         <row r="122">
           <cell r="GX122">
-            <v>18.75</v>
+            <v>12.5</v>
           </cell>
           <cell r="GY122">
-            <v>75</v>
+            <v>87.5</v>
           </cell>
           <cell r="GZ122">
-            <v>0.35354308875895318</v>
+            <v>0.41246693688544539</v>
           </cell>
         </row>
         <row r="123">
@@ -2776,37 +2776,37 @@
             <v>6.666666666666667</v>
           </cell>
           <cell r="GY134">
-            <v>93.333333333333329</v>
+            <v>100</v>
           </cell>
           <cell r="GZ134">
-            <v>1.4600321606542204</v>
+            <v>1.5643201721295217</v>
           </cell>
         </row>
         <row r="135">
           <cell r="GX135">
-            <v>13.333333333333334</v>
+            <v>6.666666666666667</v>
           </cell>
           <cell r="GY135">
-            <v>58.333333333333336</v>
+            <v>65</v>
           </cell>
           <cell r="GZ135">
-            <v>1.2011032527478884</v>
+            <v>1.3383721959190757</v>
           </cell>
         </row>
         <row r="136">
           <cell r="GX136">
-            <v>13.333333333333334</v>
+            <v>6.666666666666667</v>
           </cell>
           <cell r="GY136">
-            <v>58.333333333333336</v>
+            <v>65</v>
           </cell>
           <cell r="GZ136">
-            <v>6.5130234197550943E-2</v>
+            <v>7.2573689534413913E-2</v>
           </cell>
         </row>
         <row r="137">
           <cell r="GX137">
-            <v>6.666666666666667</v>
+            <v>0</v>
           </cell>
           <cell r="GY137">
             <v>100</v>
@@ -2850,7 +2850,7 @@
         </row>
         <row r="142">
           <cell r="GX142">
-            <v>100</v>
+            <v>0</v>
           </cell>
           <cell r="GY142">
             <v>100</v>
@@ -2861,35 +2861,35 @@
         </row>
         <row r="144">
           <cell r="GX144">
-            <v>13.333333333333334</v>
+            <v>6.666666666666667</v>
           </cell>
           <cell r="GY144">
-            <v>58.333333333333336</v>
+            <v>65</v>
           </cell>
           <cell r="GZ144">
-            <v>0.38696627850368592</v>
+            <v>0.43119099604696431</v>
           </cell>
         </row>
         <row r="146">
           <cell r="GX146">
-            <v>13.333333333333334</v>
+            <v>6.666666666666667</v>
           </cell>
           <cell r="GY146">
-            <v>58.333333333333336</v>
+            <v>65</v>
           </cell>
           <cell r="GZ146">
-            <v>9.039144177355056E-2</v>
+            <v>0.10072189226195633</v>
           </cell>
         </row>
         <row r="148">
           <cell r="GX148">
-            <v>0</v>
+            <v>25</v>
           </cell>
           <cell r="GY148">
-            <v>50</v>
+            <v>75</v>
           </cell>
           <cell r="GZ148">
-            <v>0.11677016762706485</v>
+            <v>0.17515525144059729</v>
           </cell>
         </row>
         <row r="150">
@@ -2949,13 +2949,13 @@
         </row>
         <row r="157">
           <cell r="GX157">
-            <v>13.333333333333334</v>
+            <v>20</v>
           </cell>
           <cell r="GY157">
-            <v>73.333333333333329</v>
+            <v>93.333333333333329</v>
           </cell>
           <cell r="GZ157">
-            <v>0.84180212162175783</v>
+            <v>1.071384518427692</v>
           </cell>
         </row>
         <row r="158">
@@ -2982,7 +2982,7 @@
         </row>
         <row r="160">
           <cell r="GX160">
-            <v>5</v>
+            <v>0</v>
           </cell>
           <cell r="GY160">
             <v>13.333333333333334</v>
@@ -3048,7 +3048,7 @@
         </row>
         <row r="166">
           <cell r="GX166">
-            <v>100</v>
+            <v>0</v>
           </cell>
           <cell r="GY166">
             <v>100</v>
@@ -3125,7 +3125,7 @@
         </row>
         <row r="174">
           <cell r="GX174">
-            <v>6.666666666666667</v>
+            <v>0</v>
           </cell>
           <cell r="GY174">
             <v>100</v>
@@ -3147,13 +3147,13 @@
         </row>
         <row r="176">
           <cell r="GX176">
-            <v>0</v>
+            <v>100</v>
           </cell>
           <cell r="GY176">
-            <v>0</v>
+            <v>100</v>
           </cell>
           <cell r="GZ176">
-            <v>0</v>
+            <v>0.21338305247899872</v>
           </cell>
         </row>
         <row r="178">
@@ -3477,7 +3477,7 @@
         </row>
         <row r="212">
           <cell r="GX212">
-            <v>46.666666666666664</v>
+            <v>0</v>
           </cell>
           <cell r="GY212">
             <v>100</v>
@@ -3488,7 +3488,7 @@
         </row>
         <row r="213">
           <cell r="GX213">
-            <v>46.666666666666664</v>
+            <v>0</v>
           </cell>
           <cell r="GY213">
             <v>100</v>
@@ -3565,10 +3565,10 @@
         </row>
         <row r="222">
           <cell r="GX222">
-            <v>3.8931320728235561</v>
+            <v>3.2855735822587087</v>
           </cell>
           <cell r="GZ222">
-            <v>64.962978744471414</v>
+            <v>68.24855232673012</v>
           </cell>
         </row>
       </sheetData>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="I2" s="36">
         <f>AVERAGE(I3:I12)</f>
-        <v>73.235294117647044</v>
+        <v>75.294117647058826</v>
       </c>
       <c r="J2">
         <f>0.637484224224017*100</f>
@@ -4137,11 +4137,11 @@
       </c>
       <c r="I6" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY19</f>
-        <v>61.764705882352942</v>
+        <v>64.705882352941174</v>
       </c>
       <c r="J6" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ19</f>
-        <v>0.64810679012912409</v>
+        <v>0.67896901823051092</v>
       </c>
       <c r="K6" s="37">
         <f>G6*(H6/100)</f>
@@ -4181,11 +4181,11 @@
       </c>
       <c r="I7" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY20</f>
-        <v>61.764705882352942</v>
+        <v>64.705882352941174</v>
       </c>
       <c r="J7" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ20</f>
-        <v>0.51359360062972181</v>
+        <v>0.53805043875494662</v>
       </c>
       <c r="K7" s="37">
         <f t="shared" ref="K7:K12" si="3">G7*(H7/100)</f>
@@ -4225,11 +4225,11 @@
       </c>
       <c r="I8" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY21</f>
-        <v>61.764705882352942</v>
+        <v>64.705882352941174</v>
       </c>
       <c r="J8" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ21</f>
-        <v>0.1051642200960607</v>
+        <v>0.11017204010063503</v>
       </c>
       <c r="K8" s="37">
         <f t="shared" si="3"/>
@@ -4269,11 +4269,11 @@
       </c>
       <c r="I9" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY22</f>
-        <v>61.764705882352942</v>
+        <v>64.705882352941174</v>
       </c>
       <c r="J9" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ22</f>
-        <v>4.7690417163343719E-2</v>
+        <v>4.9961389409217231E-2</v>
       </c>
       <c r="K9" s="37">
         <f t="shared" si="3"/>
@@ -4313,11 +4313,11 @@
       </c>
       <c r="I10" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY23</f>
-        <v>61.764705882352942</v>
+        <v>64.705882352941174</v>
       </c>
       <c r="J10" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ23</f>
-        <v>3.9130573315547451E-2</v>
+        <v>4.0993933949621135E-2</v>
       </c>
       <c r="K10" s="37">
         <f t="shared" si="3"/>
@@ -4357,11 +4357,11 @@
       </c>
       <c r="I11" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY24</f>
-        <v>61.764705882352942</v>
+        <v>64.705882352941174</v>
       </c>
       <c r="J11" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ24</f>
-        <v>2.5079639630382622E-2</v>
+        <v>2.6273908184210364E-2</v>
       </c>
       <c r="K11" s="37">
         <f>G11*(H11/100)</f>
@@ -4401,11 +4401,11 @@
       </c>
       <c r="I12" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY25</f>
-        <v>61.764705882352942</v>
+        <v>64.705882352941174</v>
       </c>
       <c r="J12" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ25</f>
-        <v>2.4603596689713401</v>
+        <v>2.5775196532080709</v>
       </c>
       <c r="K12" s="37">
         <f t="shared" si="3"/>
@@ -5761,11 +5761,11 @@
       <c r="G45" s="1"/>
       <c r="H45" s="36">
         <f>SUM(L46:L72)</f>
-        <v>0.33031780227039398</v>
+        <v>1.0980184100772612</v>
       </c>
       <c r="I45" s="36">
         <f>AVERAGE(I46:I72)</f>
-        <v>18.253968253968246</v>
+        <v>23.769841269841265</v>
       </c>
       <c r="J45" s="36">
         <f>0.109556413087872*100</f>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="K45" s="39">
         <f t="shared" ref="K45" si="9">SUM(K46:K72)</f>
-        <v>84087.63499999998</v>
+        <v>279517.99949999998</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
@@ -5971,23 +5971,23 @@
       </c>
       <c r="H51" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX64</f>
-        <v>8.3333333333333321</v>
+        <v>37.5</v>
       </c>
       <c r="I51" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY64</f>
-        <v>26.666666666666668</v>
+        <v>64.166666666666671</v>
       </c>
       <c r="J51" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ64</f>
-        <v>0.62534504184074968</v>
+        <v>1.5047365069293042</v>
       </c>
       <c r="K51" s="37">
         <f t="shared" ref="K51:K52" si="12">G51*(H51/100)</f>
-        <v>49747.342999999979</v>
+        <v>223863.04349999997</v>
       </c>
       <c r="L51">
         <f t="shared" ref="L51:L52" si="13">H51*D51/100</f>
-        <v>0.19542032557523428</v>
+        <v>0.87939146508855426</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
@@ -6754,23 +6754,23 @@
       </c>
       <c r="H71" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX84</f>
-        <v>24.166666666666668</v>
+        <v>39.166666666666664</v>
       </c>
       <c r="I71" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY84</f>
-        <v>25</v>
+        <v>64.166666666666671</v>
       </c>
       <c r="J71" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ84</f>
-        <v>9.6182104383050734E-2</v>
+        <v>0.24686740124983023</v>
       </c>
       <c r="K71" s="37">
         <f t="shared" ref="K71:K72" si="21">G71*(H71/100)</f>
-        <v>23668.524000000001</v>
+        <v>38359.332000000002</v>
       </c>
       <c r="L71">
         <f t="shared" ref="L71:L72" si="22">H71*D71/100</f>
-        <v>9.2976034236949057E-2</v>
+        <v>0.15068529686677948</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.3">
@@ -6798,23 +6798,23 @@
       </c>
       <c r="H72" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX85</f>
-        <v>24.166666666666668</v>
+        <v>39.166666666666664</v>
       </c>
       <c r="I72" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY85</f>
-        <v>25</v>
+        <v>64.166666666666671</v>
       </c>
       <c r="J72" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ85</f>
-        <v>4.3367009439528238E-2</v>
+        <v>0.11130865756145582</v>
       </c>
       <c r="K72" s="37">
         <f t="shared" si="21"/>
-        <v>10671.768</v>
+        <v>17295.624</v>
       </c>
       <c r="L72">
         <f t="shared" si="22"/>
-        <v>4.1921442458210632E-2</v>
+        <v>6.7941648121927573E-2</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
@@ -6836,11 +6836,11 @@
       <c r="G73" s="1"/>
       <c r="H73" s="36">
         <f>SUM(L74:L88)</f>
-        <v>6.388641775831061E-2</v>
+        <v>9.4124735014892314E-3</v>
       </c>
       <c r="I73" s="36">
         <f>AVERAGE(I74:I88)</f>
-        <v>51.217948717948715</v>
+        <v>51.730769230769234</v>
       </c>
       <c r="J73" s="36">
         <f>0.42784181832181*100</f>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="K73" s="39">
         <f t="shared" ref="K73" si="23">SUM(K74:K88)</f>
-        <v>16263.300799999999</v>
+        <v>2396.0944</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.3">
@@ -7125,7 +7125,7 @@
       </c>
       <c r="H81" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX94</f>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I81" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY94</f>
@@ -7137,11 +7137,11 @@
       </c>
       <c r="K81" s="37">
         <f t="shared" si="26"/>
-        <v>11471.111999999999</v>
+        <v>0</v>
       </c>
       <c r="L81">
         <f t="shared" si="27"/>
-        <v>4.506147075533215E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.3">
@@ -7257,23 +7257,23 @@
       </c>
       <c r="H84" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX97</f>
-        <v>13.333333333333334</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="I84" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY97</f>
-        <v>65.833333333333329</v>
+        <v>72.5</v>
       </c>
       <c r="J84" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ97</f>
-        <v>9.2948175827206145E-2</v>
+        <v>0.10236064932869537</v>
       </c>
       <c r="K84" s="37">
         <f t="shared" si="26"/>
-        <v>4792.1887999999999</v>
+        <v>2396.0944</v>
       </c>
       <c r="L84">
         <f t="shared" si="27"/>
-        <v>1.8824947002978463E-2</v>
+        <v>9.4124735014892314E-3</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.3">
@@ -7471,11 +7471,11 @@
       <c r="G89" s="1"/>
       <c r="H89" s="36">
         <f>SUM(L90:L118)</f>
-        <v>1.3143728103390011</v>
+        <v>1.1904211156647655</v>
       </c>
       <c r="I89" s="36">
         <f>AVERAGE(I90:I118)</f>
-        <v>44.722222222222221</v>
+        <v>50.798611111111093</v>
       </c>
       <c r="J89" s="36">
         <f>0.423925829955751*100</f>
@@ -7483,7 +7483,7 @@
       </c>
       <c r="K89" s="39">
         <f>SUM(K90:K118)</f>
-        <v>334594.44320000004</v>
+        <v>303040.57359999995</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.3">
@@ -7637,23 +7637,23 @@
       </c>
       <c r="H94" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX107</f>
-        <v>6.666666666666667</v>
+        <v>13.333333333333334</v>
       </c>
       <c r="I94" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY107</f>
-        <v>80</v>
+        <v>93.333333333333329</v>
       </c>
       <c r="J94" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ107</f>
-        <v>0.15511042129418484</v>
+        <v>0.18096215817654898</v>
       </c>
       <c r="K94" s="37">
         <f t="shared" ref="K94:K98" si="30">G94*(H94/100)</f>
-        <v>3290.4847999999997</v>
+        <v>6580.9695999999994</v>
       </c>
       <c r="L94">
         <f t="shared" ref="L94:L98" si="31">H94*D94/100</f>
-        <v>1.2925868441182072E-2</v>
+        <v>2.5851736882364144E-2</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.3">
@@ -7681,23 +7681,23 @@
       </c>
       <c r="H95" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX108</f>
-        <v>6.666666666666667</v>
+        <v>13.333333333333334</v>
       </c>
       <c r="I95" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY108</f>
-        <v>80</v>
+        <v>93.333333333333329</v>
       </c>
       <c r="J95" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ108</f>
-        <v>0.69653822417869082</v>
+        <v>0.81262792820847263</v>
       </c>
       <c r="K95" s="37">
         <f t="shared" si="30"/>
-        <v>14776.237599999999</v>
+        <v>29552.475199999997</v>
       </c>
       <c r="L95">
         <f t="shared" si="31"/>
-        <v>5.8044852014890902E-2</v>
+        <v>0.1160897040297818</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.3">
@@ -7725,23 +7725,23 @@
       </c>
       <c r="H96" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX109</f>
-        <v>13.333333333333334</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="I96" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY109</f>
-        <v>58.333333333333336</v>
+        <v>65</v>
       </c>
       <c r="J96" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ109</f>
-        <v>1.6763110028655075</v>
+        <v>1.867889403192994</v>
       </c>
       <c r="K96" s="37">
         <f t="shared" si="30"/>
-        <v>97538.639999999985</v>
+        <v>48769.319999999992</v>
       </c>
       <c r="L96">
         <f t="shared" si="31"/>
-        <v>0.3831568006549731</v>
+        <v>0.19157840032748655</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.3">
@@ -7769,23 +7769,23 @@
       </c>
       <c r="H97" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX110</f>
-        <v>13.333333333333334</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="I97" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY110</f>
-        <v>58.333333333333336</v>
+        <v>65</v>
       </c>
       <c r="J97" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ110</f>
-        <v>0.12763789361920108</v>
+        <v>0.14222508146139548</v>
       </c>
       <c r="K97" s="37">
         <f t="shared" si="30"/>
-        <v>7426.8</v>
+        <v>3713.4</v>
       </c>
       <c r="L97">
         <f t="shared" si="31"/>
-        <v>2.9174375684388819E-2</v>
+        <v>1.4587187842194409E-2</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.3">
@@ -7880,11 +7880,11 @@
       </c>
       <c r="I100" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY113</f>
-        <v>73.333333333333329</v>
+        <v>86.666666666666671</v>
       </c>
       <c r="J100" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ113</f>
-        <v>0.27872031051020857</v>
+        <v>0.32939673060297381</v>
       </c>
       <c r="K100" s="37">
         <f t="shared" ref="K100:K102" si="32">G100*(H100/100)</f>
@@ -7924,11 +7924,11 @@
       </c>
       <c r="I101" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY114</f>
-        <v>73.333333333333329</v>
+        <v>86.666666666666671</v>
       </c>
       <c r="J101" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ114</f>
-        <v>2.070397757810146</v>
+        <v>2.4468337137756277</v>
       </c>
       <c r="K101" s="37">
         <f t="shared" si="32"/>
@@ -7968,11 +7968,11 @@
       </c>
       <c r="I102" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY115</f>
-        <v>73.333333333333329</v>
+        <v>86.666666666666671</v>
       </c>
       <c r="J102" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ115</f>
-        <v>0.76118552323090494</v>
+        <v>0.89958289109106959</v>
       </c>
       <c r="K102" s="37">
         <f t="shared" si="32"/>
@@ -8027,7 +8027,7 @@
       </c>
       <c r="H104" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX117</f>
-        <v>6.666666666666667</v>
+        <v>0</v>
       </c>
       <c r="I104" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY117</f>
@@ -8039,11 +8039,11 @@
       </c>
       <c r="K104" s="37">
         <f t="shared" ref="K104:K106" si="34">G104*(H104/100)</f>
-        <v>9547.8287999999993</v>
+        <v>0</v>
       </c>
       <c r="L104">
         <f t="shared" ref="L104:L106" si="35">H104*D104/100</f>
-        <v>3.750632094326322E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.3">
@@ -8071,23 +8071,23 @@
       </c>
       <c r="H105" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX118</f>
-        <v>6.666666666666667</v>
+        <v>20</v>
       </c>
       <c r="I105" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY118</f>
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="J105" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ118</f>
-        <v>0.13003102678701042</v>
+        <v>0.1733747023826806</v>
       </c>
       <c r="K105" s="37">
         <f t="shared" si="34"/>
-        <v>3677.94</v>
+        <v>11033.82</v>
       </c>
       <c r="L105">
         <f t="shared" si="35"/>
-        <v>1.4447891865223382E-2</v>
+        <v>4.3343675595670143E-2</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.3">
@@ -8115,23 +8115,23 @@
       </c>
       <c r="H106" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX119</f>
-        <v>6.666666666666667</v>
+        <v>20</v>
       </c>
       <c r="I106" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY119</f>
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="J106" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ119</f>
-        <v>0.22192035441945571</v>
+        <v>0.29589380589260766</v>
       </c>
       <c r="K106" s="37">
         <f t="shared" si="34"/>
-        <v>6277.0383999999995</v>
+        <v>18831.115199999997</v>
       </c>
       <c r="L106">
         <f t="shared" si="35"/>
-        <v>2.4657817157717307E-2</v>
+        <v>7.3973451473151902E-2</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.3">
@@ -8182,11 +8182,11 @@
       </c>
       <c r="I108" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY121</f>
-        <v>80</v>
+        <v>93.333333333333329</v>
       </c>
       <c r="J108" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ121</f>
-        <v>0.60338020481528021</v>
+        <v>0.70394357228449356</v>
       </c>
       <c r="K108" s="37">
         <f t="shared" ref="K108:K118" si="36">G108*(H108/100)</f>
@@ -8222,23 +8222,23 @@
       </c>
       <c r="H109" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX122</f>
-        <v>18.75</v>
+        <v>12.5</v>
       </c>
       <c r="I109" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY122</f>
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="J109" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ122</f>
-        <v>0.35354308875895318</v>
+        <v>0.41246693688544539</v>
       </c>
       <c r="K109" s="37">
         <f t="shared" si="36"/>
-        <v>22500</v>
+        <v>15000</v>
       </c>
       <c r="L109">
         <f t="shared" si="37"/>
-        <v>8.8385772189738296E-2</v>
+        <v>5.89238481264922E-2</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.3">
@@ -8656,11 +8656,11 @@
       <c r="G119" s="1"/>
       <c r="H119" s="36">
         <f>SUM(L120:L138)</f>
-        <v>1.4791990482474358</v>
+        <v>0.36194066182856827</v>
       </c>
       <c r="I119" s="36">
         <f>AVERAGE(I120:I138)</f>
-        <v>44.358974358974358</v>
+        <v>48.846153846153847</v>
       </c>
       <c r="J119" s="36">
         <f>0.39822979986831*100</f>
@@ -8668,7 +8668,7 @@
       </c>
       <c r="K119" s="39">
         <f t="shared" ref="K119" si="38">SUM(K120:K138)</f>
-        <v>376553.576</v>
+        <v>92137.73539999999</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.3">
@@ -8719,11 +8719,11 @@
       </c>
       <c r="I121" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY134</f>
-        <v>93.333333333333329</v>
+        <v>100</v>
       </c>
       <c r="J121" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ134</f>
-        <v>1.4600321606542204</v>
+        <v>1.5643201721295217</v>
       </c>
       <c r="K121" s="37">
         <f t="shared" ref="K121:K124" si="39">G121*(H121/100)</f>
@@ -8759,23 +8759,23 @@
       </c>
       <c r="H122" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX135</f>
-        <v>13.333333333333334</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="I122" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY135</f>
-        <v>58.333333333333336</v>
+        <v>65</v>
       </c>
       <c r="J122" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ135</f>
-        <v>1.2011032527478884</v>
+        <v>1.3383721959190757</v>
       </c>
       <c r="K122" s="37">
         <f t="shared" si="39"/>
-        <v>69887.972799999989</v>
+        <v>34943.986399999994</v>
       </c>
       <c r="L122">
         <f t="shared" si="40"/>
-        <v>0.27453788634237453</v>
+        <v>0.13726894317118726</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.3">
@@ -8803,23 +8803,23 @@
       </c>
       <c r="H123" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX136</f>
-        <v>13.333333333333334</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="I123" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY136</f>
-        <v>58.333333333333336</v>
+        <v>65</v>
       </c>
       <c r="J123" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ136</f>
-        <v>6.5130234197550943E-2</v>
+        <v>7.2573689534413913E-2</v>
       </c>
       <c r="K123" s="37">
         <f t="shared" si="39"/>
-        <v>3789.6991999999996</v>
+        <v>1894.8495999999998</v>
       </c>
       <c r="L123">
         <f t="shared" si="40"/>
-        <v>1.4886910673725931E-2</v>
+        <v>7.4434553368629653E-3</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.3">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="H124" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX137</f>
-        <v>6.666666666666667</v>
+        <v>0</v>
       </c>
       <c r="I124" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY137</f>
@@ -8859,11 +8859,11 @@
       </c>
       <c r="K124" s="37">
         <f t="shared" si="39"/>
-        <v>5762.0183999999999</v>
+        <v>0</v>
       </c>
       <c r="L124">
         <f t="shared" si="40"/>
-        <v>2.2634686473576911E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.3">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="H129" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX142</f>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I129" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY142</f>
@@ -9054,11 +9054,11 @@
       </c>
       <c r="K129" s="37">
         <f t="shared" si="41"/>
-        <v>242789.95199999999</v>
+        <v>0</v>
       </c>
       <c r="L129">
         <f t="shared" si="42"/>
-        <v>0.95374121721908867</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.3">
@@ -9105,23 +9105,23 @@
       </c>
       <c r="H131" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX144</f>
-        <v>13.333333333333334</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="I131" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY144</f>
-        <v>58.333333333333336</v>
+        <v>65</v>
       </c>
       <c r="J131" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ144</f>
-        <v>0.38696627850368592</v>
+        <v>0.43119099604696431</v>
       </c>
       <c r="K131" s="37">
         <f t="shared" ref="K131" si="43">G131*(H131/100)</f>
-        <v>22516.206400000003</v>
+        <v>11258.103200000001</v>
       </c>
       <c r="L131">
         <f t="shared" ref="L131" si="44">H131*D131/100</f>
-        <v>8.8449435086556782E-2</v>
+        <v>4.4224717543278391E-2</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.3">
@@ -9168,23 +9168,23 @@
       </c>
       <c r="H133" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX146</f>
-        <v>13.333333333333334</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="I133" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY146</f>
-        <v>58.333333333333336</v>
+        <v>65</v>
       </c>
       <c r="J133" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ146</f>
-        <v>9.039144177355056E-2</v>
+        <v>0.10072189226195633</v>
       </c>
       <c r="K133" s="37">
         <f t="shared" ref="K133" si="46">G133*(H133/100)</f>
-        <v>5259.5599999999995</v>
+        <v>2629.7799999999997</v>
       </c>
       <c r="L133">
         <f t="shared" ref="L133" si="47">H133*D133/100</f>
-        <v>2.0660900976811555E-2</v>
+        <v>1.0330450488405777E-2</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.3">
@@ -9231,23 +9231,23 @@
       </c>
       <c r="H135" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX148</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I135" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY148</f>
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="J135" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ148</f>
-        <v>0.11677016762706485</v>
+        <v>0.17515525144059729</v>
       </c>
       <c r="K135" s="37">
         <f t="shared" ref="K135" si="48">G135*(H135/100)</f>
-        <v>0</v>
+        <v>14862.849</v>
       </c>
       <c r="L135">
         <f t="shared" ref="L135" si="49">H135*D135/100</f>
-        <v>0</v>
+        <v>5.8385083813532426E-2</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.3">
@@ -9376,11 +9376,11 @@
       <c r="G139" s="1"/>
       <c r="H139" s="36">
         <f>SUM(L140:L205)</f>
-        <v>0.52254052230672277</v>
+        <v>0.4429654492849327</v>
       </c>
       <c r="I139" s="36">
         <f>AVERAGE(I140:I205)</f>
-        <v>30.871569950517308</v>
+        <v>32.976833108412045</v>
       </c>
       <c r="J139" s="36">
         <f>0.414110048029731*100</f>
@@ -9388,7 +9388,7 @@
       </c>
       <c r="K139" s="39">
         <f>SUM(K140:K205)</f>
-        <v>133020.9768</v>
+        <v>112763.88</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.3">
@@ -9567,23 +9567,23 @@
       </c>
       <c r="H144" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX157</f>
-        <v>13.333333333333334</v>
+        <v>20</v>
       </c>
       <c r="I144" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY157</f>
-        <v>73.333333333333329</v>
+        <v>93.333333333333329</v>
       </c>
       <c r="J144" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ157</f>
-        <v>0.84180212162175783</v>
+        <v>1.071384518427692</v>
       </c>
       <c r="K144" s="37">
         <f t="shared" si="52"/>
-        <v>38962.559999999998</v>
+        <v>58443.840000000004</v>
       </c>
       <c r="L144">
         <f t="shared" si="53"/>
-        <v>0.153054931203956</v>
+        <v>0.22958239680593398</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.3">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="H147" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX160</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I147" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY160</f>
@@ -9711,11 +9711,11 @@
       </c>
       <c r="K147" s="37">
         <f t="shared" si="52"/>
-        <v>5907.0360000000001</v>
+        <v>0</v>
       </c>
       <c r="L147">
         <f t="shared" si="53"/>
-        <v>2.3204352809448131E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.3">
@@ -9963,7 +9963,7 @@
       </c>
       <c r="H153" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX166</f>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I153" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY166</f>
@@ -9975,11 +9975,11 @@
       </c>
       <c r="K153" s="37">
         <f t="shared" si="52"/>
-        <v>5508</v>
+        <v>0</v>
       </c>
       <c r="L153">
         <f t="shared" si="53"/>
-        <v>2.1636837032047933E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.3">
@@ -10290,7 +10290,7 @@
       </c>
       <c r="H161" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX174</f>
-        <v>6.666666666666667</v>
+        <v>0</v>
       </c>
       <c r="I161" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY174</f>
@@ -10302,11 +10302,11 @@
       </c>
       <c r="K161" s="37">
         <f t="shared" si="54"/>
-        <v>36259.599999999999</v>
+        <v>0</v>
       </c>
       <c r="L161">
         <f t="shared" si="55"/>
-        <v>0.14243701090182376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.3">
@@ -10378,23 +10378,23 @@
       </c>
       <c r="H163" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX176</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I163" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY176</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J163" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ176</f>
-        <v>0</v>
+        <v>0.21338305247899872</v>
       </c>
       <c r="K163" s="37">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>54320.039999999994</v>
       </c>
       <c r="L163">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>0.21338305247899872</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.3">
@@ -11815,7 +11815,7 @@
       </c>
       <c r="H199" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX212</f>
-        <v>46.666666666666664</v>
+        <v>0</v>
       </c>
       <c r="I199" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY212</f>
@@ -11827,11 +11827,11 @@
       </c>
       <c r="K199" s="37">
         <f t="shared" si="67"/>
-        <v>4773.6415999999999</v>
+        <v>0</v>
       </c>
       <c r="L199">
         <f t="shared" si="68"/>
-        <v>1.8752088843247014E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.3">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="H200" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX213</f>
-        <v>46.666666666666664</v>
+        <v>0</v>
       </c>
       <c r="I200" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY213</f>
@@ -11871,11 +11871,11 @@
       </c>
       <c r="K200" s="37">
         <f t="shared" si="67"/>
-        <v>41610.139199999998</v>
+        <v>0</v>
       </c>
       <c r="L200">
         <f t="shared" si="68"/>
-        <v>0.16345530151619997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.3">
@@ -12205,18 +12205,18 @@
       </c>
       <c r="H209" s="36">
         <f>[1]PLS_MODELO_LIVRE!$GX$222</f>
-        <v>3.8931320728235561</v>
+        <v>3.2855735822587087</v>
       </c>
       <c r="I209" t="s">
         <v>398</v>
       </c>
       <c r="J209" s="36">
         <f>[1]PLS_MODELO_LIVRE!$GZ$222</f>
-        <v>64.962978744471414</v>
+        <v>68.24855232673012</v>
       </c>
       <c r="K209" s="37">
         <f>K139+K119+K89+K73+K45+K27+K13+K2+K206</f>
-        <v>991058.50939999998</v>
+        <v>836394.86049999995</v>
       </c>
     </row>
   </sheetData>

--- a/data/pls.xlsx
+++ b/data/pls.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rssla\Desktop\SPE JARDIM LUZ\01. Relatorio Obra Ramon Gerenciamento\meu-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21C89E5C-14D8-4EDF-92D0-52B6156BB3D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFF86DC6-9662-4260-864D-A1EBC0B9D9E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{ECBE0EBD-AF5F-4C5B-967D-6D79DF9A9648}"/>
   </bookViews>
@@ -1764,10 +1764,10 @@
             <v>2.9411764705882351</v>
           </cell>
           <cell r="GY19">
-            <v>64.705882352941174</v>
+            <v>67.64705882352942</v>
           </cell>
           <cell r="GZ19">
-            <v>0.67896901823051092</v>
+            <v>0.70983124633189787</v>
           </cell>
         </row>
         <row r="20">
@@ -1775,10 +1775,10 @@
             <v>2.9411764705882351</v>
           </cell>
           <cell r="GY20">
-            <v>64.705882352941174</v>
+            <v>67.64705882352942</v>
           </cell>
           <cell r="GZ20">
-            <v>0.53805043875494662</v>
+            <v>0.56250727688017155</v>
           </cell>
         </row>
         <row r="21">
@@ -1786,10 +1786,10 @@
             <v>2.9411764705882351</v>
           </cell>
           <cell r="GY21">
-            <v>64.705882352941174</v>
+            <v>67.64705882352942</v>
           </cell>
           <cell r="GZ21">
-            <v>0.11017204010063503</v>
+            <v>0.11517986010520935</v>
           </cell>
         </row>
         <row r="22">
@@ -1797,10 +1797,10 @@
             <v>2.9411764705882351</v>
           </cell>
           <cell r="GY22">
-            <v>64.705882352941174</v>
+            <v>67.64705882352942</v>
           </cell>
           <cell r="GZ22">
-            <v>4.9961389409217231E-2</v>
+            <v>5.2232361655090744E-2</v>
           </cell>
         </row>
         <row r="23">
@@ -1808,10 +1808,10 @@
             <v>2.9411764705882351</v>
           </cell>
           <cell r="GY23">
-            <v>64.705882352941174</v>
+            <v>67.64705882352942</v>
           </cell>
           <cell r="GZ23">
-            <v>4.0993933949621135E-2</v>
+            <v>4.2857294583694826E-2</v>
           </cell>
         </row>
         <row r="24">
@@ -1819,10 +1819,10 @@
             <v>2.9411764705882351</v>
           </cell>
           <cell r="GY24">
-            <v>64.705882352941174</v>
+            <v>67.64705882352942</v>
           </cell>
           <cell r="GZ24">
-            <v>2.6273908184210364E-2</v>
+            <v>2.746817673803811E-2</v>
           </cell>
         </row>
         <row r="25">
@@ -1830,10 +1830,10 @@
             <v>2.9411764705882351</v>
           </cell>
           <cell r="GY25">
-            <v>64.705882352941174</v>
+            <v>67.64705882352942</v>
           </cell>
           <cell r="GZ25">
-            <v>2.5775196532080709</v>
+            <v>2.6946796374448012</v>
           </cell>
         </row>
         <row r="28">
@@ -2157,24 +2157,24 @@
         </row>
         <row r="62">
           <cell r="GX62">
-            <v>0</v>
+            <v>66.666666666666657</v>
           </cell>
           <cell r="GY62">
-            <v>0</v>
+            <v>66.666666666666657</v>
           </cell>
           <cell r="GZ62">
-            <v>0</v>
+            <v>0.21114356913756399</v>
           </cell>
         </row>
         <row r="64">
           <cell r="GX64">
-            <v>37.5</v>
+            <v>23.333333333333332</v>
           </cell>
           <cell r="GY64">
-            <v>64.166666666666671</v>
+            <v>87.5</v>
           </cell>
           <cell r="GZ64">
-            <v>1.5047365069293042</v>
+            <v>2.0519134185399599</v>
           </cell>
         </row>
         <row r="65">
@@ -2212,13 +2212,13 @@
         </row>
         <row r="69">
           <cell r="GX69">
-            <v>0</v>
+            <v>66.666666666666657</v>
           </cell>
           <cell r="GY69">
-            <v>0</v>
+            <v>66.666666666666657</v>
           </cell>
           <cell r="GZ69">
-            <v>0</v>
+            <v>0.14919361215366153</v>
           </cell>
         </row>
         <row r="70">
@@ -2344,24 +2344,24 @@
         </row>
         <row r="84">
           <cell r="GX84">
-            <v>39.166666666666664</v>
+            <v>23.333333333333332</v>
           </cell>
           <cell r="GY84">
-            <v>64.166666666666671</v>
+            <v>87.5</v>
           </cell>
           <cell r="GZ84">
-            <v>0.24686740124983023</v>
+            <v>0.33663736534067756</v>
           </cell>
         </row>
         <row r="85">
           <cell r="GX85">
-            <v>39.166666666666664</v>
+            <v>23.333333333333332</v>
           </cell>
           <cell r="GY85">
-            <v>64.166666666666671</v>
+            <v>87.5</v>
           </cell>
           <cell r="GZ85">
-            <v>0.11130865756145582</v>
+            <v>0.15178453303834882</v>
           </cell>
         </row>
         <row r="88">
@@ -2454,13 +2454,13 @@
         </row>
         <row r="97">
           <cell r="GX97">
-            <v>6.666666666666667</v>
+            <v>13.333333333333334</v>
           </cell>
           <cell r="GY97">
-            <v>72.5</v>
+            <v>85.833333333333329</v>
           </cell>
           <cell r="GZ97">
-            <v>0.10236064932869537</v>
+            <v>0.12118559633167383</v>
           </cell>
         </row>
         <row r="98">
@@ -2531,24 +2531,24 @@
         </row>
         <row r="107">
           <cell r="GX107">
-            <v>13.333333333333334</v>
+            <v>6.666666666666667</v>
           </cell>
           <cell r="GY107">
-            <v>93.333333333333329</v>
+            <v>100</v>
           </cell>
           <cell r="GZ107">
-            <v>0.18096215817654898</v>
+            <v>0.19388802661773105</v>
           </cell>
         </row>
         <row r="108">
           <cell r="GX108">
-            <v>13.333333333333334</v>
+            <v>6.666666666666667</v>
           </cell>
           <cell r="GY108">
-            <v>93.333333333333329</v>
+            <v>100</v>
           </cell>
           <cell r="GZ108">
-            <v>0.81262792820847263</v>
+            <v>0.87067278022336347</v>
           </cell>
         </row>
         <row r="109">
@@ -2556,10 +2556,10 @@
             <v>6.666666666666667</v>
           </cell>
           <cell r="GY109">
-            <v>65</v>
+            <v>71.666666666666671</v>
           </cell>
           <cell r="GZ109">
-            <v>1.867889403192994</v>
+            <v>2.0594678035204805</v>
           </cell>
         </row>
         <row r="110">
@@ -2567,10 +2567,10 @@
             <v>6.666666666666667</v>
           </cell>
           <cell r="GY110">
-            <v>65</v>
+            <v>71.666666666666671</v>
           </cell>
           <cell r="GZ110">
-            <v>0.14222508146139548</v>
+            <v>0.15681226930358988</v>
           </cell>
         </row>
         <row r="111">
@@ -2589,10 +2589,10 @@
             <v>13.333333333333334</v>
           </cell>
           <cell r="GY113">
-            <v>86.666666666666671</v>
+            <v>100</v>
           </cell>
           <cell r="GZ113">
-            <v>0.32939673060297381</v>
+            <v>0.38007315069573899</v>
           </cell>
         </row>
         <row r="114">
@@ -2600,10 +2600,10 @@
             <v>13.333333333333334</v>
           </cell>
           <cell r="GY114">
-            <v>86.666666666666671</v>
+            <v>100</v>
           </cell>
           <cell r="GZ114">
-            <v>2.4468337137756277</v>
+            <v>2.8232696697411086</v>
           </cell>
         </row>
         <row r="115">
@@ -2611,10 +2611,10 @@
             <v>13.333333333333334</v>
           </cell>
           <cell r="GY115">
-            <v>86.666666666666671</v>
+            <v>100</v>
           </cell>
           <cell r="GZ115">
-            <v>0.89958289109106959</v>
+            <v>1.0379802589512341</v>
           </cell>
         </row>
         <row r="117">
@@ -2630,35 +2630,35 @@
         </row>
         <row r="118">
           <cell r="GX118">
-            <v>20</v>
+            <v>13.333333333333334</v>
           </cell>
           <cell r="GY118">
-            <v>80</v>
+            <v>93.333333333333329</v>
           </cell>
           <cell r="GZ118">
-            <v>0.1733747023826806</v>
+            <v>0.20227048611312734</v>
           </cell>
         </row>
         <row r="119">
           <cell r="GX119">
-            <v>20</v>
+            <v>13.333333333333334</v>
           </cell>
           <cell r="GY119">
-            <v>80</v>
+            <v>93.333333333333329</v>
           </cell>
           <cell r="GZ119">
-            <v>0.29589380589260766</v>
+            <v>0.34520944020804223</v>
           </cell>
         </row>
         <row r="121">
           <cell r="GX121">
-            <v>13.333333333333334</v>
+            <v>6.666666666666667</v>
           </cell>
           <cell r="GY121">
-            <v>93.333333333333329</v>
+            <v>100</v>
           </cell>
           <cell r="GZ121">
-            <v>0.70394357228449356</v>
+            <v>0.75422525601910018</v>
           </cell>
         </row>
         <row r="122">
@@ -2666,10 +2666,10 @@
             <v>12.5</v>
           </cell>
           <cell r="GY122">
-            <v>87.5</v>
+            <v>100</v>
           </cell>
           <cell r="GZ122">
-            <v>0.41246693688544539</v>
+            <v>0.4713907850119376</v>
           </cell>
         </row>
         <row r="123">
@@ -2773,7 +2773,7 @@
         </row>
         <row r="134">
           <cell r="GX134">
-            <v>6.666666666666667</v>
+            <v>0</v>
           </cell>
           <cell r="GY134">
             <v>100</v>
@@ -2787,10 +2787,10 @@
             <v>6.666666666666667</v>
           </cell>
           <cell r="GY135">
-            <v>65</v>
+            <v>71.666666666666671</v>
           </cell>
           <cell r="GZ135">
-            <v>1.3383721959190757</v>
+            <v>1.4756411390902628</v>
           </cell>
         </row>
         <row r="136">
@@ -2798,10 +2798,10 @@
             <v>6.666666666666667</v>
           </cell>
           <cell r="GY136">
-            <v>65</v>
+            <v>71.666666666666671</v>
           </cell>
           <cell r="GZ136">
-            <v>7.2573689534413913E-2</v>
+            <v>8.0017144871276868E-2</v>
           </cell>
         </row>
         <row r="137">
@@ -2864,10 +2864,10 @@
             <v>6.666666666666667</v>
           </cell>
           <cell r="GY144">
-            <v>65</v>
+            <v>71.666666666666671</v>
           </cell>
           <cell r="GZ144">
-            <v>0.43119099604696431</v>
+            <v>0.47541571359024271</v>
           </cell>
         </row>
         <row r="146">
@@ -2875,21 +2875,21 @@
             <v>6.666666666666667</v>
           </cell>
           <cell r="GY146">
-            <v>65</v>
+            <v>71.666666666666671</v>
           </cell>
           <cell r="GZ146">
-            <v>0.10072189226195633</v>
+            <v>0.1110523427503621</v>
           </cell>
         </row>
         <row r="148">
           <cell r="GX148">
-            <v>25</v>
+            <v>12.5</v>
           </cell>
           <cell r="GY148">
-            <v>75</v>
+            <v>87.5</v>
           </cell>
           <cell r="GZ148">
-            <v>0.17515525144059729</v>
+            <v>0.2043477933473635</v>
           </cell>
         </row>
         <row r="150">
@@ -2949,7 +2949,7 @@
         </row>
         <row r="157">
           <cell r="GX157">
-            <v>20</v>
+            <v>0</v>
           </cell>
           <cell r="GY157">
             <v>93.333333333333329</v>
@@ -3092,13 +3092,13 @@
         </row>
         <row r="171">
           <cell r="GX171">
-            <v>0</v>
+            <v>100</v>
           </cell>
           <cell r="GY171">
-            <v>0</v>
+            <v>100</v>
           </cell>
           <cell r="GZ171">
-            <v>0</v>
+            <v>0.24724588091111632</v>
           </cell>
         </row>
         <row r="172">
@@ -3114,13 +3114,13 @@
         </row>
         <row r="173">
           <cell r="GX173">
-            <v>0</v>
+            <v>86.666666666666671</v>
           </cell>
           <cell r="GY173">
-            <v>13.333333333333334</v>
+            <v>100</v>
           </cell>
           <cell r="GZ173">
-            <v>0.19121527229276569</v>
+            <v>1.4341145421957426</v>
           </cell>
         </row>
         <row r="174">
@@ -3147,7 +3147,7 @@
         </row>
         <row r="176">
           <cell r="GX176">
-            <v>100</v>
+            <v>0</v>
           </cell>
           <cell r="GY176">
             <v>100</v>
@@ -3565,10 +3565,10 @@
         </row>
         <row r="222">
           <cell r="GX222">
-            <v>3.2855735822587087</v>
+            <v>3.9880686130860306</v>
           </cell>
           <cell r="GZ222">
-            <v>68.24855232673012</v>
+            <v>72.236620939816149</v>
           </cell>
         </row>
       </sheetData>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="I2" s="36">
         <f>AVERAGE(I3:I12)</f>
-        <v>75.294117647058826</v>
+        <v>77.35294117647058</v>
       </c>
       <c r="J2">
         <f>0.637484224224017*100</f>
@@ -4137,11 +4137,11 @@
       </c>
       <c r="I6" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY19</f>
-        <v>64.705882352941174</v>
+        <v>67.64705882352942</v>
       </c>
       <c r="J6" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ19</f>
-        <v>0.67896901823051092</v>
+        <v>0.70983124633189787</v>
       </c>
       <c r="K6" s="37">
         <f>G6*(H6/100)</f>
@@ -4181,11 +4181,11 @@
       </c>
       <c r="I7" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY20</f>
-        <v>64.705882352941174</v>
+        <v>67.64705882352942</v>
       </c>
       <c r="J7" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ20</f>
-        <v>0.53805043875494662</v>
+        <v>0.56250727688017155</v>
       </c>
       <c r="K7" s="37">
         <f t="shared" ref="K7:K12" si="3">G7*(H7/100)</f>
@@ -4225,11 +4225,11 @@
       </c>
       <c r="I8" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY21</f>
-        <v>64.705882352941174</v>
+        <v>67.64705882352942</v>
       </c>
       <c r="J8" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ21</f>
-        <v>0.11017204010063503</v>
+        <v>0.11517986010520935</v>
       </c>
       <c r="K8" s="37">
         <f t="shared" si="3"/>
@@ -4269,11 +4269,11 @@
       </c>
       <c r="I9" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY22</f>
-        <v>64.705882352941174</v>
+        <v>67.64705882352942</v>
       </c>
       <c r="J9" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ22</f>
-        <v>4.9961389409217231E-2</v>
+        <v>5.2232361655090744E-2</v>
       </c>
       <c r="K9" s="37">
         <f t="shared" si="3"/>
@@ -4313,11 +4313,11 @@
       </c>
       <c r="I10" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY23</f>
-        <v>64.705882352941174</v>
+        <v>67.64705882352942</v>
       </c>
       <c r="J10" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ23</f>
-        <v>4.0993933949621135E-2</v>
+        <v>4.2857294583694826E-2</v>
       </c>
       <c r="K10" s="37">
         <f t="shared" si="3"/>
@@ -4357,11 +4357,11 @@
       </c>
       <c r="I11" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY24</f>
-        <v>64.705882352941174</v>
+        <v>67.64705882352942</v>
       </c>
       <c r="J11" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ24</f>
-        <v>2.6273908184210364E-2</v>
+        <v>2.746817673803811E-2</v>
       </c>
       <c r="K11" s="37">
         <f>G11*(H11/100)</f>
@@ -4401,11 +4401,11 @@
       </c>
       <c r="I12" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY25</f>
-        <v>64.705882352941174</v>
+        <v>67.64705882352942</v>
       </c>
       <c r="J12" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ25</f>
-        <v>2.5775196532080709</v>
+        <v>2.6946796374448012</v>
       </c>
       <c r="K12" s="37">
         <f t="shared" si="3"/>
@@ -5761,11 +5761,11 @@
       <c r="G45" s="1"/>
       <c r="H45" s="36">
         <f>SUM(L46:L72)</f>
-        <v>1.0980184100772612</v>
+        <v>1.0377599324696218</v>
       </c>
       <c r="I45" s="36">
         <f>AVERAGE(I46:I72)</f>
-        <v>23.769841269841265</v>
+        <v>33.452380952380963</v>
       </c>
       <c r="J45" s="36">
         <f>0.109556413087872*100</f>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="K45" s="39">
         <f t="shared" ref="K45" si="9">SUM(K46:K72)</f>
-        <v>279517.99949999998</v>
+        <v>264178.24839999987</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
@@ -5908,23 +5908,23 @@
       </c>
       <c r="H49" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX62</f>
-        <v>0</v>
+        <v>66.666666666666657</v>
       </c>
       <c r="I49" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY62</f>
-        <v>0</v>
+        <v>66.666666666666657</v>
       </c>
       <c r="J49" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ62</f>
-        <v>0</v>
+        <v>0.21114356913756399</v>
       </c>
       <c r="K49" s="37">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>53749.943999999974</v>
       </c>
       <c r="L49">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>0.21114356913756399</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
@@ -5971,23 +5971,23 @@
       </c>
       <c r="H51" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX64</f>
-        <v>37.5</v>
+        <v>23.333333333333332</v>
       </c>
       <c r="I51" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY64</f>
-        <v>64.166666666666671</v>
+        <v>87.5</v>
       </c>
       <c r="J51" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ64</f>
-        <v>1.5047365069293042</v>
+        <v>2.0519134185399599</v>
       </c>
       <c r="K51" s="37">
         <f t="shared" ref="K51:K52" si="12">G51*(H51/100)</f>
-        <v>223863.04349999997</v>
+        <v>139292.56039999996</v>
       </c>
       <c r="L51">
         <f t="shared" ref="L51:L52" si="13">H51*D51/100</f>
-        <v>0.87939146508855426</v>
+        <v>0.54717691161065607</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
@@ -6166,23 +6166,23 @@
       </c>
       <c r="H56" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX69</f>
-        <v>0</v>
+        <v>66.666666666666657</v>
       </c>
       <c r="I56" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY69</f>
-        <v>0</v>
+        <v>66.666666666666657</v>
       </c>
       <c r="J56" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ69</f>
-        <v>0</v>
+        <v>0.14919361215366153</v>
       </c>
       <c r="K56" s="37">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>37979.599999999991</v>
       </c>
       <c r="L56">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>0.14919361215366153</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
@@ -6754,23 +6754,23 @@
       </c>
       <c r="H71" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX84</f>
-        <v>39.166666666666664</v>
+        <v>23.333333333333332</v>
       </c>
       <c r="I71" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY84</f>
-        <v>64.166666666666671</v>
+        <v>87.5</v>
       </c>
       <c r="J71" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ84</f>
-        <v>0.24686740124983023</v>
+        <v>0.33663736534067756</v>
       </c>
       <c r="K71" s="37">
         <f t="shared" ref="K71:K72" si="21">G71*(H71/100)</f>
-        <v>38359.332000000002</v>
+        <v>22852.367999999999</v>
       </c>
       <c r="L71">
         <f t="shared" ref="L71:L72" si="22">H71*D71/100</f>
-        <v>0.15068529686677948</v>
+        <v>8.9769964090847351E-2</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.3">
@@ -6798,23 +6798,23 @@
       </c>
       <c r="H72" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX85</f>
-        <v>39.166666666666664</v>
+        <v>23.333333333333332</v>
       </c>
       <c r="I72" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY85</f>
-        <v>64.166666666666671</v>
+        <v>87.5</v>
       </c>
       <c r="J72" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ85</f>
-        <v>0.11130865756145582</v>
+        <v>0.15178453303834882</v>
       </c>
       <c r="K72" s="37">
         <f t="shared" si="21"/>
-        <v>17295.624</v>
+        <v>10303.776</v>
       </c>
       <c r="L72">
         <f t="shared" si="22"/>
-        <v>6.7941648121927573E-2</v>
+        <v>4.047587547689302E-2</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
@@ -6836,11 +6836,11 @@
       <c r="G73" s="1"/>
       <c r="H73" s="36">
         <f>SUM(L74:L88)</f>
-        <v>9.4124735014892314E-3</v>
+        <v>1.8824947002978463E-2</v>
       </c>
       <c r="I73" s="36">
         <f>AVERAGE(I74:I88)</f>
-        <v>51.730769230769234</v>
+        <v>52.756410256410248</v>
       </c>
       <c r="J73" s="36">
         <f>0.42784181832181*100</f>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="K73" s="39">
         <f t="shared" ref="K73" si="23">SUM(K74:K88)</f>
-        <v>2396.0944</v>
+        <v>4792.1887999999999</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.3">
@@ -7257,23 +7257,23 @@
       </c>
       <c r="H84" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX97</f>
-        <v>6.666666666666667</v>
+        <v>13.333333333333334</v>
       </c>
       <c r="I84" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY97</f>
-        <v>72.5</v>
+        <v>85.833333333333329</v>
       </c>
       <c r="J84" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ97</f>
-        <v>0.10236064932869537</v>
+        <v>0.12118559633167383</v>
       </c>
       <c r="K84" s="37">
         <f t="shared" si="26"/>
-        <v>2396.0944</v>
+        <v>4792.1887999999999</v>
       </c>
       <c r="L84">
         <f t="shared" si="27"/>
-        <v>9.4124735014892314E-3</v>
+        <v>1.8824947002978463E-2</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.3">
@@ -7471,11 +7471,11 @@
       <c r="G89" s="1"/>
       <c r="H89" s="36">
         <f>SUM(L90:L118)</f>
-        <v>1.1904211156647655</v>
+        <v>1.0300630024511452</v>
       </c>
       <c r="I89" s="36">
         <f>AVERAGE(I90:I118)</f>
-        <v>50.798611111111093</v>
+        <v>55.486111111111107</v>
       </c>
       <c r="J89" s="36">
         <f>0.423925829955751*100</f>
@@ -7483,7 +7483,7 @@
       </c>
       <c r="K89" s="39">
         <f>SUM(K90:K118)</f>
-        <v>303040.57359999995</v>
+        <v>262218.87280000001</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.3">
@@ -7637,23 +7637,23 @@
       </c>
       <c r="H94" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX107</f>
-        <v>13.333333333333334</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="I94" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY107</f>
-        <v>93.333333333333329</v>
+        <v>100</v>
       </c>
       <c r="J94" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ107</f>
-        <v>0.18096215817654898</v>
+        <v>0.19388802661773105</v>
       </c>
       <c r="K94" s="37">
         <f t="shared" ref="K94:K98" si="30">G94*(H94/100)</f>
-        <v>6580.9695999999994</v>
+        <v>3290.4847999999997</v>
       </c>
       <c r="L94">
         <f t="shared" ref="L94:L98" si="31">H94*D94/100</f>
-        <v>2.5851736882364144E-2</v>
+        <v>1.2925868441182072E-2</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.3">
@@ -7681,23 +7681,23 @@
       </c>
       <c r="H95" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX108</f>
-        <v>13.333333333333334</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="I95" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY108</f>
-        <v>93.333333333333329</v>
+        <v>100</v>
       </c>
       <c r="J95" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ108</f>
-        <v>0.81262792820847263</v>
+        <v>0.87067278022336347</v>
       </c>
       <c r="K95" s="37">
         <f t="shared" si="30"/>
-        <v>29552.475199999997</v>
+        <v>14776.237599999999</v>
       </c>
       <c r="L95">
         <f t="shared" si="31"/>
-        <v>0.1160897040297818</v>
+        <v>5.8044852014890902E-2</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.3">
@@ -7729,11 +7729,11 @@
       </c>
       <c r="I96" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY109</f>
-        <v>65</v>
+        <v>71.666666666666671</v>
       </c>
       <c r="J96" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ109</f>
-        <v>1.867889403192994</v>
+        <v>2.0594678035204805</v>
       </c>
       <c r="K96" s="37">
         <f t="shared" si="30"/>
@@ -7773,11 +7773,11 @@
       </c>
       <c r="I97" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY110</f>
-        <v>65</v>
+        <v>71.666666666666671</v>
       </c>
       <c r="J97" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ110</f>
-        <v>0.14222508146139548</v>
+        <v>0.15681226930358988</v>
       </c>
       <c r="K97" s="37">
         <f t="shared" si="30"/>
@@ -7880,11 +7880,11 @@
       </c>
       <c r="I100" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY113</f>
-        <v>86.666666666666671</v>
+        <v>100</v>
       </c>
       <c r="J100" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ113</f>
-        <v>0.32939673060297381</v>
+        <v>0.38007315069573899</v>
       </c>
       <c r="K100" s="37">
         <f t="shared" ref="K100:K102" si="32">G100*(H100/100)</f>
@@ -7924,11 +7924,11 @@
       </c>
       <c r="I101" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY114</f>
-        <v>86.666666666666671</v>
+        <v>100</v>
       </c>
       <c r="J101" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ114</f>
-        <v>2.4468337137756277</v>
+        <v>2.8232696697411086</v>
       </c>
       <c r="K101" s="37">
         <f t="shared" si="32"/>
@@ -7968,11 +7968,11 @@
       </c>
       <c r="I102" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY115</f>
-        <v>86.666666666666671</v>
+        <v>100</v>
       </c>
       <c r="J102" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ115</f>
-        <v>0.89958289109106959</v>
+        <v>1.0379802589512341</v>
       </c>
       <c r="K102" s="37">
         <f t="shared" si="32"/>
@@ -8071,23 +8071,23 @@
       </c>
       <c r="H105" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX118</f>
-        <v>20</v>
+        <v>13.333333333333334</v>
       </c>
       <c r="I105" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY118</f>
-        <v>80</v>
+        <v>93.333333333333329</v>
       </c>
       <c r="J105" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ118</f>
-        <v>0.1733747023826806</v>
+        <v>0.20227048611312734</v>
       </c>
       <c r="K105" s="37">
         <f t="shared" si="34"/>
-        <v>11033.82</v>
+        <v>7355.88</v>
       </c>
       <c r="L105">
         <f t="shared" si="35"/>
-        <v>4.3343675595670143E-2</v>
+        <v>2.8895783730446763E-2</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.3">
@@ -8115,23 +8115,23 @@
       </c>
       <c r="H106" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX119</f>
-        <v>20</v>
+        <v>13.333333333333334</v>
       </c>
       <c r="I106" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY119</f>
-        <v>80</v>
+        <v>93.333333333333329</v>
       </c>
       <c r="J106" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ119</f>
-        <v>0.29589380589260766</v>
+        <v>0.34520944020804223</v>
       </c>
       <c r="K106" s="37">
         <f t="shared" si="34"/>
-        <v>18831.115199999997</v>
+        <v>12554.076799999999</v>
       </c>
       <c r="L106">
         <f t="shared" si="35"/>
-        <v>7.3973451473151902E-2</v>
+        <v>4.9315634315434613E-2</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.3">
@@ -8178,23 +8178,23 @@
       </c>
       <c r="H108" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX121</f>
-        <v>13.333333333333334</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="I108" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY121</f>
-        <v>93.333333333333329</v>
+        <v>100</v>
       </c>
       <c r="J108" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ121</f>
-        <v>0.70394357228449356</v>
+        <v>0.75422525601910018</v>
       </c>
       <c r="K108" s="37">
         <f t="shared" ref="K108:K118" si="36">G108*(H108/100)</f>
-        <v>25600</v>
+        <v>12800</v>
       </c>
       <c r="L108">
         <f t="shared" ref="L108:L118" si="37">H108*D108/100</f>
-        <v>0.10056336746921335</v>
+        <v>5.0281683734606675E-2</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.3">
@@ -8226,11 +8226,11 @@
       </c>
       <c r="I109" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY122</f>
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="J109" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ122</f>
-        <v>0.41246693688544539</v>
+        <v>0.4713907850119376</v>
       </c>
       <c r="K109" s="37">
         <f t="shared" si="36"/>
@@ -8656,11 +8656,11 @@
       <c r="G119" s="1"/>
       <c r="H119" s="36">
         <f>SUM(L120:L138)</f>
-        <v>0.36194066182856827</v>
+        <v>0.22846010844650061</v>
       </c>
       <c r="I119" s="36">
         <f>AVERAGE(I120:I138)</f>
-        <v>48.846153846153847</v>
+        <v>51.858974358974358</v>
       </c>
       <c r="J119" s="36">
         <f>0.39822979986831*100</f>
@@ -8668,7 +8668,7 @@
       </c>
       <c r="K119" s="39">
         <f t="shared" ref="K119" si="38">SUM(K120:K138)</f>
-        <v>92137.73539999999</v>
+        <v>58158.143699999993</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.3">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="H121" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX134</f>
-        <v>6.666666666666667</v>
+        <v>0</v>
       </c>
       <c r="I121" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY134</f>
@@ -8727,11 +8727,11 @@
       </c>
       <c r="K121" s="37">
         <f t="shared" ref="K121:K124" si="39">G121*(H121/100)</f>
-        <v>26548.167199999996</v>
+        <v>0</v>
       </c>
       <c r="L121">
         <f t="shared" ref="L121:L124" si="40">H121*D121/100</f>
-        <v>0.10428801147530145</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.3">
@@ -8763,11 +8763,11 @@
       </c>
       <c r="I122" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY135</f>
-        <v>65</v>
+        <v>71.666666666666671</v>
       </c>
       <c r="J122" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ135</f>
-        <v>1.3383721959190757</v>
+        <v>1.4756411390902628</v>
       </c>
       <c r="K122" s="37">
         <f t="shared" si="39"/>
@@ -8807,11 +8807,11 @@
       </c>
       <c r="I123" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY136</f>
-        <v>65</v>
+        <v>71.666666666666671</v>
       </c>
       <c r="J123" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ136</f>
-        <v>7.2573689534413913E-2</v>
+        <v>8.0017144871276868E-2</v>
       </c>
       <c r="K123" s="37">
         <f t="shared" si="39"/>
@@ -9109,11 +9109,11 @@
       </c>
       <c r="I131" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY144</f>
-        <v>65</v>
+        <v>71.666666666666671</v>
       </c>
       <c r="J131" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ144</f>
-        <v>0.43119099604696431</v>
+        <v>0.47541571359024271</v>
       </c>
       <c r="K131" s="37">
         <f t="shared" ref="K131" si="43">G131*(H131/100)</f>
@@ -9172,11 +9172,11 @@
       </c>
       <c r="I133" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY146</f>
-        <v>65</v>
+        <v>71.666666666666671</v>
       </c>
       <c r="J133" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ146</f>
-        <v>0.10072189226195633</v>
+        <v>0.1110523427503621</v>
       </c>
       <c r="K133" s="37">
         <f t="shared" ref="K133" si="46">G133*(H133/100)</f>
@@ -9231,23 +9231,23 @@
       </c>
       <c r="H135" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX148</f>
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="I135" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY148</f>
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="J135" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ148</f>
-        <v>0.17515525144059729</v>
+        <v>0.2043477933473635</v>
       </c>
       <c r="K135" s="37">
         <f t="shared" ref="K135" si="48">G135*(H135/100)</f>
-        <v>14862.849</v>
+        <v>7431.4245000000001</v>
       </c>
       <c r="L135">
         <f t="shared" ref="L135" si="49">H135*D135/100</f>
-        <v>5.8385083813532426E-2</v>
+        <v>2.9192541906766213E-2</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.3">
@@ -9376,11 +9376,11 @@
       <c r="G139" s="1"/>
       <c r="H139" s="36">
         <f>SUM(L140:L205)</f>
-        <v>0.4429654492849327</v>
+        <v>1.4901451508140933</v>
       </c>
       <c r="I139" s="36">
         <f>AVERAGE(I140:I205)</f>
-        <v>32.976833108412045</v>
+        <v>36.251686909581636</v>
       </c>
       <c r="J139" s="36">
         <f>0.414110048029731*100</f>
@@ -9388,7 +9388,7 @@
       </c>
       <c r="K139" s="39">
         <f>SUM(K140:K205)</f>
-        <v>112763.88</v>
+        <v>379340.07999999996</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.3">
@@ -9567,7 +9567,7 @@
       </c>
       <c r="H144" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX157</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I144" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY157</f>
@@ -9579,11 +9579,11 @@
       </c>
       <c r="K144" s="37">
         <f t="shared" si="52"/>
-        <v>58443.840000000004</v>
+        <v>0</v>
       </c>
       <c r="L144">
         <f t="shared" si="53"/>
-        <v>0.22958239680593398</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.3">
@@ -10158,23 +10158,23 @@
       </c>
       <c r="H158" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX171</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I158" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY171</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J158" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ171</f>
-        <v>0</v>
+        <v>0.24724588091111632</v>
       </c>
       <c r="K158" s="37">
         <f t="shared" ref="K158:K163" si="54">G158*(H158/100)</f>
-        <v>0</v>
+        <v>62940.360000000008</v>
       </c>
       <c r="L158">
         <f t="shared" ref="L158:L163" si="55">H158*D158/100</f>
-        <v>0</v>
+        <v>0.24724588091111632</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.3">
@@ -10246,23 +10246,23 @@
       </c>
       <c r="H160" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX173</f>
-        <v>0</v>
+        <v>86.666666666666671</v>
       </c>
       <c r="I160" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY173</f>
-        <v>13.333333333333334</v>
+        <v>100</v>
       </c>
       <c r="J160" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ173</f>
-        <v>0.19121527229276569</v>
+        <v>1.4341145421957426</v>
       </c>
       <c r="K160" s="37">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>316399.71999999997</v>
       </c>
       <c r="L160">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>1.2428992699029771</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.3">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="H163" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX176</f>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I163" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY176</f>
@@ -10390,11 +10390,11 @@
       </c>
       <c r="K163" s="37">
         <f t="shared" si="54"/>
-        <v>54320.039999999994</v>
+        <v>0</v>
       </c>
       <c r="L163">
         <f t="shared" si="55"/>
-        <v>0.21338305247899872</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.3">
@@ -12205,18 +12205,18 @@
       </c>
       <c r="H209" s="36">
         <f>[1]PLS_MODELO_LIVRE!$GX$222</f>
-        <v>3.2855735822587087</v>
+        <v>3.9880686130860306</v>
       </c>
       <c r="I209" t="s">
         <v>398</v>
       </c>
       <c r="J209" s="36">
         <f>[1]PLS_MODELO_LIVRE!$GZ$222</f>
-        <v>68.24855232673012</v>
+        <v>72.236620939816149</v>
       </c>
       <c r="K209" s="37">
         <f>K139+K119+K89+K73+K45+K27+K13+K2+K206</f>
-        <v>836394.86049999995</v>
+        <v>1015226.1112999998</v>
       </c>
     </row>
   </sheetData>

--- a/data/pls.xlsx
+++ b/data/pls.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30425"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -1764,10 +1764,10 @@
             <v>2.9411764705882351</v>
           </cell>
           <cell r="GY19">
-            <v>67.64705882352942</v>
+            <v>70.588235294117652</v>
           </cell>
           <cell r="GZ19">
-            <v>0.70983124633189787</v>
+            <v>0.7406934744332847</v>
           </cell>
         </row>
         <row r="20">
@@ -1775,10 +1775,10 @@
             <v>2.9411764705882351</v>
           </cell>
           <cell r="GY20">
-            <v>67.64705882352942</v>
+            <v>70.588235294117652</v>
           </cell>
           <cell r="GZ20">
-            <v>0.56250727688017155</v>
+            <v>0.58696411500539636</v>
           </cell>
         </row>
         <row r="21">
@@ -1786,10 +1786,10 @@
             <v>2.9411764705882351</v>
           </cell>
           <cell r="GY21">
-            <v>67.64705882352942</v>
+            <v>70.588235294117652</v>
           </cell>
           <cell r="GZ21">
-            <v>0.11517986010520935</v>
+            <v>0.12018768010978367</v>
           </cell>
         </row>
         <row r="22">
@@ -1797,10 +1797,10 @@
             <v>2.9411764705882351</v>
           </cell>
           <cell r="GY22">
-            <v>67.64705882352942</v>
+            <v>70.588235294117652</v>
           </cell>
           <cell r="GZ22">
-            <v>5.2232361655090744E-2</v>
+            <v>5.4503333900964256E-2</v>
           </cell>
         </row>
         <row r="23">
@@ -1808,10 +1808,10 @@
             <v>2.9411764705882351</v>
           </cell>
           <cell r="GY23">
-            <v>67.64705882352942</v>
+            <v>70.588235294117652</v>
           </cell>
           <cell r="GZ23">
-            <v>4.2857294583694826E-2</v>
+            <v>4.4720655217768517E-2</v>
           </cell>
         </row>
         <row r="24">
@@ -1819,10 +1819,10 @@
             <v>2.9411764705882351</v>
           </cell>
           <cell r="GY24">
-            <v>67.64705882352942</v>
+            <v>70.588235294117652</v>
           </cell>
           <cell r="GZ24">
-            <v>2.746817673803811E-2</v>
+            <v>2.8662445291865853E-2</v>
           </cell>
         </row>
         <row r="25">
@@ -1830,10 +1830,10 @@
             <v>2.9411764705882351</v>
           </cell>
           <cell r="GY25">
-            <v>67.64705882352942</v>
+            <v>70.588235294117652</v>
           </cell>
           <cell r="GZ25">
-            <v>2.6946796374448012</v>
+            <v>2.8118396216815316</v>
           </cell>
         </row>
         <row r="28">
@@ -2157,7 +2157,7 @@
         </row>
         <row r="62">
           <cell r="GX62">
-            <v>66.666666666666657</v>
+            <v>0</v>
           </cell>
           <cell r="GY62">
             <v>66.666666666666657</v>
@@ -2168,7 +2168,7 @@
         </row>
         <row r="64">
           <cell r="GX64">
-            <v>23.333333333333332</v>
+            <v>0</v>
           </cell>
           <cell r="GY64">
             <v>87.5</v>
@@ -2212,24 +2212,24 @@
         </row>
         <row r="69">
           <cell r="GX69">
-            <v>66.666666666666657</v>
+            <v>33.333333333333329</v>
           </cell>
           <cell r="GY69">
-            <v>66.666666666666657</v>
+            <v>100</v>
           </cell>
           <cell r="GZ69">
-            <v>0.14919361215366153</v>
+            <v>0.22379041823049231</v>
           </cell>
         </row>
         <row r="70">
           <cell r="GX70">
-            <v>0</v>
+            <v>100</v>
           </cell>
           <cell r="GY70">
-            <v>0</v>
+            <v>100</v>
           </cell>
           <cell r="GZ70">
-            <v>0</v>
+            <v>9.9670867582924098E-3</v>
           </cell>
         </row>
         <row r="71">
@@ -2344,7 +2344,7 @@
         </row>
         <row r="84">
           <cell r="GX84">
-            <v>23.333333333333332</v>
+            <v>0</v>
           </cell>
           <cell r="GY84">
             <v>87.5</v>
@@ -2355,7 +2355,7 @@
         </row>
         <row r="85">
           <cell r="GX85">
-            <v>23.333333333333332</v>
+            <v>0</v>
           </cell>
           <cell r="GY85">
             <v>87.5</v>
@@ -2457,10 +2457,10 @@
             <v>13.333333333333334</v>
           </cell>
           <cell r="GY97">
-            <v>85.833333333333329</v>
+            <v>99.166666666666671</v>
           </cell>
           <cell r="GZ97">
-            <v>0.12118559633167383</v>
+            <v>0.14001054333465232</v>
           </cell>
         </row>
         <row r="98">
@@ -2531,7 +2531,7 @@
         </row>
         <row r="107">
           <cell r="GX107">
-            <v>6.666666666666667</v>
+            <v>0</v>
           </cell>
           <cell r="GY107">
             <v>100</v>
@@ -2542,7 +2542,7 @@
         </row>
         <row r="108">
           <cell r="GX108">
-            <v>6.666666666666667</v>
+            <v>0</v>
           </cell>
           <cell r="GY108">
             <v>100</v>
@@ -2553,24 +2553,24 @@
         </row>
         <row r="109">
           <cell r="GX109">
-            <v>6.666666666666667</v>
+            <v>10</v>
           </cell>
           <cell r="GY109">
-            <v>71.666666666666671</v>
+            <v>81.666666666666671</v>
           </cell>
           <cell r="GZ109">
-            <v>2.0594678035204805</v>
+            <v>2.3468354040117103</v>
           </cell>
         </row>
         <row r="110">
           <cell r="GX110">
-            <v>6.666666666666667</v>
+            <v>10</v>
           </cell>
           <cell r="GY110">
-            <v>71.666666666666671</v>
+            <v>81.666666666666671</v>
           </cell>
           <cell r="GZ110">
-            <v>0.15681226930358988</v>
+            <v>0.17869305106688149</v>
           </cell>
         </row>
         <row r="111">
@@ -2586,7 +2586,7 @@
         </row>
         <row r="113">
           <cell r="GX113">
-            <v>13.333333333333334</v>
+            <v>0</v>
           </cell>
           <cell r="GY113">
             <v>100</v>
@@ -2597,7 +2597,7 @@
         </row>
         <row r="114">
           <cell r="GX114">
-            <v>13.333333333333334</v>
+            <v>0</v>
           </cell>
           <cell r="GY114">
             <v>100</v>
@@ -2608,7 +2608,7 @@
         </row>
         <row r="115">
           <cell r="GX115">
-            <v>13.333333333333334</v>
+            <v>0</v>
           </cell>
           <cell r="GY115">
             <v>100</v>
@@ -2630,29 +2630,29 @@
         </row>
         <row r="118">
           <cell r="GX118">
-            <v>13.333333333333334</v>
+            <v>6.666666666666667</v>
           </cell>
           <cell r="GY118">
-            <v>93.333333333333329</v>
+            <v>100</v>
           </cell>
           <cell r="GZ118">
-            <v>0.20227048611312734</v>
+            <v>0.21671837797835072</v>
           </cell>
         </row>
         <row r="119">
           <cell r="GX119">
-            <v>13.333333333333334</v>
+            <v>6.666666666666667</v>
           </cell>
           <cell r="GY119">
-            <v>93.333333333333329</v>
+            <v>100</v>
           </cell>
           <cell r="GZ119">
-            <v>0.34520944020804223</v>
+            <v>0.36986725736575954</v>
           </cell>
         </row>
         <row r="121">
           <cell r="GX121">
-            <v>6.666666666666667</v>
+            <v>0</v>
           </cell>
           <cell r="GY121">
             <v>100</v>
@@ -2663,7 +2663,7 @@
         </row>
         <row r="122">
           <cell r="GX122">
-            <v>12.5</v>
+            <v>0</v>
           </cell>
           <cell r="GY122">
             <v>100</v>
@@ -2718,13 +2718,13 @@
         </row>
         <row r="127">
           <cell r="GX127">
-            <v>0</v>
+            <v>26.666666666666668</v>
           </cell>
           <cell r="GY127">
-            <v>0</v>
+            <v>26.666666666666668</v>
           </cell>
           <cell r="GZ127">
-            <v>0</v>
+            <v>0.63829593170480026</v>
           </cell>
         </row>
         <row r="128">
@@ -2751,13 +2751,13 @@
         </row>
         <row r="130">
           <cell r="GX130">
-            <v>0</v>
+            <v>26.666666666666668</v>
           </cell>
           <cell r="GY130">
-            <v>0</v>
+            <v>26.666666666666668</v>
           </cell>
           <cell r="GZ130">
-            <v>0</v>
+            <v>0.63829593170480026</v>
           </cell>
         </row>
         <row r="131">
@@ -2784,24 +2784,24 @@
         </row>
         <row r="135">
           <cell r="GX135">
-            <v>6.666666666666667</v>
+            <v>10</v>
           </cell>
           <cell r="GY135">
-            <v>71.666666666666671</v>
+            <v>81.666666666666671</v>
           </cell>
           <cell r="GZ135">
-            <v>1.4756411390902628</v>
+            <v>1.6815445538470437</v>
           </cell>
         </row>
         <row r="136">
           <cell r="GX136">
-            <v>6.666666666666667</v>
+            <v>10</v>
           </cell>
           <cell r="GY136">
-            <v>71.666666666666671</v>
+            <v>81.666666666666671</v>
           </cell>
           <cell r="GZ136">
-            <v>8.0017144871276868E-2</v>
+            <v>9.1182327876571323E-2</v>
           </cell>
         </row>
         <row r="137">
@@ -2861,13 +2861,13 @@
         </row>
         <row r="144">
           <cell r="GX144">
-            <v>6.666666666666667</v>
+            <v>10</v>
           </cell>
           <cell r="GY144">
-            <v>71.666666666666671</v>
+            <v>81.666666666666671</v>
           </cell>
           <cell r="GZ144">
-            <v>0.47541571359024271</v>
+            <v>0.54175278990516029</v>
           </cell>
         </row>
         <row r="146">
@@ -2875,15 +2875,15 @@
             <v>6.666666666666667</v>
           </cell>
           <cell r="GY146">
-            <v>71.666666666666671</v>
+            <v>78.333333333333329</v>
           </cell>
           <cell r="GZ146">
-            <v>0.1110523427503621</v>
+            <v>0.12138279323876788</v>
           </cell>
         </row>
         <row r="148">
           <cell r="GX148">
-            <v>12.5</v>
+            <v>0</v>
           </cell>
           <cell r="GY148">
             <v>87.5</v>
@@ -2938,24 +2938,24 @@
         </row>
         <row r="156">
           <cell r="GX156">
-            <v>0</v>
+            <v>100</v>
           </cell>
           <cell r="GY156">
-            <v>0</v>
+            <v>100</v>
           </cell>
           <cell r="GZ156">
-            <v>0</v>
+            <v>0.66499569432419037</v>
           </cell>
         </row>
         <row r="157">
           <cell r="GX157">
-            <v>0</v>
+            <v>6.666666666666667</v>
           </cell>
           <cell r="GY157">
-            <v>93.333333333333329</v>
+            <v>100</v>
           </cell>
           <cell r="GZ157">
-            <v>1.071384518427692</v>
+            <v>1.1479119840296699</v>
           </cell>
         </row>
         <row r="158">
@@ -3026,13 +3026,13 @@
         </row>
         <row r="164">
           <cell r="GX164">
-            <v>0</v>
+            <v>100</v>
           </cell>
           <cell r="GY164">
-            <v>0</v>
+            <v>100</v>
           </cell>
           <cell r="GZ164">
-            <v>0</v>
+            <v>0.46502795219584647</v>
           </cell>
         </row>
         <row r="165">
@@ -3092,7 +3092,7 @@
         </row>
         <row r="171">
           <cell r="GX171">
-            <v>100</v>
+            <v>0</v>
           </cell>
           <cell r="GY171">
             <v>100</v>
@@ -3114,7 +3114,7 @@
         </row>
         <row r="173">
           <cell r="GX173">
-            <v>86.666666666666671</v>
+            <v>0</v>
           </cell>
           <cell r="GY173">
             <v>100</v>
@@ -3323,13 +3323,13 @@
         </row>
         <row r="195">
           <cell r="GX195">
-            <v>0</v>
+            <v>100</v>
           </cell>
           <cell r="GY195">
-            <v>0</v>
+            <v>100</v>
           </cell>
           <cell r="GZ195">
-            <v>0</v>
+            <v>0.17500524310803686</v>
           </cell>
         </row>
         <row r="196">
@@ -3389,13 +3389,13 @@
         </row>
         <row r="203">
           <cell r="GX203">
-            <v>0</v>
+            <v>21.666666666666668</v>
           </cell>
           <cell r="GY203">
-            <v>0.83333333333333337</v>
+            <v>22.5</v>
           </cell>
           <cell r="GZ203">
-            <v>3.0895737700990743E-3</v>
+            <v>8.3418491792675006E-2</v>
           </cell>
         </row>
         <row r="204">
@@ -3422,13 +3422,13 @@
         </row>
         <row r="206">
           <cell r="GX206">
-            <v>0</v>
+            <v>21.666666666666668</v>
           </cell>
           <cell r="GY206">
-            <v>0.83333333333333337</v>
+            <v>22.5</v>
           </cell>
           <cell r="GZ206">
-            <v>2.0607633818105204E-3</v>
+            <v>5.564061130888405E-2</v>
           </cell>
         </row>
         <row r="207">
@@ -3565,10 +3565,10 @@
         </row>
         <row r="222">
           <cell r="GX222">
-            <v>3.9880686130860306</v>
+            <v>3.720351512171955</v>
           </cell>
           <cell r="GZ222">
-            <v>72.236620939816149</v>
+            <v>75.956972451988108</v>
           </cell>
         </row>
       </sheetData>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="I2" s="36">
         <f>AVERAGE(I3:I12)</f>
-        <v>77.35294117647058</v>
+        <v>79.411764705882376</v>
       </c>
       <c r="J2">
         <f>0.637484224224017*100</f>
@@ -4137,11 +4137,11 @@
       </c>
       <c r="I6" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY19</f>
-        <v>67.64705882352942</v>
+        <v>70.588235294117652</v>
       </c>
       <c r="J6" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ19</f>
-        <v>0.70983124633189787</v>
+        <v>0.7406934744332847</v>
       </c>
       <c r="K6" s="37">
         <f>G6*(H6/100)</f>
@@ -4181,11 +4181,11 @@
       </c>
       <c r="I7" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY20</f>
-        <v>67.64705882352942</v>
+        <v>70.588235294117652</v>
       </c>
       <c r="J7" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ20</f>
-        <v>0.56250727688017155</v>
+        <v>0.58696411500539636</v>
       </c>
       <c r="K7" s="37">
         <f t="shared" ref="K7:K12" si="3">G7*(H7/100)</f>
@@ -4225,11 +4225,11 @@
       </c>
       <c r="I8" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY21</f>
-        <v>67.64705882352942</v>
+        <v>70.588235294117652</v>
       </c>
       <c r="J8" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ21</f>
-        <v>0.11517986010520935</v>
+        <v>0.12018768010978367</v>
       </c>
       <c r="K8" s="37">
         <f t="shared" si="3"/>
@@ -4269,11 +4269,11 @@
       </c>
       <c r="I9" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY22</f>
-        <v>67.64705882352942</v>
+        <v>70.588235294117652</v>
       </c>
       <c r="J9" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ22</f>
-        <v>5.2232361655090744E-2</v>
+        <v>5.4503333900964256E-2</v>
       </c>
       <c r="K9" s="37">
         <f t="shared" si="3"/>
@@ -4313,11 +4313,11 @@
       </c>
       <c r="I10" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY23</f>
-        <v>67.64705882352942</v>
+        <v>70.588235294117652</v>
       </c>
       <c r="J10" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ23</f>
-        <v>4.2857294583694826E-2</v>
+        <v>4.4720655217768517E-2</v>
       </c>
       <c r="K10" s="37">
         <f t="shared" si="3"/>
@@ -4357,11 +4357,11 @@
       </c>
       <c r="I11" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY24</f>
-        <v>67.64705882352942</v>
+        <v>70.588235294117652</v>
       </c>
       <c r="J11" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ24</f>
-        <v>2.746817673803811E-2</v>
+        <v>2.8662445291865853E-2</v>
       </c>
       <c r="K11" s="37">
         <f>G11*(H11/100)</f>
@@ -4401,11 +4401,11 @@
       </c>
       <c r="I12" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY25</f>
-        <v>67.64705882352942</v>
+        <v>70.588235294117652</v>
       </c>
       <c r="J12" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ25</f>
-        <v>2.6946796374448012</v>
+        <v>2.8118396216815316</v>
       </c>
       <c r="K12" s="37">
         <f t="shared" si="3"/>
@@ -5761,11 +5761,11 @@
       <c r="G45" s="1"/>
       <c r="H45" s="36">
         <f>SUM(L46:L72)</f>
-        <v>1.0377599324696218</v>
+        <v>8.4563892835123181E-2</v>
       </c>
       <c r="I45" s="36">
         <f>AVERAGE(I46:I72)</f>
-        <v>33.452380952380963</v>
+        <v>39.801587301587311</v>
       </c>
       <c r="J45" s="36">
         <f>0.109556413087872*100</f>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="K45" s="39">
         <f t="shared" ref="K45" si="9">SUM(K46:K72)</f>
-        <v>264178.24839999987</v>
+        <v>21527.079999999994</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="H49" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX62</f>
-        <v>66.666666666666657</v>
+        <v>0</v>
       </c>
       <c r="I49" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY62</f>
@@ -5920,11 +5920,11 @@
       </c>
       <c r="K49" s="37">
         <f t="shared" si="10"/>
-        <v>53749.943999999974</v>
+        <v>0</v>
       </c>
       <c r="L49">
         <f t="shared" si="11"/>
-        <v>0.21114356913756399</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="H51" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX64</f>
-        <v>23.333333333333332</v>
+        <v>0</v>
       </c>
       <c r="I51" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY64</f>
@@ -5983,11 +5983,11 @@
       </c>
       <c r="K51" s="37">
         <f t="shared" ref="K51:K52" si="12">G51*(H51/100)</f>
-        <v>139292.56039999996</v>
+        <v>0</v>
       </c>
       <c r="L51">
         <f t="shared" ref="L51:L52" si="13">H51*D51/100</f>
-        <v>0.54717691161065607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
@@ -6166,23 +6166,23 @@
       </c>
       <c r="H56" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX69</f>
-        <v>66.666666666666657</v>
+        <v>33.333333333333329</v>
       </c>
       <c r="I56" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY69</f>
-        <v>66.666666666666657</v>
+        <v>100</v>
       </c>
       <c r="J56" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ69</f>
-        <v>0.14919361215366153</v>
+        <v>0.22379041823049231</v>
       </c>
       <c r="K56" s="37">
         <f t="shared" si="14"/>
-        <v>37979.599999999991</v>
+        <v>18989.799999999996</v>
       </c>
       <c r="L56">
         <f t="shared" si="15"/>
-        <v>0.14919361215366153</v>
+        <v>7.4596806076830766E-2</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
@@ -6210,23 +6210,23 @@
       </c>
       <c r="H57" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX70</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I57" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY70</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J57" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ70</f>
-        <v>0</v>
+        <v>9.9670867582924098E-3</v>
       </c>
       <c r="K57" s="37">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>2537.2800000000002</v>
       </c>
       <c r="L57">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>9.9670867582924098E-3</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
@@ -6754,7 +6754,7 @@
       </c>
       <c r="H71" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX84</f>
-        <v>23.333333333333332</v>
+        <v>0</v>
       </c>
       <c r="I71" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY84</f>
@@ -6766,11 +6766,11 @@
       </c>
       <c r="K71" s="37">
         <f t="shared" ref="K71:K72" si="21">G71*(H71/100)</f>
-        <v>22852.367999999999</v>
+        <v>0</v>
       </c>
       <c r="L71">
         <f t="shared" ref="L71:L72" si="22">H71*D71/100</f>
-        <v>8.9769964090847351E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.3">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="H72" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX85</f>
-        <v>23.333333333333332</v>
+        <v>0</v>
       </c>
       <c r="I72" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY85</f>
@@ -6810,11 +6810,11 @@
       </c>
       <c r="K72" s="37">
         <f t="shared" si="21"/>
-        <v>10303.776</v>
+        <v>0</v>
       </c>
       <c r="L72">
         <f t="shared" si="22"/>
-        <v>4.047587547689302E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="I73" s="36">
         <f>AVERAGE(I74:I88)</f>
-        <v>52.756410256410248</v>
+        <v>53.782051282051285</v>
       </c>
       <c r="J73" s="36">
         <f>0.42784181832181*100</f>
@@ -7261,11 +7261,11 @@
       </c>
       <c r="I84" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY97</f>
-        <v>85.833333333333329</v>
+        <v>99.166666666666671</v>
       </c>
       <c r="J84" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ97</f>
-        <v>0.12118559633167383</v>
+        <v>0.14001054333465232</v>
       </c>
       <c r="K84" s="37">
         <f t="shared" si="26"/>
@@ -7471,11 +7471,11 @@
       <c r="G89" s="1"/>
       <c r="H89" s="36">
         <f>SUM(L90:L118)</f>
-        <v>1.0300630024511452</v>
+        <v>1.6249459546870626</v>
       </c>
       <c r="I89" s="36">
         <f>AVERAGE(I90:I118)</f>
-        <v>55.486111111111107</v>
+        <v>59.097222222222229</v>
       </c>
       <c r="J89" s="36">
         <f>0.423925829955751*100</f>
@@ -7483,7 +7483,7 @@
       </c>
       <c r="K89" s="39">
         <f>SUM(K90:K118)</f>
-        <v>262218.87280000001</v>
+        <v>413655.76240000001</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.3">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="H94" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX107</f>
-        <v>6.666666666666667</v>
+        <v>0</v>
       </c>
       <c r="I94" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY107</f>
@@ -7649,11 +7649,11 @@
       </c>
       <c r="K94" s="37">
         <f t="shared" ref="K94:K98" si="30">G94*(H94/100)</f>
-        <v>3290.4847999999997</v>
+        <v>0</v>
       </c>
       <c r="L94">
         <f t="shared" ref="L94:L98" si="31">H94*D94/100</f>
-        <v>1.2925868441182072E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.3">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="H95" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX108</f>
-        <v>6.666666666666667</v>
+        <v>0</v>
       </c>
       <c r="I95" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY108</f>
@@ -7693,11 +7693,11 @@
       </c>
       <c r="K95" s="37">
         <f t="shared" si="30"/>
-        <v>14776.237599999999</v>
+        <v>0</v>
       </c>
       <c r="L95">
         <f t="shared" si="31"/>
-        <v>5.8044852014890902E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.3">
@@ -7725,23 +7725,23 @@
       </c>
       <c r="H96" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX109</f>
-        <v>6.666666666666667</v>
+        <v>10</v>
       </c>
       <c r="I96" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY109</f>
-        <v>71.666666666666671</v>
+        <v>81.666666666666671</v>
       </c>
       <c r="J96" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ109</f>
-        <v>2.0594678035204805</v>
+        <v>2.3468354040117103</v>
       </c>
       <c r="K96" s="37">
         <f t="shared" si="30"/>
-        <v>48769.319999999992</v>
+        <v>73153.98</v>
       </c>
       <c r="L96">
         <f t="shared" si="31"/>
-        <v>0.19157840032748655</v>
+        <v>0.28736760049122984</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.3">
@@ -7769,23 +7769,23 @@
       </c>
       <c r="H97" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX110</f>
-        <v>6.666666666666667</v>
+        <v>10</v>
       </c>
       <c r="I97" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY110</f>
-        <v>71.666666666666671</v>
+        <v>81.666666666666671</v>
       </c>
       <c r="J97" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ110</f>
-        <v>0.15681226930358988</v>
+        <v>0.17869305106688149</v>
       </c>
       <c r="K97" s="37">
         <f t="shared" si="30"/>
-        <v>3713.4</v>
+        <v>5570.1</v>
       </c>
       <c r="L97">
         <f t="shared" si="31"/>
-        <v>1.4587187842194409E-2</v>
+        <v>2.1880781763291609E-2</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.3">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="H100" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX113</f>
-        <v>13.333333333333334</v>
+        <v>0</v>
       </c>
       <c r="I100" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY113</f>
@@ -7888,11 +7888,11 @@
       </c>
       <c r="K100" s="37">
         <f t="shared" ref="K100:K102" si="32">G100*(H100/100)</f>
-        <v>12900.486399999998</v>
+        <v>0</v>
       </c>
       <c r="L100">
         <f t="shared" ref="L100:L102" si="33">H100*D100/100</f>
-        <v>5.0676420092765205E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.3">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="H101" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX114</f>
-        <v>13.333333333333334</v>
+        <v>0</v>
       </c>
       <c r="I101" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY114</f>
@@ -7932,11 +7932,11 @@
       </c>
       <c r="K101" s="37">
         <f t="shared" si="32"/>
-        <v>95827.742399999988</v>
+        <v>0</v>
       </c>
       <c r="L101">
         <f t="shared" si="33"/>
-        <v>0.37643595596548118</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.3">
@@ -7964,7 +7964,7 @@
       </c>
       <c r="H102" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX115</f>
-        <v>13.333333333333334</v>
+        <v>0</v>
       </c>
       <c r="I102" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY115</f>
@@ -7976,11 +7976,11 @@
       </c>
       <c r="K102" s="37">
         <f t="shared" si="32"/>
-        <v>35231.2448</v>
+        <v>0</v>
       </c>
       <c r="L102">
         <f t="shared" si="33"/>
-        <v>0.13839736786016454</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.3">
@@ -8071,23 +8071,23 @@
       </c>
       <c r="H105" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX118</f>
-        <v>13.333333333333334</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="I105" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY118</f>
-        <v>93.333333333333329</v>
+        <v>100</v>
       </c>
       <c r="J105" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ118</f>
-        <v>0.20227048611312734</v>
+        <v>0.21671837797835072</v>
       </c>
       <c r="K105" s="37">
         <f t="shared" si="34"/>
-        <v>7355.88</v>
+        <v>3677.94</v>
       </c>
       <c r="L105">
         <f t="shared" si="35"/>
-        <v>2.8895783730446763E-2</v>
+        <v>1.4447891865223382E-2</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.3">
@@ -8115,23 +8115,23 @@
       </c>
       <c r="H106" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX119</f>
-        <v>13.333333333333334</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="I106" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY119</f>
-        <v>93.333333333333329</v>
+        <v>100</v>
       </c>
       <c r="J106" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ119</f>
-        <v>0.34520944020804223</v>
+        <v>0.36986725736575954</v>
       </c>
       <c r="K106" s="37">
         <f t="shared" si="34"/>
-        <v>12554.076799999999</v>
+        <v>6277.0383999999995</v>
       </c>
       <c r="L106">
         <f t="shared" si="35"/>
-        <v>4.9315634315434613E-2</v>
+        <v>2.4657817157717307E-2</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.3">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="H108" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX121</f>
-        <v>6.666666666666667</v>
+        <v>0</v>
       </c>
       <c r="I108" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY121</f>
@@ -8190,11 +8190,11 @@
       </c>
       <c r="K108" s="37">
         <f t="shared" ref="K108:K118" si="36">G108*(H108/100)</f>
-        <v>12800</v>
+        <v>0</v>
       </c>
       <c r="L108">
         <f t="shared" ref="L108:L118" si="37">H108*D108/100</f>
-        <v>5.0281683734606675E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.3">
@@ -8222,7 +8222,7 @@
       </c>
       <c r="H109" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX122</f>
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="I109" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY122</f>
@@ -8234,11 +8234,11 @@
       </c>
       <c r="K109" s="37">
         <f t="shared" si="36"/>
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="L109">
         <f t="shared" si="37"/>
-        <v>5.89238481264922E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.3">
@@ -8442,23 +8442,23 @@
       </c>
       <c r="H114" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX127</f>
-        <v>0</v>
+        <v>26.666666666666668</v>
       </c>
       <c r="I114" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY127</f>
-        <v>0</v>
+        <v>26.666666666666668</v>
       </c>
       <c r="J114" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ127</f>
-        <v>0</v>
+        <v>0.63829593170480026</v>
       </c>
       <c r="K114" s="37">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>162488.35199999998</v>
       </c>
       <c r="L114">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>0.63829593170480026</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.3">
@@ -8574,23 +8574,23 @@
       </c>
       <c r="H117" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX130</f>
-        <v>0</v>
+        <v>26.666666666666668</v>
       </c>
       <c r="I117" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY130</f>
-        <v>0</v>
+        <v>26.666666666666668</v>
       </c>
       <c r="J117" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ130</f>
-        <v>0</v>
+        <v>0.63829593170480026</v>
       </c>
       <c r="K117" s="37">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>162488.35199999998</v>
       </c>
       <c r="L117">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>0.63829593170480026</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.3">
@@ -8656,11 +8656,11 @@
       <c r="G119" s="1"/>
       <c r="H119" s="36">
         <f>SUM(L120:L138)</f>
-        <v>0.22846010844650061</v>
+        <v>0.29373612456539866</v>
       </c>
       <c r="I119" s="36">
         <f>AVERAGE(I120:I138)</f>
-        <v>51.858974358974358</v>
+        <v>54.679487179487182</v>
       </c>
       <c r="J119" s="36">
         <f>0.39822979986831*100</f>
@@ -8668,7 +8668,7 @@
       </c>
       <c r="K119" s="39">
         <f t="shared" ref="K119" si="38">SUM(K120:K138)</f>
-        <v>58158.143699999993</v>
+        <v>74775.188799999989</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.3">
@@ -8759,23 +8759,23 @@
       </c>
       <c r="H122" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX135</f>
-        <v>6.666666666666667</v>
+        <v>10</v>
       </c>
       <c r="I122" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY135</f>
-        <v>71.666666666666671</v>
+        <v>81.666666666666671</v>
       </c>
       <c r="J122" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ135</f>
-        <v>1.4756411390902628</v>
+        <v>1.6815445538470437</v>
       </c>
       <c r="K122" s="37">
         <f t="shared" si="39"/>
-        <v>34943.986399999994</v>
+        <v>52415.979599999991</v>
       </c>
       <c r="L122">
         <f t="shared" si="40"/>
-        <v>0.13726894317118726</v>
+        <v>0.20590341475678087</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.3">
@@ -8803,23 +8803,23 @@
       </c>
       <c r="H123" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX136</f>
-        <v>6.666666666666667</v>
+        <v>10</v>
       </c>
       <c r="I123" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY136</f>
-        <v>71.666666666666671</v>
+        <v>81.666666666666671</v>
       </c>
       <c r="J123" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ136</f>
-        <v>8.0017144871276868E-2</v>
+        <v>9.1182327876571323E-2</v>
       </c>
       <c r="K123" s="37">
         <f t="shared" si="39"/>
-        <v>1894.8495999999998</v>
+        <v>2842.2744000000002</v>
       </c>
       <c r="L123">
         <f t="shared" si="40"/>
-        <v>7.4434553368629653E-3</v>
+        <v>1.1165183005294448E-2</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.3">
@@ -9105,23 +9105,23 @@
       </c>
       <c r="H131" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX144</f>
-        <v>6.666666666666667</v>
+        <v>10</v>
       </c>
       <c r="I131" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY144</f>
-        <v>71.666666666666671</v>
+        <v>81.666666666666671</v>
       </c>
       <c r="J131" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ144</f>
-        <v>0.47541571359024271</v>
+        <v>0.54175278990516029</v>
       </c>
       <c r="K131" s="37">
         <f t="shared" ref="K131" si="43">G131*(H131/100)</f>
-        <v>11258.103200000001</v>
+        <v>16887.1548</v>
       </c>
       <c r="L131">
         <f t="shared" ref="L131" si="44">H131*D131/100</f>
-        <v>4.4224717543278391E-2</v>
+        <v>6.6337076314917587E-2</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.3">
@@ -9172,11 +9172,11 @@
       </c>
       <c r="I133" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY146</f>
-        <v>71.666666666666671</v>
+        <v>78.333333333333329</v>
       </c>
       <c r="J133" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ146</f>
-        <v>0.1110523427503621</v>
+        <v>0.12138279323876788</v>
       </c>
       <c r="K133" s="37">
         <f t="shared" ref="K133" si="46">G133*(H133/100)</f>
@@ -9231,7 +9231,7 @@
       </c>
       <c r="H135" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX148</f>
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="I135" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY148</f>
@@ -9243,11 +9243,11 @@
       </c>
       <c r="K135" s="37">
         <f t="shared" ref="K135" si="48">G135*(H135/100)</f>
-        <v>7431.4245000000001</v>
+        <v>0</v>
       </c>
       <c r="L135">
         <f t="shared" ref="L135" si="49">H135*D135/100</f>
-        <v>2.9192541906766213E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.3">
@@ -9376,11 +9376,11 @@
       <c r="G139" s="1"/>
       <c r="H139" s="36">
         <f>SUM(L140:L205)</f>
-        <v>1.4901451508140933</v>
+        <v>1.5154651211797012</v>
       </c>
       <c r="I139" s="36">
         <f>AVERAGE(I140:I205)</f>
-        <v>36.251686909581636</v>
+        <v>42.392037786774644</v>
       </c>
       <c r="J139" s="36">
         <f>0.414110048029731*100</f>
@@ -9388,7 +9388,7 @@
       </c>
       <c r="K139" s="39">
         <f>SUM(K140:K205)</f>
-        <v>379340.07999999996</v>
+        <v>385785.67999999993</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.3">
@@ -9523,23 +9523,23 @@
       </c>
       <c r="H143" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX156</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I143" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY156</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J143" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ156</f>
-        <v>0</v>
+        <v>0.66499569432419037</v>
       </c>
       <c r="K143" s="37">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>169285.19999999998</v>
       </c>
       <c r="L143">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>0.66499569432419037</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.3">
@@ -9567,23 +9567,23 @@
       </c>
       <c r="H144" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX157</f>
-        <v>0</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="I144" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY157</f>
-        <v>93.333333333333329</v>
+        <v>100</v>
       </c>
       <c r="J144" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ157</f>
-        <v>1.071384518427692</v>
+        <v>1.1479119840296699</v>
       </c>
       <c r="K144" s="37">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>19481.28</v>
       </c>
       <c r="L144">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>7.6527465601977998E-2</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.3">
@@ -9875,23 +9875,23 @@
       </c>
       <c r="H151" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX164</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I151" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY164</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J151" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ164</f>
-        <v>0</v>
+        <v>0.46502795219584647</v>
       </c>
       <c r="K151" s="37">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>118380.23999999999</v>
       </c>
       <c r="L151">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>0.46502795219584647</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.3">
@@ -10158,7 +10158,7 @@
       </c>
       <c r="H158" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX171</f>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I158" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY171</f>
@@ -10170,11 +10170,11 @@
       </c>
       <c r="K158" s="37">
         <f t="shared" ref="K158:K163" si="54">G158*(H158/100)</f>
-        <v>62940.360000000008</v>
+        <v>0</v>
       </c>
       <c r="L158">
         <f t="shared" ref="L158:L163" si="55">H158*D158/100</f>
-        <v>0.24724588091111632</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.3">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="H160" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX173</f>
-        <v>86.666666666666671</v>
+        <v>0</v>
       </c>
       <c r="I160" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY173</f>
@@ -10258,11 +10258,11 @@
       </c>
       <c r="K160" s="37">
         <f t="shared" si="54"/>
-        <v>316399.71999999997</v>
+        <v>0</v>
       </c>
       <c r="L160">
         <f t="shared" si="55"/>
-        <v>1.2428992699029771</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.3">
@@ -11142,23 +11142,23 @@
       </c>
       <c r="H182" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX195</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I182" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY195</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J182" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ195</f>
-        <v>0</v>
+        <v>0.17500524310803686</v>
       </c>
       <c r="K182" s="37">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>44550.36</v>
       </c>
       <c r="L182">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>0.17500524310803686</v>
       </c>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.3">
@@ -11444,23 +11444,23 @@
       </c>
       <c r="H190" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX203</f>
-        <v>0</v>
+        <v>21.666666666666668</v>
       </c>
       <c r="I190" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY203</f>
-        <v>0.83333333333333337</v>
+        <v>22.5</v>
       </c>
       <c r="J190" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ203</f>
-        <v>3.0895737700990743E-3</v>
+        <v>8.3418491792675006E-2</v>
       </c>
       <c r="K190" s="37">
         <f t="shared" si="64"/>
-        <v>0</v>
+        <v>20449</v>
       </c>
       <c r="L190">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>8.0328918022575926E-2</v>
       </c>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.3">
@@ -11576,23 +11576,23 @@
       </c>
       <c r="H193" s="36">
         <f>[1]PLS_MODELO_LIVRE!GX206</f>
-        <v>0</v>
+        <v>21.666666666666668</v>
       </c>
       <c r="I193" s="36">
         <f>[1]PLS_MODELO_LIVRE!GY206</f>
-        <v>0.83333333333333337</v>
+        <v>22.5</v>
       </c>
       <c r="J193" s="36">
         <f>[1]PLS_MODELO_LIVRE!GZ206</f>
-        <v>2.0607633818105204E-3</v>
+        <v>5.564061130888405E-2</v>
       </c>
       <c r="K193" s="37">
         <f t="shared" si="64"/>
-        <v>0</v>
+        <v>13639.6</v>
       </c>
       <c r="L193">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>5.3579847927073529E-2</v>
       </c>
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.3">
@@ -12205,18 +12205,18 @@
       </c>
       <c r="H209" s="36">
         <f>[1]PLS_MODELO_LIVRE!$GX$222</f>
-        <v>3.9880686130860306</v>
+        <v>3.720351512171955</v>
       </c>
       <c r="I209" t="s">
         <v>398</v>
       </c>
       <c r="J209" s="36">
         <f>[1]PLS_MODELO_LIVRE!$GZ$222</f>
-        <v>72.236620939816149</v>
+        <v>75.956972451988108</v>
       </c>
       <c r="K209" s="37">
         <f>K139+K119+K89+K73+K45+K27+K13+K2+K206</f>
-        <v>1015226.1112999998</v>
+        <v>947074.47759999987</v>
       </c>
     </row>
   </sheetData>
